--- a/backend/wp_templates/D/D3 预收账款.xlsx
+++ b/backend/wp_templates/D/D3 预收账款.xlsx
@@ -25,11 +25,6 @@
     <sheet name="预收账款检查表D3-7" sheetId="64" r:id="rId11"/>
     <sheet name="GT_Custom" sheetId="35" state="hidden" r:id="rId12"/>
   </sheets>
-  <externalReferences>
-    <externalReference r:id="rId13"/>
-    <externalReference r:id="rId14"/>
-    <externalReference r:id="rId15"/>
-  </externalReferences>
   <definedNames>
     <definedName name="AFV">#REF!</definedName>
     <definedName name="AS2DocOpenMode">"AS2DocumentEdit"</definedName>
@@ -37,9 +32,7 @@
     <definedName name="CDE">#REF!</definedName>
     <definedName name="DEX">#REF!</definedName>
     <definedName name="EDC">#REF!</definedName>
-    <definedName name="FAD">[1]Breakdown!#REF!</definedName>
     <definedName name="FASD">#REF!</definedName>
-    <definedName name="FEDC">'[2]2004'!#REF!</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">底稿目录!$A$1:$F$21</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="6">'调整分录汇总表D3-3'!$A$1:$J$20</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="4">'附注披露信息(国企)'!$A$1:$D$15</definedName>
@@ -58,9 +51,7 @@
     <definedName name="XAQ">#REF!</definedName>
     <definedName name="XCD">#REF!</definedName>
     <definedName name="XREF_COLUMN_1">#REF!</definedName>
-    <definedName name="XREF_COLUMN_2">[1]Breakdown!#REF!</definedName>
     <definedName name="XREF_COLUMN_3">#REF!</definedName>
-    <definedName name="XREF_COLUMN_5">'[2]2004'!#REF!</definedName>
     <definedName name="XRefActiveRow">#REF!</definedName>
     <definedName name="XRefColumnsCount">2</definedName>
     <definedName name="XRefCopy1">#REF!</definedName>
@@ -74,7 +65,6 @@
     <definedName name="XRefPaste3">#REF!</definedName>
     <definedName name="XRefPaste3Row">#REF!</definedName>
     <definedName name="XRefPasteRangeCount">2</definedName>
-    <definedName name="本循环科目">[3]索引!$D$15:$D$76</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
   <extLst>
@@ -7573,7689 +7563,6 @@
 </styleSheet>
 </file>
 
-<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="Breakdown"/>
-      <sheetName val="徐淮分部"/>
-      <sheetName val="Stock turnover"/>
-      <sheetName val="Prov-Mvmt"/>
-      <sheetName val="Obsolete Stock List"/>
-      <sheetName val="Negative sales"/>
-      <sheetName val="XREF"/>
-      <sheetName val="Tickmarks"/>
-      <sheetName val="B"/>
-      <sheetName val="2009年受限统计表"/>
-      <sheetName val="银行存款"/>
-      <sheetName val="04"/>
-      <sheetName val="03"/>
-      <sheetName val="表头"/>
-      <sheetName val="其他应收个人"/>
-      <sheetName val="Summary"/>
-      <sheetName val="35.1租赁明细"/>
-      <sheetName val="1"/>
-      <sheetName val="2"/>
-      <sheetName val="3"/>
-      <sheetName val="4"/>
-      <sheetName val="5"/>
-      <sheetName val="6"/>
-      <sheetName val="7"/>
-      <sheetName val="8"/>
-      <sheetName val="9"/>
-      <sheetName val="10"/>
-      <sheetName val="11"/>
-      <sheetName val="12"/>
-      <sheetName val="1-12"/>
-      <sheetName val="3 (2)"/>
-      <sheetName val="4 (2)"/>
-      <sheetName val="5 (2)"/>
-      <sheetName val="6 (2)"/>
-      <sheetName val="7 (2)"/>
-      <sheetName val="8 (2)"/>
-      <sheetName val="9 (2)"/>
-      <sheetName val="10 (2)"/>
-      <sheetName val="11 (2)"/>
-      <sheetName val="12 (2)"/>
-      <sheetName val="1 (2)"/>
-      <sheetName val="2 (2)"/>
-      <sheetName val="5月"/>
-      <sheetName val="6月"/>
-      <sheetName val="1-10月明细表"/>
-      <sheetName val="索引"/>
-      <sheetName val="Investment Property"/>
-      <sheetName val="대외공문"/>
-      <sheetName val="2004"/>
-      <sheetName val="资产负债表"/>
-      <sheetName val="营业费用测试"/>
-      <sheetName val="利润及分配表"/>
-      <sheetName val="资产方"/>
-      <sheetName val="减值准备表"/>
-      <sheetName val="负债方"/>
-      <sheetName val="系统参数设置"/>
-      <sheetName val="固定资产清单"/>
-      <sheetName val="#REF!"/>
-      <sheetName val="预收帐款明细"/>
-      <sheetName val="项目成本-制作成本明细G1-6"/>
-      <sheetName val="固定资产明细"/>
-      <sheetName val="kmmc"/>
-      <sheetName val="科目表"/>
-      <sheetName val="现金明细（勿删）"/>
-      <sheetName val="选择键"/>
-      <sheetName val="&lt;原报&gt;资产负债表"/>
-      <sheetName val="W"/>
-      <sheetName val="其他应收款－个人借款明细"/>
-      <sheetName val="无正式发票的支出"/>
-      <sheetName val="E1020"/>
-      <sheetName val="UFPrn20080707101342"/>
-      <sheetName val="库龄"/>
-      <sheetName val="Audit Sampling Table"/>
-      <sheetName val="For Ref"/>
-      <sheetName val="Inventory"/>
-      <sheetName val="PFS"/>
-      <sheetName val="土地"/>
-      <sheetName val="建筑工程"/>
-      <sheetName val="装潢工程"/>
-      <sheetName val="间接费用"/>
-      <sheetName val="利息资本化"/>
-      <sheetName val="配套工程"/>
-      <sheetName val="机电工程"/>
-      <sheetName val="Payment test"/>
-      <sheetName val="RM"/>
-      <sheetName val="在途物资"/>
-      <sheetName val="WIP"/>
-      <sheetName val="FG"/>
-      <sheetName val="跌价准备"/>
-      <sheetName val="跌价准备清单"/>
-      <sheetName val="Sample Design"/>
-      <sheetName val="审计调整"/>
-      <sheetName val="生产成本"/>
-      <sheetName val="完"/>
-      <sheetName val="企业表一"/>
-      <sheetName val="M-5C"/>
-      <sheetName val="M-5A"/>
-      <sheetName val="表头（请先填写）"/>
-      <sheetName val="200)年受限统计表"/>
-      <sheetName val="35.1租赁明滆"/>
-      <sheetName val="PER SALES ORG"/>
-      <sheetName val="eqpmad2"/>
-      <sheetName val="本期报表"/>
-      <sheetName val="Repayment Summary"/>
-      <sheetName val="Breakdown-本部"/>
-      <sheetName val="DATA"/>
-      <sheetName val="UFPrn20061113135115"/>
-      <sheetName val="KM"/>
-      <sheetName val="inventory list index"/>
-      <sheetName val="costing"/>
-      <sheetName val="差异分摊计算表"/>
-      <sheetName val="调整分录汇总"/>
-      <sheetName val="PTC"/>
-      <sheetName val="Stock turnove_x0002_"/>
-      <sheetName val="For Report"/>
-      <sheetName val="BKD"/>
-      <sheetName val="商品明細"/>
-      <sheetName val="PFD"/>
-      <sheetName val="开发产品-三期"/>
-      <sheetName val="PFS SAR"/>
-      <sheetName val="Property For Rental"/>
-      <sheetName val="开发成本汇总表-南块"/>
-      <sheetName val="南块会所成本调整及PFS"/>
-      <sheetName val="开发成本汇总表-北块"/>
-      <sheetName val="北块PFS"/>
-      <sheetName val="会所"/>
-      <sheetName val="PUD"/>
-      <sheetName val="开发成本汇总表"/>
-      <sheetName val="项目 Summary"/>
-      <sheetName val="Confirmation Control"/>
-      <sheetName val="Payment Detail"/>
-      <sheetName val="项目"/>
-      <sheetName val="2006"/>
-      <sheetName val="建筑"/>
-      <sheetName val="机电"/>
-      <sheetName val="装潢"/>
-      <sheetName val="在途存货清单及测试"/>
-      <sheetName val="Appendix"/>
-      <sheetName val="3mon-1Year"/>
-      <sheetName val="per mgt"/>
-      <sheetName val="above5y"/>
-      <sheetName val="1-3MON"/>
-      <sheetName val="1year-5year"/>
-      <sheetName val="个人借款明细"/>
-      <sheetName val="POWER ASSUMPTIONS"/>
-      <sheetName val="lookup"/>
-      <sheetName val="Unit Information"/>
-      <sheetName val="Company Information"/>
-      <sheetName val="基础数据"/>
-      <sheetName val="原材料余额表"/>
-      <sheetName val="21710103"/>
-      <sheetName val="2171010501"/>
-      <sheetName val="2171010502"/>
-      <sheetName val="217102"/>
-      <sheetName val="cover"/>
-      <sheetName val="Toolbox"/>
-      <sheetName val="折旧测试2007"/>
-      <sheetName val="剥离前"/>
-      <sheetName val="Stock turnove_x005f_x0002_"/>
-      <sheetName val="中山低值"/>
-      <sheetName val="YS02-02"/>
-      <sheetName val="主营业务税金及附加Dy"/>
-      <sheetName val="应收账款Dy"/>
-      <sheetName val="original"/>
-      <sheetName val="C_301"/>
-      <sheetName val="C_311"/>
-      <sheetName val="C_318"/>
-      <sheetName val="Sheet1"/>
-      <sheetName val="目錄"/>
-      <sheetName val="税金汇总"/>
-      <sheetName val="1-6yue"/>
-      <sheetName val="Worksheet in 8240 COS breakdown"/>
-      <sheetName val="余额表"/>
-      <sheetName val="09差异分摊计算表"/>
-      <sheetName val="08差异分摊计算表"/>
-      <sheetName val="材料差异"/>
-      <sheetName val="收入明细－按客户"/>
-      <sheetName val="内部往来"/>
-      <sheetName val="材料采购-入库"/>
-      <sheetName val="原材料－其他"/>
-      <sheetName val="材料成本差异－运费等"/>
-      <sheetName val="_______"/>
-      <sheetName val="核算项目余额表"/>
-      <sheetName val="应交税金"/>
-      <sheetName val="G.1R-Shou COP Gf"/>
-      <sheetName val="成本调整明细表"/>
-      <sheetName val="XL4Poppy"/>
-      <sheetName val="凤县折旧测算"/>
-      <sheetName val="BALANCE SHEET"/>
-      <sheetName val="FA-2"/>
-      <sheetName val="7-11销售"/>
-      <sheetName val="制造费用"/>
-      <sheetName val="关联交易-存款"/>
-      <sheetName val="报表科目"/>
-      <sheetName val="应收账款贷方余额表"/>
-      <sheetName val="应收账款借方余额表"/>
-      <sheetName val="应收账款余额表"/>
-      <sheetName val="试算"/>
-      <sheetName val="附注汇总"/>
-      <sheetName val="内部销售明细表"/>
-      <sheetName val="预付账款Dy"/>
-      <sheetName val="STATPARA"/>
-      <sheetName val="Lead"/>
-      <sheetName val="CF"/>
-      <sheetName val="preBS"/>
-      <sheetName val="preCF"/>
-      <sheetName val="preIS"/>
-      <sheetName val="preCE"/>
-      <sheetName val="TB"/>
-      <sheetName val="主营业务成本Dy"/>
-      <sheetName val="分录"/>
-      <sheetName val="存货_包装物"/>
-      <sheetName val="存货_库存商品mx"/>
-      <sheetName val="存货_生产成本mx1"/>
-      <sheetName val="存货_委托加工物资mx"/>
-      <sheetName val="存货_制造费用Mx"/>
-      <sheetName val="坏账准备_其他应收款Dy"/>
-      <sheetName val="营业外收入Dy"/>
-      <sheetName val="固定资产Dy"/>
-      <sheetName val="累计折旧Dy"/>
-      <sheetName val="界面"/>
-      <sheetName val="Payroll"/>
-      <sheetName val="递延税款Dy"/>
-      <sheetName val="资本公积Dy"/>
-      <sheetName val="盈余公积Dy"/>
-      <sheetName val="未分配利润Dy"/>
-      <sheetName val="补贴收入Dy"/>
-      <sheetName val="所得税Dy"/>
-      <sheetName val="坏账准备_应收账款Dy"/>
-      <sheetName val="预收账款Dy"/>
-      <sheetName val="应交税金Dy"/>
-      <sheetName val="其他应交款Dy"/>
-      <sheetName val="主营业务收入Dy"/>
-      <sheetName val="坏账准备_应收账款Mx"/>
-      <sheetName val="专项应付款Dy"/>
-      <sheetName val="Ðì»´·Ö²¿"/>
-      <sheetName val="工作表目录"/>
-      <sheetName val="明细表"/>
-      <sheetName val="固定资产(原表)"/>
-      <sheetName val="Worksheet in 5440 Inventory"/>
-      <sheetName val="账面外销"/>
-      <sheetName val="Control"/>
-      <sheetName val="Pre-operating Exp"/>
-      <sheetName val="Miscellaneous Exp."/>
-      <sheetName val="Rental 2002"/>
-      <sheetName val="Rental 2001"/>
-      <sheetName val="成本倒扎"/>
-      <sheetName val="IMPORT"/>
-      <sheetName val="账龄4"/>
-      <sheetName val="披露表(标准)"/>
-      <sheetName val="披露表(国资)"/>
-      <sheetName val="邻酮定乙酚发出测试"/>
-      <sheetName val="材料采购－原材料（购价）"/>
-      <sheetName val="房屋及建筑物"/>
-      <sheetName val="委托加工材料"/>
-      <sheetName val="上期试算"/>
-      <sheetName val="累计产销存"/>
-      <sheetName val="营业外收支明细"/>
-      <sheetName val="PL Statement_CN_WK"/>
-      <sheetName val="三兴2"/>
-      <sheetName val="附注披露信息(上市公司)G4-1"/>
-      <sheetName val="Aging 06-03-2002"/>
-      <sheetName val="DI-ESTI"/>
-      <sheetName val="Ctinh 10kV"/>
-      <sheetName val="Source"/>
-      <sheetName val="dxnsjtempsheet"/>
-      <sheetName val="试算号"/>
-      <sheetName val="2-试算"/>
-      <sheetName val="1-平衡表"/>
-      <sheetName val="工程结算明细账1-6月"/>
-      <sheetName val="低值易耗品"/>
-      <sheetName val="劳务费"/>
-      <sheetName val="折旧"/>
-      <sheetName val="工资"/>
-      <sheetName val="福利费"/>
-      <sheetName val="水电费"/>
-      <sheetName val="办公费"/>
-      <sheetName val="业务招待费"/>
-      <sheetName val="差"/>
-      <sheetName val="机"/>
-      <sheetName val="劳保"/>
-      <sheetName val="通迅费"/>
-      <sheetName val="修"/>
-      <sheetName val="科目名称表"/>
-      <sheetName val="表头信息"/>
-      <sheetName val="国内CP2产品收入明细"/>
-      <sheetName val="Sheet9"/>
-      <sheetName val="05大桥分卡片"/>
-      <sheetName val="KKKKKKKK"/>
-      <sheetName val="试算16"/>
-      <sheetName val="试算17"/>
-      <sheetName val="Stock turnove_x005f_x005f_x005f_x0002_"/>
-      <sheetName val="2.대외공문"/>
-      <sheetName val="US Codes"/>
-      <sheetName val="消费税率"/>
-      <sheetName val="N1"/>
-      <sheetName val="Reconciliation连云港"/>
-      <sheetName val="Ex Diff"/>
-      <sheetName val="银行"/>
-      <sheetName val="1月"/>
-      <sheetName val="至10月末全成本汇总表（动态）"/>
-      <sheetName val="Stock turnove_x005f_x005f_x005f_x005f_x005f"/>
-      <sheetName val="FS"/>
-      <sheetName val="gl"/>
-      <sheetName val="Adm"/>
-      <sheetName val="sell"/>
-      <sheetName val="Fin"/>
-      <sheetName val="Calendar"/>
-      <sheetName val="Disclosure"/>
-      <sheetName val="Segment info"/>
-      <sheetName val="Adjustment"/>
-      <sheetName val="Count Diff"/>
-      <sheetName val="General Instruction"/>
-      <sheetName val="Sample"/>
-      <sheetName val="InventoryList"/>
-      <sheetName val="Stock List"/>
-      <sheetName val="Trina Breakdown"/>
-      <sheetName val="2007 Q3"/>
-      <sheetName val="Breakdown-Trina"/>
-      <sheetName val="Breakdown-TEI"/>
-      <sheetName val="Note"/>
-      <sheetName val="Audit Procedure"/>
-      <sheetName val="Turnover"/>
-      <sheetName val="FG Mov"/>
-      <sheetName val="#REF"/>
-      <sheetName val="For disclosure"/>
-      <sheetName val="CZ AJE summary"/>
-      <sheetName val="折旧测算"/>
-      <sheetName val="12月份品种酒生产月报表"/>
-      <sheetName val="物料收发汇总表"/>
-      <sheetName val="应收账款"/>
-      <sheetName val="营业外支出Dy"/>
-      <sheetName val="应付账款Dy"/>
-      <sheetName val="应付账款mx"/>
-      <sheetName val="待摊费用mx"/>
-      <sheetName val="固定资产减值准备mx"/>
-      <sheetName val="累计折旧mx"/>
-      <sheetName val="应付福利费mx"/>
-      <sheetName val="应付工资mx"/>
-      <sheetName val="预提费用mx"/>
-      <sheetName val="在建工程mx"/>
-      <sheetName val="制造费用mx"/>
-      <sheetName val="2008年"/>
-      <sheetName val="余额表10-12"/>
-      <sheetName val="Macro1"/>
-      <sheetName val="XL4Test5"/>
-      <sheetName val="多级销售汇总表（备用）"/>
-      <sheetName val="上期报表"/>
-      <sheetName val="BJ Expenses"/>
-      <sheetName val="Sample Rev"/>
-      <sheetName val="Sample IS"/>
-      <sheetName val="Probability View"/>
-      <sheetName val="FY04ExpDetail"/>
-      <sheetName val="VODAC"/>
-      <sheetName val="sumdepn01"/>
-      <sheetName val="降低额统计(会签)"/>
-      <sheetName val="附件25.2-销售收入"/>
-      <sheetName val="高层领导支持计划"/>
-      <sheetName val="8月乘用车分公司期间费用统计表"/>
-      <sheetName val="소상 &quot;1&quot;"/>
-      <sheetName val="Sheet2"/>
-      <sheetName val="培训执行汇总"/>
-      <sheetName val="외주현황.wq1"/>
-      <sheetName val="薪酬表"/>
-      <sheetName val="收入明细账"/>
-      <sheetName val="PRC-BS-SZ"/>
-      <sheetName val="名称"/>
-      <sheetName val="A3-1合并汇总报表"/>
-      <sheetName val="参数"/>
-      <sheetName val="序时账"/>
-      <sheetName val="所得税明细表"/>
-      <sheetName val="other lia"/>
-      <sheetName val="prepayment"/>
-      <sheetName val="related co"/>
-      <sheetName val="sel"/>
-      <sheetName val="AR"/>
-      <sheetName val="15287贵阳市乌当区天网工程"/>
-      <sheetName val="Coach Chassis (inventory)"/>
-      <sheetName val="10年12月差异分摊计算表"/>
-      <sheetName val="管理费用审定表"/>
-      <sheetName val="基本信息输入"/>
-      <sheetName val="分录汇总表"/>
-      <sheetName val="Sheet1 (11)"/>
-      <sheetName val="封面"/>
-      <sheetName val="Inventory list provison"/>
-      <sheetName val="NRV test"/>
-      <sheetName val="FG Aging provision"/>
-      <sheetName val="Breakdown "/>
-      <sheetName val="Detail list 0512"/>
-      <sheetName val="Detail list 0510"/>
-      <sheetName val="Obsolete provision"/>
-      <sheetName val="备品配件 低值易耗品清单"/>
-      <sheetName val="break down"/>
-      <sheetName val="openning balance "/>
-      <sheetName val="2005.4.30 inventory list"/>
-      <sheetName val="Obsolelte provision"/>
-      <sheetName val="provision reversal list"/>
-      <sheetName val="Detail list 0611"/>
-      <sheetName val="工时统计"/>
-      <sheetName val="06费用化明细"/>
-      <sheetName val="明细科目余额表"/>
-      <sheetName val="A3"/>
-      <sheetName val="外地"/>
-      <sheetName val="坯布"/>
-      <sheetName val="材料"/>
-      <sheetName val="外销"/>
-      <sheetName val="清单12.31"/>
-      <sheetName val="科目余额表"/>
-      <sheetName val="Title"/>
-      <sheetName val="인사현황(부서)"/>
-      <sheetName val="主营业务明细表"/>
-      <sheetName val="会计科目"/>
-      <sheetName val="Stock turnove_x005f_x005f_x005f"/>
-      <sheetName val="B-S"/>
-      <sheetName val="Income Statement"/>
-      <sheetName val="M3 - BS"/>
-      <sheetName val="M3 - PL"/>
-      <sheetName val="Erection"/>
-      <sheetName val="P12 TB SZ"/>
-      <sheetName val="Validation"/>
-      <sheetName val="审定表D3"/>
-      <sheetName val="明细分类账"/>
-      <sheetName val="报表层次重要性水平"/>
-      <sheetName val="所有者权益（股东权益）变动表(未审)"/>
-      <sheetName val="TB0212"/>
-      <sheetName val="个所税"/>
-      <sheetName val="企业所得税"/>
-      <sheetName val="4-2长投债券"/>
-      <sheetName val="3流资汇总"/>
-      <sheetName val="存货跌价准备Dy"/>
-      <sheetName val="基本生产成本"/>
-      <sheetName val="预提费用"/>
-      <sheetName val="长期应付款Dy"/>
-      <sheetName val="逾龄"/>
-      <sheetName val="役龄"/>
-      <sheetName val="福州路仓库(3)"/>
-      <sheetName val="物资采购-1"/>
-      <sheetName val="物资采购-2"/>
-      <sheetName val="祁连山路仓库(5)"/>
-      <sheetName val="特种储备物资"/>
-      <sheetName val="张江库"/>
-      <sheetName val="amended"/>
-      <sheetName val="原材料"/>
-      <sheetName val="SP"/>
-      <sheetName val="基本情况表"/>
-      <sheetName val="分产品销售收入、成本分析表"/>
-      <sheetName val="合并2"/>
-      <sheetName val="短期借款汇总表"/>
-      <sheetName val="长期借款汇总表"/>
-      <sheetName val="UFPrn20031203195053"/>
-      <sheetName val="SW-TEO"/>
-      <sheetName val="其他货币资金.dbf"/>
-      <sheetName val="银行存款.dbf"/>
-      <sheetName val="银行存款Dy"/>
-      <sheetName val="应收利息Dy"/>
-      <sheetName val="短期投资Dy"/>
-      <sheetName val="货币资金Dy"/>
-      <sheetName val="标本-资产"/>
-      <sheetName val="cs"/>
-      <sheetName val="Procedure"/>
-      <sheetName val="存货跌价准备清单"/>
-      <sheetName val="期末关联方库存"/>
-      <sheetName val=" Breakdown"/>
-      <sheetName val="warehouse"/>
-      <sheetName val="Provision mov't"/>
-      <sheetName val="05.10存货估价"/>
-      <sheetName val="Aging test"/>
-      <sheetName val="仓库分部"/>
-      <sheetName val="存货明细汇总"/>
-      <sheetName val="Inventory list"/>
-      <sheetName val="NRV &amp;Valuation Test"/>
-      <sheetName val="Qty test"/>
-      <sheetName val="Inventory provision"/>
-      <sheetName val="200912减值准备清单"/>
-      <sheetName val="2008年减值未销售"/>
-      <sheetName val="201006减值准备清单"/>
-      <sheetName val="存货分布"/>
-      <sheetName val="FG Adj"/>
-      <sheetName val="报表项目"/>
-      <sheetName val="A02"/>
-      <sheetName val="CJE"/>
-      <sheetName val="Intercompany balance"/>
-      <sheetName val="BS"/>
-      <sheetName val="吴江评估增值摊销"/>
-      <sheetName val="青岛泰信评估增值摊销"/>
-      <sheetName val="石油设备评估增值摊销"/>
-      <sheetName val="未实现毛利"/>
-      <sheetName val="Equity Movement"/>
-      <sheetName val="非经常性损益"/>
-      <sheetName val="MI"/>
-      <sheetName val="NFC TB"/>
-      <sheetName val="订单"/>
-      <sheetName val="A16C"/>
-      <sheetName val="Main"/>
-      <sheetName val="应付账款明细BS.09 "/>
-      <sheetName val="4-货币资金-现金"/>
-      <sheetName val="CF附注"/>
-      <sheetName val="试算平衡表"/>
-      <sheetName val="调整分录"/>
-      <sheetName val="数量金额总账"/>
-      <sheetName val="细节测试审计抽样"/>
-      <sheetName val="其他应付款科目余额2005.12.31"/>
-      <sheetName val="固定资产及累计折旧凭证抽查表"/>
-      <sheetName val="固定资产增加检查表"/>
-      <sheetName val="固定资产审定表"/>
-      <sheetName val="固定资产减少检查表"/>
-      <sheetName val="固定资产盘点检查情况表"/>
-      <sheetName val="审定表"/>
-      <sheetName val="折旧计算检查表"/>
-      <sheetName val="83套公房"/>
-      <sheetName val="损益"/>
-      <sheetName val="投资收益Dy"/>
-      <sheetName val="한계원가"/>
-      <sheetName val="Sheet4"/>
-      <sheetName val="Sheet6"/>
-      <sheetName val="Sheet5"/>
-      <sheetName val="Sheet3"/>
-      <sheetName val="折旧表2006年1-6月"/>
-      <sheetName val="Oct"/>
-      <sheetName val="base"/>
-      <sheetName val="存货月度明细"/>
-      <sheetName val="OS test"/>
-      <sheetName val="US test"/>
-      <sheetName val="调整汇总说明"/>
-      <sheetName val="SALES-ADJ"/>
-      <sheetName val="F.G Adj"/>
-      <sheetName val="存货汇总表"/>
-      <sheetName val="存货-自制半成品"/>
-      <sheetName val="存货-产成品"/>
-      <sheetName val="存货-原材料"/>
-      <sheetName val="存货-包装物"/>
-      <sheetName val="存货-低值易耗品"/>
-      <sheetName val="长期股权投资Dy"/>
-      <sheetName val="其他应收款Dy"/>
-      <sheetName val="商誉Dy"/>
-      <sheetName val="04收发存汇总表"/>
-      <sheetName val="其他应付款Dy"/>
-      <sheetName val="差异调整97"/>
-      <sheetName val="流资汇总"/>
-      <sheetName val="收入"/>
-      <sheetName val="说明"/>
-      <sheetName val="差异调整95"/>
-      <sheetName val="差异调整96"/>
-      <sheetName val="NFMSDLQJ"/>
-      <sheetName val="应收账款明细表"/>
-      <sheetName val="期初帐龄辅助表MT"/>
-      <sheetName val="坏账准备辅助表MT"/>
-      <sheetName val="UFPrn20021130165512"/>
-      <sheetName val="财务费用"/>
-      <sheetName val="管理费用"/>
-      <sheetName val="UFPrn20031114182129"/>
-      <sheetName val="2006年TB"/>
-      <sheetName val="27-7"/>
-      <sheetName val="UFPrn20200302102412"/>
-      <sheetName val="SysRefTables"/>
-      <sheetName val="数量对比"/>
-      <sheetName val="存货外购单价分析表-年度G2-3-1-1"/>
-      <sheetName val="存货总体分析表G2-3"/>
-      <sheetName val="二级明细"/>
-      <sheetName val="其他应收-导出"/>
-      <sheetName val="营业外支出"/>
-      <sheetName val="UFPrn20040104084034"/>
-      <sheetName val="BNWXVLNN"/>
-      <sheetName val="利润分析"/>
-      <sheetName val="资产负债分析"/>
-      <sheetName val="Economic evaluation - FY98 base"/>
-      <sheetName val="基础信息"/>
-      <sheetName val="隐藏页"/>
-      <sheetName val="loan database"/>
-      <sheetName val="货币资金审定表"/>
-      <sheetName val="Administration"/>
-      <sheetName val="08.8"/>
-      <sheetName val="库存商品库龄分析G2-3-3"/>
-      <sheetName val="发出计价汇总－库存商品"/>
-      <sheetName val="预计负债Dy"/>
-      <sheetName val="选择报表"/>
-      <sheetName val="2019年研发费用按项目汇总M8-6"/>
-      <sheetName val="param"/>
-      <sheetName val="Traduction"/>
-      <sheetName val="2550"/>
-      <sheetName val="2552"/>
-      <sheetName val="_2562"/>
-      <sheetName val="_2565"/>
-      <sheetName val="_8004"/>
-      <sheetName val="_8025"/>
-      <sheetName val="3331"/>
-      <sheetName val="3334"/>
-      <sheetName val="3388"/>
-      <sheetName val="3389"/>
-      <sheetName val="4213"/>
-      <sheetName val="5357"/>
-      <sheetName val="8066"/>
-      <sheetName val="下拉菜单"/>
-      <sheetName val="Adj. spreadsheet for June"/>
-      <sheetName val="TT04"/>
-      <sheetName val="Catalogo Roca 1Oct'01"/>
-      <sheetName val="附表"/>
-      <sheetName val="SENSITIVITY"/>
-      <sheetName val="Parameters"/>
-      <sheetName val="PIT"/>
-      <sheetName val="Movement"/>
-      <sheetName val="成品"/>
-      <sheetName val="短期投资股票投资.dbf"/>
-      <sheetName val="短期投资国债投资.dbf"/>
-      <sheetName val="股票投资收益.dbf"/>
-      <sheetName val="其他货币海通.dbf"/>
-      <sheetName val="其他货币零领路.dbf"/>
-      <sheetName val="投资收益债券.dbf"/>
-      <sheetName val="存货审定表G2"/>
-      <sheetName val="跌价准备测试表G2-2-4-1"/>
-      <sheetName val="参数表"/>
-      <sheetName val="原材料收发"/>
-      <sheetName val="A140-00"/>
-      <sheetName val="A141-20"/>
-      <sheetName val="A142-50"/>
-      <sheetName val="A141-60"/>
-      <sheetName val="CAS"/>
-      <sheetName val="A141-10"/>
-      <sheetName val="短期借款Dy"/>
-      <sheetName val="Input_Hide"/>
-      <sheetName val="FX"/>
-      <sheetName val="06"/>
-      <sheetName val="List"/>
-      <sheetName val="广州库"/>
-      <sheetName val="制费-分月"/>
-      <sheetName val="应付账款 (2)"/>
-      <sheetName val="Index"/>
-      <sheetName val="2008年1月"/>
-      <sheetName val="2007年12月  "/>
-      <sheetName val="2008年2月"/>
-      <sheetName val="1999TL"/>
-      <sheetName val="入库分类"/>
-      <sheetName val="外销涤布"/>
-      <sheetName val="原TB表"/>
-      <sheetName val="主菜单"/>
-      <sheetName val="其他应收款分录表"/>
-      <sheetName val="MasterList"/>
-      <sheetName val="信息"/>
-      <sheetName val="Part_Datum"/>
-      <sheetName val="FU-OTHER"/>
-      <sheetName val="管理费用Dy"/>
-      <sheetName val="财务费用mx"/>
-      <sheetName val="其他应收款Mx"/>
-      <sheetName val="其他应付款Mx"/>
-      <sheetName val="营业外支出Mx"/>
-      <sheetName val="披露表(上市)"/>
-      <sheetName val="程序表原始数据"/>
-      <sheetName val="其他应交款mx"/>
-      <sheetName val="应交税金mx1"/>
-      <sheetName val="应收票据Mx"/>
-      <sheetName val="预收账款Mx"/>
-      <sheetName val="生产成本mx"/>
-      <sheetName val="明细汇总表（见附件）G2-2"/>
-      <sheetName val="生产成本分配G2-8-6"/>
-      <sheetName val="科目名称"/>
-      <sheetName val="蓝谷全层级"/>
-      <sheetName val="Confirmation"/>
-      <sheetName val="statement 1998"/>
-      <sheetName val="c_data"/>
-      <sheetName val="co_code"/>
-      <sheetName val="Register"/>
-      <sheetName val="K31X"/>
-      <sheetName val="XVIa(i) - average price (2)"/>
-      <sheetName val="153541"/>
-      <sheetName val="PLAC"/>
-      <sheetName val="June 2004 13%&amp;17% details"/>
-      <sheetName val="June 2004 7% details"/>
-      <sheetName val="财务费用Dy"/>
-      <sheetName val="2002 DTT mgt ac"/>
-      <sheetName val="Actual (n)"/>
-      <sheetName val="2002-2004产销率"/>
-      <sheetName val="J300"/>
-      <sheetName val="HEADER"/>
-      <sheetName val="版权方2004年度频道分布汇总表"/>
-      <sheetName val="项目信息"/>
-      <sheetName val="Input"/>
-      <sheetName val="D3"/>
-      <sheetName val="Conversion to EUR"/>
-      <sheetName val="报表项目列表"/>
-      <sheetName val="jhcyl"/>
-      <sheetName val="FA-LISTING"/>
-      <sheetName val="Sample Design(季报不适用)"/>
-      <sheetName val="Provision"/>
-      <sheetName val="5-1.存货明细-原物料"/>
-      <sheetName val="5-1.存货明细-WIP"/>
-      <sheetName val="5-1.存货明细-FG"/>
-      <sheetName val="5-2.原物料報廢倉明細"/>
-      <sheetName val="原物料報廢倉明細"/>
-      <sheetName val="Sample size design"/>
-      <sheetName val="存货清单"/>
-      <sheetName val="IV1209"/>
-      <sheetName val="制成品-产品"/>
-      <sheetName val="在制品-产品"/>
-      <sheetName val="原料"/>
-      <sheetName val="物料"/>
-      <sheetName val="2010.12.31"/>
-      <sheetName val="WIP LCM"/>
-      <sheetName val="FG LCM"/>
-      <sheetName val="5-3.存货明细-WIP"/>
-      <sheetName val="5-4.存货明细-FG"/>
-      <sheetName val="原材料+物料存貨明細表"/>
-      <sheetName val="WIP存貨明細表"/>
-      <sheetName val="製成品存貨明細表"/>
-      <sheetName val="原料報廢倉明細"/>
-      <sheetName val="预付账款汇总表"/>
-      <sheetName val="Chart of Acct"/>
-      <sheetName val="This year-Budget-20092010"/>
-      <sheetName val="Basic information"/>
-      <sheetName val="9200"/>
-      <sheetName val="总公司2002.12.31"/>
-      <sheetName val="应付账款明细表"/>
-      <sheetName val="固定资产"/>
-      <sheetName val="I151-10"/>
-      <sheetName val="Lease adjustment"/>
-      <sheetName val="17应付票据明细表"/>
-      <sheetName val="10-12"/>
-      <sheetName val="ws9"/>
-      <sheetName val="Rate"/>
-      <sheetName val="附表6"/>
-      <sheetName val="A.R 01"/>
-      <sheetName val="公司代码"/>
-      <sheetName val="UFPrn20190109164420"/>
-      <sheetName val="销售6.13"/>
-      <sheetName val="K420"/>
-      <sheetName val="Vendor"/>
-      <sheetName val="Consol FS"/>
-      <sheetName val="J&amp;Q"/>
-      <sheetName val="ARP"/>
-      <sheetName val="审定表P6"/>
-      <sheetName val="原材料发出计价测试-OK"/>
-      <sheetName val="Group1"/>
-      <sheetName val="差旅费"/>
-      <sheetName val="PPE"/>
-      <sheetName val="9月结存固定资产清单"/>
-      <sheetName val="填表说明"/>
-      <sheetName val="实收资本Dy"/>
-      <sheetName val="1_12月"/>
-      <sheetName val="11月"/>
-      <sheetName val="12月"/>
-      <sheetName val="56271-2"/>
-      <sheetName val="５８D"/>
-      <sheetName val="1_10月"/>
-      <sheetName val="UFPrn20071013211250"/>
-      <sheetName val="物资采购含税转出"/>
-      <sheetName val="1-11基础信息"/>
-      <sheetName val="3-03-01固资折旧"/>
-      <sheetName val="TB表"/>
-      <sheetName val="明细表K7-2"/>
-      <sheetName val="UFPrn20030305081341"/>
-      <sheetName val="税费动力"/>
-      <sheetName val="报表20130630信威永胜"/>
-      <sheetName val="A6"/>
-      <sheetName val="pos. descr."/>
-      <sheetName val="广告费和业务宣传费表"/>
-      <sheetName val="资产减值准备表"/>
-      <sheetName val="工资薪金表"/>
-      <sheetName val="投资收益表"/>
-      <sheetName val="附件(excel）"/>
-      <sheetName val="业务招待费表"/>
-      <sheetName val="成本日报(4-10)"/>
-      <sheetName val="Canada"/>
-      <sheetName val="填写参数"/>
-      <sheetName val="存货审核表"/>
-      <sheetName val="资产减值损失"/>
-      <sheetName val="01 Bid Price summary"/>
-      <sheetName val="GiaVL"/>
-      <sheetName val="Thuc thanh"/>
-      <sheetName val="DTCT"/>
-      <sheetName val="基本参数"/>
-      <sheetName val="Liabrary"/>
-      <sheetName val="靶材分配比例"/>
-      <sheetName val="Set-up"/>
-      <sheetName val="E15-AFL"/>
-      <sheetName val="基本信息"/>
-      <sheetName val="BalanceSheet"/>
-      <sheetName val="TB-2018"/>
-      <sheetName val="GL-2018"/>
-      <sheetName val="PPD Schedule"/>
-      <sheetName val="目录"/>
-      <sheetName val="ITEM"/>
-      <sheetName val="SAR"/>
-      <sheetName val="报表科目明细"/>
-      <sheetName val="专项应付款Mx"/>
-      <sheetName val="DONVIBAN"/>
-      <sheetName val="NGUON"/>
-      <sheetName val="设定"/>
-      <sheetName val="01成品"/>
-      <sheetName val="应付"/>
-      <sheetName val="UFPrn20120201171347"/>
-      <sheetName val="UFPrn20120201171700"/>
-      <sheetName val="公司清单"/>
-      <sheetName val="公司名单"/>
-      <sheetName val="合并范围清单"/>
-      <sheetName val="管理费用表分析-1"/>
-      <sheetName val="利息支出分类表"/>
-      <sheetName val="0605"/>
-      <sheetName val="未安排订单（集团）"/>
-      <sheetName val="2.1.CM6150(导入)"/>
-      <sheetName val="Financ. Overview"/>
-      <sheetName val="Category"/>
-      <sheetName val="Variables"/>
-      <sheetName val="安盛其他应收款-坏账"/>
-      <sheetName val="1月固定资产清单"/>
-      <sheetName val="期后回款情况 D2-4"/>
-      <sheetName val="审计说明"/>
-      <sheetName val="分项目明细 D2-M"/>
-      <sheetName val="分客户预收明细表 D3-2"/>
-      <sheetName val="#511BkRec"/>
-      <sheetName val="#511-DEC97"/>
-      <sheetName val="主要规划指标"/>
-      <sheetName val="凭证核对内容"/>
-      <sheetName val="Stock turnove_x005f"/>
-      <sheetName val="12-坏账计提表"/>
-      <sheetName val="Stock_turnove_x005f_x005f_x005f_x005f_x00_2"/>
-      <sheetName val="公允价值变动损益Dy"/>
-      <sheetName val="工程物资Dy"/>
-      <sheetName val="Non-Statistical Sampling Master"/>
-      <sheetName val="期后回款测试"/>
-      <sheetName val="选择选项"/>
-      <sheetName val="99.12"/>
-      <sheetName val="evaluate资金回收"/>
-      <sheetName val="库存商品"/>
-      <sheetName val="1(分品种)"/>
-      <sheetName val="xbase"/>
-      <sheetName val="现金流量表"/>
-      <sheetName val="收入明细表"/>
-      <sheetName val="A430"/>
-      <sheetName val="2013调整分录"/>
-      <sheetName val="2012调整分录"/>
-      <sheetName val="项目索引"/>
-      <sheetName val="2009调整分录"/>
-      <sheetName val="Menu"/>
-      <sheetName val="3-11待摊"/>
-      <sheetName val="6-1土地"/>
-      <sheetName val="TB98"/>
-      <sheetName val="应收账款Mx"/>
-      <sheetName val="conWP"/>
-      <sheetName val="p.5, bank int income"/>
-      <sheetName val="税审调整分录汇总表"/>
-      <sheetName val="利息测算表"/>
-      <sheetName val="视同销售收入"/>
-      <sheetName val="审计调整分录汇总表"/>
-      <sheetName val="调整类型"/>
-      <sheetName val="税审调整底稿"/>
-      <sheetName val="营业收入"/>
-      <sheetName val="报表格式"/>
-      <sheetName val="视同销售成本"/>
-      <sheetName val="营业成本"/>
-      <sheetName val="YA-1-1"/>
-      <sheetName val="关键控制测试表"/>
-      <sheetName val="所有者权益(股东权益)变动表(未审)"/>
-      <sheetName val="役"/>
-      <sheetName val="3.现金流量表"/>
-      <sheetName val="暂估"/>
-      <sheetName val="06 六类公摊"/>
-      <sheetName val="财务成本"/>
-      <sheetName val="核算现金流量表"/>
-      <sheetName val="生产成本账"/>
-      <sheetName val="销售预测表"/>
-      <sheetName val="信息说明"/>
-      <sheetName val="2004电器设备"/>
-      <sheetName val="2004电子设备"/>
-      <sheetName val="2004房屋建筑物"/>
-      <sheetName val="2004家具"/>
-      <sheetName val="2004通用设备"/>
-      <sheetName val="2004土地"/>
-      <sheetName val="2004仪器仪表"/>
-      <sheetName val="2004运输设备"/>
-      <sheetName val="2004专用设备"/>
-      <sheetName val="一区"/>
-      <sheetName val="二区"/>
-      <sheetName val="三区"/>
-      <sheetName val="四区"/>
-      <sheetName val="五区"/>
-      <sheetName val="六区"/>
-      <sheetName val="七区"/>
-      <sheetName val="幼儿园小学"/>
-      <sheetName val="进度"/>
-      <sheetName val="项目规划指标"/>
-      <sheetName val="现金流一区"/>
-      <sheetName val="现金流(二区)"/>
-      <sheetName val="现金流(三区)"/>
-      <sheetName val="现金流(四区)"/>
-      <sheetName val="现金流(五区)"/>
-      <sheetName val="现金流(六区)"/>
-      <sheetName val="现金流(七区)"/>
-      <sheetName val="现金流(幼儿园小学)"/>
-      <sheetName val="使用说明"/>
-      <sheetName val="累计销售"/>
-      <sheetName val="销售出库序时簿"/>
-      <sheetName val="预收明细表"/>
-      <sheetName val="预付明细"/>
-      <sheetName val="分期收款发出12月"/>
-      <sheetName val="应收市内"/>
-      <sheetName val="应收外埠"/>
-      <sheetName val="T  B"/>
-      <sheetName val="损益推导"/>
-      <sheetName val="项目利润表(PS)"/>
-      <sheetName val="应付账款审定表"/>
-      <sheetName val="master"/>
-      <sheetName val="tot"/>
-      <sheetName val=" "/>
-      <sheetName val="Mp-team 1"/>
-      <sheetName val="银行借款询证"/>
-      <sheetName val="维简及井巷"/>
-      <sheetName val="产销存"/>
-      <sheetName val="1-6累计销售"/>
-      <sheetName val="收入个月"/>
-      <sheetName val="12进销存"/>
-      <sheetName val="_x0000__x0000__x0000__x0000__x0000__x0000__x0000__x0000_"/>
-      <sheetName val="名称（勿删）"/>
-      <sheetName val="3480總表"/>
-      <sheetName val="现金"/>
-      <sheetName val="列表"/>
-      <sheetName val="工资表"/>
-      <sheetName val="年终奖合并"/>
-      <sheetName val="个人所得税表"/>
-      <sheetName val="薪酬标准"/>
-      <sheetName val="人员信息表"/>
-      <sheetName val="员工银行账号明细表"/>
-      <sheetName val="内部公司清单"/>
-      <sheetName val="ARP-U501"/>
-      <sheetName val="g101"/>
-      <sheetName val="E101"/>
-      <sheetName val="ARP-U201"/>
-      <sheetName val="K204"/>
-      <sheetName val="机器设备"/>
-      <sheetName val="低保五保电费支出"/>
-      <sheetName val="Stock_turnove_x005f_x005f_x00_2"/>
-      <sheetName val="13-坏账计提表"/>
-      <sheetName val="上报资产负债表"/>
-      <sheetName val="上报损益表"/>
-      <sheetName val="现金流量表（月报）"/>
-      <sheetName val="补充表"/>
-      <sheetName val="Word附注"/>
-      <sheetName val="Lifetable 80 percent Mortality"/>
-      <sheetName val="FSM"/>
-      <sheetName val="表1.5"/>
-      <sheetName val="xj"/>
-      <sheetName val="1.公司概况"/>
-      <sheetName val="production cost"/>
-      <sheetName val="General Data"/>
-      <sheetName val="Sch PR-2"/>
-      <sheetName val="Sch PR-3"/>
-      <sheetName val="科目索引"/>
-      <sheetName val="GT_Custom"/>
-      <sheetName val="UFPrn20070303114642"/>
-      <sheetName val="合并试算表"/>
-      <sheetName val="2005"/>
-      <sheetName val="可供出售金融资产Dy"/>
-      <sheetName val="清单1"/>
-      <sheetName val="主表"/>
-      <sheetName val="附表三"/>
-      <sheetName val="改造后数据表"/>
-      <sheetName val="华房01"/>
-      <sheetName val="健翔01"/>
-      <sheetName val="京通01"/>
-      <sheetName val="应付利息Dy"/>
-      <sheetName val="VV"/>
-      <sheetName val="YH1"/>
-      <sheetName val="#511-SEPT97"/>
-      <sheetName val="#511-OCT97"/>
-      <sheetName val="#511-NOV97"/>
-      <sheetName val="现调整"/>
-      <sheetName val="附表2关联交易"/>
-      <sheetName val="重要性水平"/>
-      <sheetName val="关联方清单"/>
-      <sheetName val="J411"/>
-      <sheetName val="J412"/>
-      <sheetName val="FY02"/>
-      <sheetName val="Notes"/>
-      <sheetName val="Inventory list "/>
-      <sheetName val="存货材料成本差异"/>
-      <sheetName val="北京"/>
-      <sheetName val="北京原材料明细表"/>
-      <sheetName val="深圳"/>
-      <sheetName val="广州"/>
-      <sheetName val="期末存货中关联方采购金额"/>
-      <sheetName val="科目代码"/>
-      <sheetName val="表二十九1（01）"/>
-      <sheetName val="明细表2016"/>
-      <sheetName val="会计科目表"/>
-      <sheetName val="银行存款核对表"/>
-      <sheetName val="Top22(GER)"/>
-      <sheetName val="Rental PIT"/>
-      <sheetName val="Sample test"/>
-      <sheetName val="Business tax PIT"/>
-      <sheetName val="Professional fee"/>
-      <sheetName val="十一、消耗性生物资产G2-2-11"/>
-      <sheetName val="管理费用明细表(2001年)"/>
-      <sheetName val="出库"/>
-      <sheetName val="入库"/>
-      <sheetName val="TB资产"/>
-      <sheetName val="其他应收款-2019.12.31"/>
-      <sheetName val="其他应付款"/>
-      <sheetName val="选项清单列表（不归档）"/>
-      <sheetName val="UFPrn20050930091710"/>
-      <sheetName val="UFPrn20050930204109"/>
-      <sheetName val="关联方"/>
-      <sheetName val="2021.10"/>
-      <sheetName val="B1-1001"/>
-      <sheetName val="明细表（账龄）M1-2"/>
-      <sheetName val="明细表M9-2"/>
-      <sheetName val="AFEMAI"/>
-      <sheetName val="Detail Loan Move. &amp; Listing"/>
-      <sheetName val="CAUDIT"/>
-      <sheetName val="风险分类"/>
-      <sheetName val="O101"/>
-      <sheetName val="J8-9使用权资产负债确认汇总表2020年1月1日的租赁合同）"/>
-      <sheetName val="KEY"/>
-      <sheetName val="起"/>
-      <sheetName val="末"/>
-      <sheetName val="补贴收入明细表"/>
-      <sheetName val="以前年度损益调整Dy"/>
-      <sheetName val="dongia (2)"/>
-      <sheetName val="销售收入"/>
-      <sheetName val="代码"/>
-      <sheetName val="06汇总"/>
-      <sheetName val="主数据(车型)"/>
-      <sheetName val="2月修改"/>
-      <sheetName val="项目成本明细表"/>
-      <sheetName val="收入毛利分析D4-3-1-分析"/>
-      <sheetName val="D4-12-1销售退回核查-分析"/>
-      <sheetName val="自定义名称"/>
-      <sheetName val="Stock_turnove_x00_2"/>
-      <sheetName val="抵销科目"/>
-      <sheetName val="增值税测算表O1-4 -2019年"/>
-      <sheetName val="科目设置"/>
-      <sheetName val="产品名称.勿删"/>
-      <sheetName val="Collateral"/>
-      <sheetName val="Disposition"/>
-      <sheetName val="BAS"/>
-      <sheetName val="BUDGET"/>
-      <sheetName val="Input-Act"/>
-      <sheetName val="A股IPO审计程序汇总"/>
-      <sheetName val="General"/>
-      <sheetName val="待售物业"/>
-      <sheetName val="发展中物业"/>
-      <sheetName val="发展中物业明细"/>
-      <sheetName val="其他存货"/>
-      <sheetName val="Valuation of PFS"/>
-      <sheetName val="Valuation of PUD"/>
-      <sheetName val="Detail test"/>
-      <sheetName val="Cut-off"/>
-      <sheetName val="Detailed test"/>
-      <sheetName val="PUD Breakdown"/>
-      <sheetName val="Adjustment on 一期成本"/>
-      <sheetName val="Initialize"/>
-      <sheetName val="提足折旧"/>
-      <sheetName val="G1-3b月度销售分析"/>
-      <sheetName val="Setting"/>
-      <sheetName val="BlsFinAss"/>
-      <sheetName val="BlsFinTdp"/>
-      <sheetName val="BlsGdw"/>
-      <sheetName val="BlsOia"/>
-      <sheetName val="BlsDch"/>
-      <sheetName val="BlsOla"/>
-      <sheetName val="BlsPrvPrp"/>
-      <sheetName val="BlsPrvSre"/>
-      <sheetName val="BlsPrvLit"/>
-      <sheetName val="BlsPrvPrs"/>
-      <sheetName val="BlsPrvSpb"/>
-      <sheetName val="BlsPrvLst"/>
-      <sheetName val="BlsPrvCbc"/>
-      <sheetName val="BlsPrvOpv"/>
-      <sheetName val="SysNavigation"/>
-      <sheetName val="SysCompanyCodes"/>
-      <sheetName val="SysOpcoCompanyCodes"/>
-      <sheetName val="CafOpa"/>
-      <sheetName val="O5 Lead-其他应付-Consol"/>
-      <sheetName val="G2 Lead"/>
-      <sheetName val="O5-4  Lead"/>
-      <sheetName val="Bloomberg"/>
-      <sheetName val="Summary (Wuhan)"/>
-      <sheetName val="其他应收款明细表"/>
-      <sheetName val="0_Menu"/>
-      <sheetName val="Version"/>
-      <sheetName val="Rates"/>
-      <sheetName val="Summary_retrieve"/>
-      <sheetName val="Malasia"/>
-      <sheetName val="存货差异分析表"/>
-      <sheetName val="B-3"/>
-      <sheetName val="B-4"/>
-      <sheetName val="表2&lt;销售出库单&gt;"/>
-      <sheetName val="A300"/>
-      <sheetName val="6月末SP库存"/>
-      <sheetName val="Customize Your Loan Manager"/>
-      <sheetName val="CE"/>
-      <sheetName val="IS"/>
-      <sheetName val="内销收人"/>
-      <sheetName val="折旧测算表"/>
-      <sheetName val="Final"/>
-      <sheetName val="dm"/>
-      <sheetName val="JA#1"/>
-      <sheetName val="JA#2&amp;5"/>
-      <sheetName val="清冊"/>
-      <sheetName val="12月开票明细"/>
-      <sheetName val="Income tax reconciliation"/>
-      <sheetName val="账户汇总表_2017年1月至12月_"/>
-      <sheetName val="2013.10-2014.9原材料外购入库序时簿"/>
-      <sheetName val="未实现毛利及收入成本抵消"/>
-      <sheetName val="Dis."/>
-      <sheetName val="合并TB-19年"/>
-      <sheetName val="采购订单3名"/>
-      <sheetName val="校验"/>
-      <sheetName val="原报表"/>
-      <sheetName val="上年审前调整"/>
-      <sheetName val="上年审前试算表"/>
-      <sheetName val="本年审前调整"/>
-      <sheetName val="本年审前试算表"/>
-      <sheetName val="审前报表"/>
-      <sheetName val="初始设定"/>
-      <sheetName val="profit2 (2)"/>
-      <sheetName val="351B发出商品明细-不打印"/>
-      <sheetName val="351A发出商品测试"/>
-      <sheetName val="3402存货导引表"/>
-      <sheetName val="3月生产成本凭证"/>
-      <sheetName val="能耗计算 OK "/>
-      <sheetName val="2019收入成本（未审）"/>
-      <sheetName val="2019年6月-2020年5月项目收入成本一览"/>
-      <sheetName val="院级设计"/>
-      <sheetName val="银行存款明细表"/>
-      <sheetName val="人员支出"/>
-      <sheetName val="农业用地"/>
-      <sheetName val="2002年一般预算收入"/>
-      <sheetName val="截止测试-入库G2-7-1"/>
-      <sheetName val="TB-公证天业"/>
-      <sheetName val="BKD-氢能"/>
-      <sheetName val="2045020001"/>
-      <sheetName val="schedule"/>
-      <sheetName val="2008 SPL"/>
-      <sheetName val="TargetReports"/>
-      <sheetName val="KIINAS"/>
-      <sheetName val="BW_FAELI"/>
-      <sheetName val="（27）实收资本"/>
-      <sheetName val="USD Data input"/>
-      <sheetName val="附表2"/>
-      <sheetName val="在制"/>
-      <sheetName val="科目代码表"/>
-      <sheetName val="BW系统 原稿"/>
-      <sheetName val="UFPrn20200514122159"/>
-      <sheetName val="accode"/>
-      <sheetName val="NBCF"/>
-      <sheetName val="2019年6月其他应付款明细表M4-2  "/>
-      <sheetName val="关联方应收款"/>
-      <sheetName val="长期借款 (2)"/>
-      <sheetName val="短期借款"/>
-      <sheetName val="存货Dy"/>
-      <sheetName val="收入和成本对应表"/>
-      <sheetName val="调整分录 "/>
-      <sheetName val="营业费用截止"/>
-      <sheetName val="2017_6_30记6号"/>
-      <sheetName val="1_主营业务收入"/>
-      <sheetName val="工程汇总表 2020新收入准则"/>
-      <sheetName val="799"/>
-      <sheetName val="A3 &amp; U 09-01"/>
-      <sheetName val="6.6-存货-制造费用明细表"/>
-      <sheetName val="核算项目组合表"/>
-      <sheetName val="全部预算"/>
-      <sheetName val="公司名称一览表"/>
-      <sheetName val="UFPrn20210115161842"/>
-      <sheetName val="单位往来"/>
-      <sheetName val="投资保证金"/>
-      <sheetName val="2019—库存商品库龄"/>
-      <sheetName val="A180-10"/>
-      <sheetName val="填制说明"/>
-      <sheetName val="科目2015"/>
-      <sheetName val="2018"/>
-      <sheetName val="2018年报表"/>
-      <sheetName val="预期信用损失的计量测试D2-14（20201231）"/>
-      <sheetName val="应交税费审定表"/>
-      <sheetName val="合并"/>
-      <sheetName val="审计程序D29"/>
-      <sheetName val="合并起点"/>
-      <sheetName val="母公司汇总"/>
-      <sheetName val="九、开发成本G2-2-9"/>
-      <sheetName val="八、开发产品G2-2-8"/>
-      <sheetName val="一、原材料明细表G2-2-1"/>
-      <sheetName val="二、材料采购、在途物资明细表G2-2-2"/>
-      <sheetName val="三、周转材料、低值易耗品，包装物明细表G2-2-3"/>
-      <sheetName val="四、自制半成品明细表G2-2-4"/>
-      <sheetName val="六、库存商品明细表G2-2-6"/>
-      <sheetName val="七、发出商品G2-2-7"/>
-      <sheetName val="画底稿使用"/>
-      <sheetName val="调整后报表"/>
-      <sheetName val="D4-3-2"/>
-      <sheetName val="AP"/>
-      <sheetName val="NPBOC"/>
-      <sheetName val="NPIC"/>
-      <sheetName val="会企01表"/>
-      <sheetName val="会企02表"/>
-      <sheetName val="G2-5生产成本审定表"/>
-      <sheetName val="款项性质明细"/>
-      <sheetName val="审计调整汇总G1-0-1"/>
-      <sheetName val="房租物业余额G1-3"/>
-      <sheetName val="HL"/>
-      <sheetName val="Provision list"/>
-      <sheetName val="原材料&amp;存货跌价 list"/>
-      <sheetName val="生产成本list"/>
-      <sheetName val="2009.12.31日完工比例"/>
-      <sheetName val="2011.12.31完工比例"/>
-      <sheetName val="2010.06.30完工比例"/>
-      <sheetName val="库存明细2011"/>
-      <sheetName val="在途"/>
-      <sheetName val="固定资产2001年折旧"/>
-      <sheetName val="所得税凭证抽查"/>
-      <sheetName val="W3"/>
-      <sheetName val="数字视频并帐"/>
-      <sheetName val="P1"/>
-      <sheetName val="Listen"/>
-      <sheetName val="(6413)销售费用"/>
-      <sheetName val="管理"/>
-      <sheetName val="主营成本"/>
-      <sheetName val="其他应付款 "/>
-      <sheetName val="UFPrn20050217103510"/>
-      <sheetName val="应付账款"/>
-      <sheetName val="6113应收账款"/>
-      <sheetName val="Start"/>
-      <sheetName val="cov"/>
-      <sheetName val="046 Fixed Ass. mov."/>
-      <sheetName val="Open"/>
-      <sheetName val="获签学生登记表-直客"/>
-      <sheetName val="TPM"/>
-      <sheetName val="UFPrn20010510092817"/>
-      <sheetName val="UFPrn20010510092918"/>
-      <sheetName val="F01-A (2)"/>
-      <sheetName val="固定资产、累计折旧、减值准备明细表"/>
-      <sheetName val="现金流量1-10月"/>
-      <sheetName val="2011调整分录"/>
-      <sheetName val="10月"/>
-      <sheetName val="2月"/>
-      <sheetName val="3月"/>
-      <sheetName val="4月"/>
-      <sheetName val="7月"/>
-      <sheetName val="8月"/>
-      <sheetName val="9月"/>
-      <sheetName val="敏感参数"/>
-      <sheetName val="1 项目情况"/>
-      <sheetName val="1 项目利润表(PS)"/>
-      <sheetName val="3 损益推导"/>
-      <sheetName val="鼎信诺字典表"/>
-      <sheetName val="现金流量表(未审)"/>
-      <sheetName val="偿债力分析"/>
-      <sheetName val="应收帐款询证函"/>
-      <sheetName val="Stock_turnove_x005f_x005f_x005f_x005f_x005f"/>
-      <sheetName val="订"/>
-      <sheetName val="l&gt;y"/>
-      <sheetName val="inventories aging"/>
-      <sheetName val="原材料 (y.e.)"/>
-      <sheetName val="不合格原材料 (y.e.)"/>
-      <sheetName val="产成品 (y.e.)"/>
-      <sheetName val="Aging"/>
-      <sheetName val="产成品"/>
-      <sheetName val="不合格原材料"/>
-      <sheetName val="委外加工"/>
-      <sheetName val="Aging Summary（2005.6）"/>
-      <sheetName val="Aging-材料"/>
-      <sheetName val="Aging-产品"/>
-      <sheetName val="Aging-特别"/>
-      <sheetName val="Summary 06.9"/>
-      <sheetName val="Inventory Breakdown"/>
-      <sheetName val="Tickmark"/>
-      <sheetName val="2006TB"/>
-      <sheetName val="银行列表"/>
-      <sheetName val="报表11"/>
-      <sheetName val="母公司TB"/>
-      <sheetName val="Chart of Account"/>
-      <sheetName val="清单"/>
-      <sheetName val="关联方_物流集团"/>
-      <sheetName val="存货_生产成本Dy"/>
-      <sheetName val="主营业务成本mx"/>
-      <sheetName val="注释补充表1"/>
-      <sheetName val="1－5月余额表"/>
-      <sheetName val="1－10月余额表"/>
-      <sheetName val="数量金额明细账"/>
-      <sheetName val="B7-2-1应付账款余额表"/>
-      <sheetName val="Jumei"/>
-      <sheetName val="SW"/>
-      <sheetName val="JDMCode"/>
-      <sheetName val="PanelInfo"/>
-      <sheetName val="2.1 PS估值分析-上市公司"/>
-      <sheetName val="3111"/>
-      <sheetName val="3113"/>
-      <sheetName val="_8013"/>
-      <sheetName val="序时帐"/>
-      <sheetName val="Common Assumptions"/>
-      <sheetName val="4528"/>
-      <sheetName val="设备部房屋"/>
-      <sheetName val="表六 "/>
-      <sheetName val="披露表（上市）"/>
-      <sheetName val="有效性"/>
-      <sheetName val="Bid_Details"/>
-      <sheetName val="产能统计（2014）"/>
-      <sheetName val="审定_资产负债表"/>
-      <sheetName val="未审_资产负债表"/>
-      <sheetName val="C1"/>
-      <sheetName val="China"/>
-      <sheetName val="inventories list by amount"/>
-      <sheetName val="Sheet841"/>
-      <sheetName val="BKD-库存材料"/>
-      <sheetName val="BKD-周转材料"/>
-      <sheetName val="存货周转率测试"/>
-      <sheetName val="周转材料摊销"/>
-      <sheetName val="Purchase Test"/>
-      <sheetName val="定义"/>
-      <sheetName val="枚举字典"/>
-      <sheetName val="营业费用02"/>
-      <sheetName val="mvt"/>
-      <sheetName val="支出项目对应现金流项目"/>
-      <sheetName val="UFPrn2003其他"/>
-      <sheetName val="sales"/>
-      <sheetName val="数据源"/>
-      <sheetName val="审计工作底稿目录"/>
-      <sheetName val="面料"/>
-      <sheetName val="辅料"/>
-      <sheetName val="燃料"/>
-      <sheetName val="预收帐款"/>
-      <sheetName val="福利费1"/>
-      <sheetName val="毛利分析图"/>
-      <sheetName val="_"/>
-      <sheetName val="控制测试样本量"/>
-      <sheetName val="01"/>
-      <sheetName val="010"/>
-      <sheetName val="011"/>
-      <sheetName val="012"/>
-      <sheetName val="02"/>
-      <sheetName val="05"/>
-      <sheetName val="07"/>
-      <sheetName val="08"/>
-      <sheetName val="09"/>
-      <sheetName val="37.租赁明细"/>
-      <sheetName val="正式"/>
-      <sheetName val="D2-7本期应收结算单查验"/>
-      <sheetName val="预算假设-项目状态"/>
-      <sheetName val="23"/>
-      <sheetName val="研发项目"/>
-      <sheetName val="资金计划项目说明"/>
-      <sheetName val="database"/>
-      <sheetName val="원단위"/>
-      <sheetName val="往来"/>
-      <sheetName val="类型设置"/>
-      <sheetName val="分析报告 "/>
-      <sheetName val="Master Data"/>
-      <sheetName val="detail"/>
-      <sheetName val="汇总"/>
-      <sheetName val="税后工资测算"/>
-      <sheetName val="UFPrn20050405152516"/>
-      <sheetName val="Net Sales (Monthly) Projection"/>
-      <sheetName val="销售明细-2021"/>
-      <sheetName val="存货收发存-2021"/>
-      <sheetName val="明细表D4-20"/>
-      <sheetName val="应收-全"/>
-      <sheetName val="二月"/>
-      <sheetName val="其他业务利润"/>
-      <sheetName val="其他材料收入重复"/>
-      <sheetName val="其他材料收入账"/>
-      <sheetName val="预收"/>
-      <sheetName val="销售费用"/>
-      <sheetName val="资产"/>
-      <sheetName val="租赁计算表19"/>
-      <sheetName val="租赁计算表30"/>
-      <sheetName val="租赁计算表37"/>
-      <sheetName val="租赁计算表26"/>
-      <sheetName val="租赁计算表42"/>
-      <sheetName val="租赁计算表49"/>
-      <sheetName val="租赁计算表48"/>
-      <sheetName val="租赁计算表47"/>
-      <sheetName val="租赁计算表59"/>
-      <sheetName val="租赁计算表73"/>
-      <sheetName val="租赁计算表76"/>
-      <sheetName val="租赁计算表107"/>
-      <sheetName val="租赁计算表111"/>
-      <sheetName val="租赁计算表120"/>
-      <sheetName val="租赁计算表89"/>
-      <sheetName val="租赁计算表52"/>
-      <sheetName val="租赁计算表69"/>
-      <sheetName val="租赁计算表86"/>
-      <sheetName val="租赁计算表127"/>
-      <sheetName val="租赁计算表132"/>
-      <sheetName val="明细汇总表"/>
-      <sheetName val="租赁计算表133"/>
-      <sheetName val="租赁计算表134"/>
-      <sheetName val="租赁计算表135"/>
-      <sheetName val="租赁计算表137"/>
-      <sheetName val="租赁计算表138"/>
-      <sheetName val="租赁计算表100"/>
-      <sheetName val="租赁计算表16"/>
-      <sheetName val="担保"/>
-      <sheetName val="CRITERIA1"/>
-      <sheetName val="CRITERIA2"/>
-      <sheetName val="1461（12.6）"/>
-      <sheetName val="销售毛利润汇总表"/>
-      <sheetName val="A子公司"/>
-      <sheetName val="98调整分录表"/>
-      <sheetName val="FA-06-不看"/>
-      <sheetName val="FA-05-不看"/>
-      <sheetName val="mapping"/>
-      <sheetName val="产品销售毛利表"/>
-      <sheetName val="资产负债表-母"/>
-      <sheetName val="01 Balance Sheet资产负债表"/>
-      <sheetName val="PY-pp"/>
-      <sheetName val="Sheet761"/>
-      <sheetName val="A41-2折旧测试"/>
-      <sheetName val="TB试算表_本年"/>
-      <sheetName val="RYRPADTN"/>
-      <sheetName val="面积指标"/>
-      <sheetName val="P-7 CF Fed"/>
-      <sheetName val="一级"/>
-      <sheetName val="2003本部资产负债试算表"/>
-      <sheetName val="2003本部利润及利润分配表试算表"/>
-      <sheetName val="tra-vat-lieu"/>
-      <sheetName val="威海汉邦"/>
-      <sheetName val="dtct cong"/>
-      <sheetName val="数据源-勿动"/>
-      <sheetName val="BPR"/>
-      <sheetName val="2015PPE"/>
-      <sheetName val="Sheet668"/>
-      <sheetName val="22"/>
-      <sheetName val="M 67"/>
-      <sheetName val="整理"/>
-      <sheetName val="RawData"/>
-      <sheetName val="F1"/>
-      <sheetName val="现金流分录汇总"/>
-      <sheetName val="F.T"/>
-      <sheetName val="CONSOL"/>
-      <sheetName val="待摊费用明细表"/>
-      <sheetName val="资产评估结果分类汇总表 (2)"/>
-      <sheetName val="调整汇总19"/>
-      <sheetName val="调整汇总16"/>
-      <sheetName val="调整汇总18"/>
-      <sheetName val="调整汇总17"/>
-      <sheetName val="母公司调整汇总17"/>
-      <sheetName val="项目名称"/>
-      <sheetName val="参考1-项目明细"/>
-      <sheetName val="期別全体表"/>
-      <sheetName val="2017年开发支出余额"/>
-      <sheetName val="分析表L1-3-1"/>
-      <sheetName val="2004年试算表"/>
-      <sheetName val="BKD天津瑞贝"/>
-      <sheetName val="BKD瑞奇北京"/>
-      <sheetName val="BKD上海华外"/>
-      <sheetName val="BKD瑞奇中国"/>
-      <sheetName val="DEP PIT-SH"/>
-      <sheetName val="DEP PIT -GZ"/>
-      <sheetName val="库存商品余额表.dbf"/>
-      <sheetName val="销售单价公允性"/>
-      <sheetName val="工作底稿扉页"/>
-      <sheetName val="Y3-1一般会计制度附注"/>
-      <sheetName val="PAF"/>
-      <sheetName val="營業成本表"/>
-      <sheetName val="94"/>
-      <sheetName val="Adm97"/>
-      <sheetName val="2005-5"/>
-      <sheetName val="TB2005"/>
-      <sheetName val="SCH 2 - Highlights_2"/>
-      <sheetName val="dentaltable"/>
-      <sheetName val="Products"/>
-      <sheetName val="Flow"/>
-      <sheetName val="G2 存货"/>
-      <sheetName val="G5 主营业务成本"/>
-      <sheetName val="TB2017"/>
-      <sheetName val="TB2018"/>
-      <sheetName val="GL2018"/>
-      <sheetName val="JE JX "/>
-      <sheetName val="JE SH"/>
-      <sheetName val="TB2021"/>
-      <sheetName val="JE2021"/>
-      <sheetName val="Excel版财务报表附注"/>
-      <sheetName val="Sheet481"/>
-      <sheetName val="20年出库"/>
-      <sheetName val="无形资产"/>
-      <sheetName val="利润表项目"/>
-      <sheetName val="INVDAYS"/>
-      <sheetName val="表三甲"/>
-      <sheetName val="11-1"/>
-      <sheetName val="数据汇总表"/>
-      <sheetName val="A2-1试算"/>
-      <sheetName val="Sheet929"/>
-      <sheetName val="管理费用(集团董事会)"/>
-      <sheetName val="收发存汇总表"/>
-      <sheetName val="折旧计算表"/>
-      <sheetName val="Currency"/>
-      <sheetName val="DropDown"/>
-      <sheetName val="Non-Statistical Sampling"/>
-      <sheetName val="基础条件"/>
-      <sheetName val="数据库表"/>
-      <sheetName val="销售明细账审计后"/>
-      <sheetName val="08现金流量底稿"/>
-      <sheetName val="09现金流量底稿"/>
-      <sheetName val="Major"/>
-      <sheetName val="阳光365人员情况表（截至2005.9.30）"/>
-      <sheetName val="TAX COM"/>
-      <sheetName val="其它业务收入分类"/>
-      <sheetName val="B15 重要性计算表"/>
-      <sheetName val="集团关联方清单"/>
-      <sheetName val="数据有效性"/>
-      <sheetName val="conBS"/>
-      <sheetName val="conCE"/>
-      <sheetName val="conCF"/>
-      <sheetName val="conIS"/>
-      <sheetName val="N__其他应收款"/>
-      <sheetName val="N__应收账款"/>
-      <sheetName val="N__营业收入及营业成本"/>
-      <sheetName val="源"/>
-      <sheetName val="Marco"/>
-      <sheetName val="应收账款明细分类账2019"/>
-      <sheetName val="20年销售出库"/>
-      <sheetName val="2-R1619"/>
-      <sheetName val="递延所得税资产Dy"/>
-      <sheetName val="FIN48 TP Doc"/>
-      <sheetName val="应付帐款余额表"/>
-      <sheetName val="或有事项"/>
-      <sheetName val="关联方交易"/>
-      <sheetName val="其他综合收益"/>
-      <sheetName val="审定表M4"/>
-      <sheetName val="Sheet751"/>
-      <sheetName val="银行未达账项明细表"/>
-      <sheetName val="资产负债表（新）"/>
-      <sheetName val="Sheet910"/>
-      <sheetName val="制造费用明细表"/>
-      <sheetName val="生产成本检查表"/>
-      <sheetName val="销售费用截止测试"/>
-      <sheetName val="附注披露信息（上市公司）L1-1"/>
-      <sheetName val="Sheet447"/>
-      <sheetName val="销项税"/>
-      <sheetName val="SCH H"/>
-      <sheetName val="Planning"/>
-      <sheetName val="Planning Extension"/>
-      <sheetName val="Audit Results Ext"/>
-      <sheetName val="Audit Results Upper Stratum Ext"/>
-      <sheetName val="Population Characteristics"/>
-      <sheetName val="Individually Significant Items"/>
-      <sheetName val="Projection Extended Sample"/>
-      <sheetName val="Projection"/>
-      <sheetName val="D2-1 应收账款Leadsheet"/>
-      <sheetName val="存货明细表"/>
-      <sheetName val="收入检查表（是否全部开票及船舶离港时间1-10）D4-3-1"/>
-      <sheetName val="No.305"/>
-      <sheetName val="No.404"/>
-      <sheetName val="Contents"/>
-      <sheetName val="市场比较法"/>
-      <sheetName val="基础资料"/>
-      <sheetName val="账项调整"/>
-      <sheetName val="索引表"/>
-      <sheetName val="申报表封面"/>
-      <sheetName val="全年折旧"/>
-      <sheetName val="固定资产清理"/>
-      <sheetName val="Basic_Information"/>
-      <sheetName val="FORM14_2"/>
-      <sheetName val="新城资金明细"/>
-      <sheetName val="申鑫大厦租金明细"/>
-      <sheetName val="三林明细"/>
-      <sheetName val="东陆明细"/>
-      <sheetName val="在建工程"/>
-      <sheetName val="函证结果汇总表M1-5"/>
-      <sheetName val="集团关联单位"/>
-      <sheetName val="个人备用金账龄"/>
-      <sheetName val="审定表M1 "/>
-      <sheetName val="预期信用损失的计量测试M1-7-1"/>
-      <sheetName val="发货单列表"/>
-      <sheetName val="Sheet829"/>
-      <sheetName val="Sheet703"/>
-      <sheetName val="披露表-国企报告"/>
-      <sheetName val="披露表-上市公司报告"/>
-      <sheetName val="Sheet748"/>
-      <sheetName val="投资"/>
-      <sheetName val="筹资"/>
-      <sheetName val="首页"/>
-      <sheetName val="绝对估值"/>
-      <sheetName val="销售输入表"/>
-      <sheetName val="C101"/>
-      <sheetName val="管理费用检查表"/>
-      <sheetName val="营业外收入检查情况表"/>
-      <sheetName val="营业费用检查表"/>
-      <sheetName val="A105010"/>
-      <sheetName val="nada"/>
-      <sheetName val="dropdowns"/>
-      <sheetName val="通用设备折旧复核"/>
-      <sheetName val="专用设备折旧复核"/>
-      <sheetName val="运输设备折旧复核"/>
-      <sheetName val="电子设备折旧复核"/>
-      <sheetName val="其他设备折旧"/>
-      <sheetName val="Sheet794"/>
-      <sheetName val="白玻综合成本"/>
-      <sheetName val="综合成本"/>
-      <sheetName val="LF"/>
-      <sheetName val="MB51"/>
-      <sheetName val="Nov,01"/>
-      <sheetName val="存货收发存汇总表"/>
-      <sheetName val="CE_P"/>
-      <sheetName val="ADJ Sum(console)"/>
-      <sheetName val="利润中心"/>
-      <sheetName val="折旧表"/>
-      <sheetName val="固定资产卡片"/>
-      <sheetName val="2009投资明细表"/>
-      <sheetName val="a"/>
-      <sheetName val="L1-1"/>
-      <sheetName val="97년"/>
-      <sheetName val="LADJ Recon "/>
-      <sheetName val="For report Disclosure"/>
-      <sheetName val="Turnover days analysis"/>
-      <sheetName val="5442(ref)"/>
-      <sheetName val="5443(ref)"/>
-      <sheetName val="For PACKAGE"/>
-      <sheetName val="本部"/>
-      <sheetName val="西安"/>
-      <sheetName val="重庆"/>
-      <sheetName val="成都"/>
-      <sheetName val="哈尔滨"/>
-      <sheetName val="大连"/>
-      <sheetName val="沈阳"/>
-      <sheetName val="秦皇岛"/>
-      <sheetName val="武汉"/>
-      <sheetName val="郑州"/>
-      <sheetName val="天津"/>
-      <sheetName val="烟台"/>
-      <sheetName val="青岛"/>
-      <sheetName val="济南"/>
-      <sheetName val="南昌"/>
-      <sheetName val="合肥"/>
-      <sheetName val="嘉兴"/>
-      <sheetName val="温州"/>
-      <sheetName val="台州"/>
-      <sheetName val="宁波"/>
-      <sheetName val="杭州"/>
-      <sheetName val="扬州"/>
-      <sheetName val="南通"/>
-      <sheetName val="常州"/>
-      <sheetName val="南京"/>
-      <sheetName val="张家港"/>
-      <sheetName val="江阴"/>
-      <sheetName val="无锡"/>
-      <sheetName val="昆山"/>
-      <sheetName val="苏州"/>
-      <sheetName val="嘉定"/>
-      <sheetName val="松江"/>
-      <sheetName val="长沙"/>
-      <sheetName val="福州"/>
-      <sheetName val="泉州"/>
-      <sheetName val="厦门"/>
-      <sheetName val="惠州"/>
-      <sheetName val="汕头"/>
-      <sheetName val="花都"/>
-      <sheetName val="番禺"/>
-      <sheetName val="莞城"/>
-      <sheetName val="塘厦"/>
-      <sheetName val="长安"/>
-      <sheetName val="佛山"/>
-      <sheetName val="顺德"/>
-      <sheetName val="中山"/>
-      <sheetName val="龙岗"/>
-      <sheetName val="漳州"/>
-      <sheetName val="浦东"/>
-      <sheetName val="绍兴"/>
-      <sheetName val="石家庄"/>
-      <sheetName val="存货--12.31"/>
-      <sheetName val="存货库龄分析"/>
-      <sheetName val="存货跌价2013.1.4"/>
-      <sheetName val="6月生产成本"/>
-      <sheetName val="3-1-1现金"/>
-      <sheetName val="股本Dy"/>
-      <sheetName val="应收出口退税mx"/>
-      <sheetName val="payroll "/>
-      <sheetName val="2003年预付账款明细账"/>
-      <sheetName val="其他业务利润Dy"/>
-      <sheetName val="营业费用Dy"/>
-      <sheetName val="应收票据Dy"/>
-      <sheetName val="LinkData"/>
-      <sheetName val="30.06.03"/>
-      <sheetName val="主营业务收入mx"/>
-      <sheetName val="余额表（终稿）"/>
-      <sheetName val="5-1-3管沟"/>
-      <sheetName val="5-3工程物资"/>
-      <sheetName val="5-4-2在建安装"/>
-      <sheetName val="5-5固定清理"/>
-      <sheetName val="5-6待处理固定损失"/>
-      <sheetName val="丁字帐户"/>
-      <sheetName val="KLHT"/>
-      <sheetName val="每月資料"/>
-      <sheetName val="无形资产Dy"/>
-      <sheetName val="无形资产减值准备Dy"/>
-      <sheetName val="应收补贴款Dy"/>
-      <sheetName val="其他流动资产Dy"/>
-      <sheetName val="内部往来Dy"/>
-      <sheetName val="长期待摊费用Dy"/>
-      <sheetName val="管理费用mx"/>
-      <sheetName val="存货Cx"/>
-      <sheetName val="按客户"/>
-      <sheetName val="FLdeleted"/>
-      <sheetName val="存货_库存商品Dy"/>
-      <sheetName val="应付工资Dy"/>
-      <sheetName val="应付福利费Dy"/>
-      <sheetName val="预提费用Dy"/>
-      <sheetName val="长期股权投资Mx"/>
-      <sheetName val="Final sample listing"/>
-      <sheetName val="UFPrn20200921194626"/>
-      <sheetName val="余额表200606"/>
-      <sheetName val="200611"/>
-      <sheetName val="200612"/>
-      <sheetName val="Segment"/>
-      <sheetName val="list of LC"/>
-      <sheetName val="冻品入库"/>
-      <sheetName val="鸡油车间"/>
-      <sheetName val="conWP1"/>
-      <sheetName val="外销收入明细表"/>
-      <sheetName val="UFPrn20060111164230"/>
-      <sheetName val="07年1-9月"/>
-      <sheetName val="dep08"/>
-      <sheetName val="成本计提模板"/>
-      <sheetName val="信用证分银行"/>
-      <sheetName val="商承分银行"/>
-      <sheetName val="基本情况"/>
-      <sheetName val="商保"/>
-      <sheetName val="投资收益Mx"/>
-      <sheetName val="三分厂04年1-12月销售价 "/>
-      <sheetName val="05年1月销售价"/>
-      <sheetName val="04年12月销售价"/>
-      <sheetName val="大额未达"/>
-      <sheetName val="校对"/>
-      <sheetName val="抵消信息表"/>
-      <sheetName val="以前年度损益调整"/>
-      <sheetName val="已审CF"/>
-      <sheetName val="Khoan cong truong Tan De"/>
-      <sheetName val="成本"/>
-      <sheetName val="MG1"/>
-      <sheetName val="USCV3"/>
-      <sheetName val="879099"/>
-      <sheetName val="资产负债表(本部原报)"/>
-      <sheetName val="_Profile"/>
-      <sheetName val="附件3-1 穿行待补-展升"/>
-      <sheetName val="待摊费用Dy"/>
-      <sheetName val="固定资产折旧报表"/>
-      <sheetName val="在建工程Dy"/>
-      <sheetName val="Accounts"/>
-      <sheetName val="生产成本Dy"/>
-      <sheetName val="ACTINV"/>
-      <sheetName val="H增"/>
-      <sheetName val="Net Trans Sum"/>
-      <sheetName val="A_Gen"/>
-      <sheetName val="Sens"/>
-      <sheetName val="20071-10月原材料发出计价测试(不打)"/>
-      <sheetName val="200712"/>
-      <sheetName val="自制半成品1-12计价测试"/>
-      <sheetName val="产成品收发存余额表1-12"/>
-      <sheetName val="预付账款Mx"/>
-      <sheetName val="帐上"/>
-      <sheetName val="$TB 1"/>
-      <sheetName val="$TB"/>
-      <sheetName val="Devices"/>
-      <sheetName val="3. Textile"/>
-      <sheetName val="7. NN staff turnover report"/>
-      <sheetName val="帐套"/>
-      <sheetName val="明细"/>
-      <sheetName val="生产领料序时簿"/>
-      <sheetName val="新的工作表"/>
-      <sheetName val="合并试算平衡表"/>
-      <sheetName val="综合成本分析01.01-0205"/>
-      <sheetName val="武平流水"/>
-      <sheetName val="销售收入底稿"/>
-      <sheetName val="混料"/>
-      <sheetName val="基本信息_百鑫"/>
-      <sheetName val="To tied 2001 opening RE"/>
-      <sheetName val="T.B."/>
-      <sheetName val="Sheet697"/>
-      <sheetName val="Sheet912"/>
-      <sheetName val="预收分期表"/>
-      <sheetName val="预收账款明细表D3-2"/>
-      <sheetName val="轨道一厂在产品盘点倒轧表G2-6-5"/>
-      <sheetName val="重分类错报表"/>
-      <sheetName val="裕华城"/>
-      <sheetName val="收入毛利分析D4-21"/>
-      <sheetName val="海外客户提单检查"/>
-      <sheetName val="U8数据"/>
-      <sheetName val="Competition ¥"/>
-      <sheetName val="表头及目录"/>
-      <sheetName val="B15 重要性计算表(审计前）"/>
-      <sheetName val="N__财务费用"/>
-      <sheetName val="N__持有至到期投资"/>
-      <sheetName val="N__存货"/>
-      <sheetName val="N__递延所得税资产和递延所得税负债"/>
-      <sheetName val="N__短期借款"/>
-      <sheetName val="所合并"/>
-      <sheetName val="资合并"/>
-      <sheetName val="N__工程物资"/>
-      <sheetName val="N__公允价值变动收益"/>
-      <sheetName val="N__股本"/>
-      <sheetName val="N__固定资产"/>
-      <sheetName val="N__固定资产清理"/>
-      <sheetName val="N__管理费用"/>
-      <sheetName val="N__货币资金"/>
-      <sheetName val="N__交易性金融负债"/>
-      <sheetName val="N__交易性金融资产"/>
-      <sheetName val="N__开发支出"/>
-      <sheetName val="N__可供出售金融资产"/>
-      <sheetName val="N__库存股"/>
-      <sheetName val="利合并"/>
-      <sheetName val="N__每股收益"/>
-      <sheetName val="N__其他非流动负债"/>
-      <sheetName val="N__其他非流动资产"/>
-      <sheetName val="N__其他流动负债"/>
-      <sheetName val="N__其他应付款"/>
-      <sheetName val="N__其他综合收益"/>
-      <sheetName val="N__其他流动资产"/>
-      <sheetName val="N__商誉"/>
-      <sheetName val="N__生产性生物资产"/>
-      <sheetName val="N__所得税费用"/>
-      <sheetName val="N__投资收益"/>
-      <sheetName val="N__投资性房地产"/>
-      <sheetName val="N__未分配利润"/>
-      <sheetName val="N__无形资产"/>
-      <sheetName val="N__现金流量表附注"/>
-      <sheetName val="现合并"/>
-      <sheetName val="N__销售费用"/>
-      <sheetName val="N__一年内到期的非流动负债"/>
-      <sheetName val="N__一年内到期的非流动资产"/>
-      <sheetName val="N__盈余公积"/>
-      <sheetName val="N__税金及附加"/>
-      <sheetName val="N__营业外收入"/>
-      <sheetName val="N__营业外支出"/>
-      <sheetName val="N__应付股利"/>
-      <sheetName val="N__应付利息"/>
-      <sheetName val="N__应付票据"/>
-      <sheetName val="N__应付债券"/>
-      <sheetName val="N__应付账款"/>
-      <sheetName val="N__应付职工薪酬"/>
-      <sheetName val="N__应交税费"/>
-      <sheetName val="N__应收股利"/>
-      <sheetName val="N__应收利息"/>
-      <sheetName val="N__应收票据"/>
-      <sheetName val="N__油气资产"/>
-      <sheetName val="N__预付款项"/>
-      <sheetName val="N__预计负债"/>
-      <sheetName val="N__预收账款"/>
-      <sheetName val="N__在建工程"/>
-      <sheetName val="N__长期待摊费用"/>
-      <sheetName val="N__长期借款"/>
-      <sheetName val="N__长期应付款"/>
-      <sheetName val="N__长期应收款"/>
-      <sheetName val="N__专项储备"/>
-      <sheetName val="N__专项应付款"/>
-      <sheetName val="N__资本公积"/>
-      <sheetName val="N__资产减值损失"/>
-      <sheetName val="N__资产减值准备"/>
-      <sheetName val="Sheet_Serial"/>
-      <sheetName val="FA MVT"/>
-      <sheetName val="Physical Description"/>
-      <sheetName val="DEF"/>
-      <sheetName val="社員リスト"/>
-      <sheetName val="固定资产借贷方分析J1-3"/>
-      <sheetName val="折旧测算表（不含减值）-直线法J1-8-1-页数多，仅打印头尾"/>
-      <sheetName val="明细表J1-2"/>
-      <sheetName val="累计折旧重新测算（不含减值）J1-8-2-仅打印头尾"/>
-      <sheetName val="标准UPPH"/>
-      <sheetName val="28"/>
-      <sheetName val="14"/>
-      <sheetName val="36"/>
-      <sheetName val="13"/>
-      <sheetName val="16-1"/>
-      <sheetName val="16-2"/>
-      <sheetName val="16-3"/>
-      <sheetName val="Group"/>
-      <sheetName val="FK Ma"/>
-      <sheetName val="MetaData"/>
-      <sheetName val="現金流量"/>
-      <sheetName val="固清"/>
-      <sheetName val="Wacc"/>
-      <sheetName val="5440彙總表"/>
-      <sheetName val="PopCache_Sheet1"/>
-      <sheetName val="IPO"/>
-      <sheetName val="总账"/>
-      <sheetName val="yszk200412.dbf"/>
-      <sheetName val="U321"/>
-      <sheetName val="dd"/>
-      <sheetName val="维简费"/>
-      <sheetName val="维简费返还"/>
-      <sheetName val="Threshold Table"/>
-      <sheetName val="Translation FRF"/>
-      <sheetName val="凭证汇总"/>
-      <sheetName val="Sales by customer- details"/>
-      <sheetName val="&lt;FF&gt; Tax Payable"/>
-      <sheetName val="基础设置"/>
-      <sheetName val="期末应付账款明细表G4-2"/>
-      <sheetName val="C - Cash and Bank"/>
-      <sheetName val="8-1"/>
-      <sheetName val="大额运费分析表G4-4-4"/>
-      <sheetName val="科目设定"/>
-      <sheetName val="销售发票专用序时簿"/>
-      <sheetName val="PRC 15"/>
-      <sheetName val="本期调整分录"/>
-      <sheetName val="上期调整分录"/>
-      <sheetName val="现流本期编制分录"/>
-      <sheetName val="现流上期编制分录"/>
-      <sheetName val="资产负债表、利润表、现金流量表"/>
-      <sheetName val="销售发票序时簿"/>
-      <sheetName val="PRC 13"/>
-      <sheetName val="May"/>
-      <sheetName val="33230"/>
-      <sheetName val="hidesheet"/>
-      <sheetName val="函证结果汇总表D4-34"/>
-      <sheetName val="财企01表_南宁轨道交通集团有限责任公司（集团合并）期末数"/>
-      <sheetName val="2021年TB"/>
-      <sheetName val="凭证汇总1"/>
-      <sheetName val="Cash Flows"/>
-      <sheetName val="人事明细"/>
-      <sheetName val="半成品slje"/>
-      <sheetName val="9-12月"/>
-      <sheetName val="附注索引"/>
-      <sheetName val="汇总核对表"/>
-      <sheetName val="2005余额表"/>
-      <sheetName val="委托贷款Dy"/>
-      <sheetName val="坏账准备_预付账款Dy"/>
-      <sheetName val="基础"/>
-      <sheetName val="累计折旧_2"/>
-      <sheetName val="Header Data"/>
-      <sheetName val="项目编号列表"/>
-      <sheetName val="单位"/>
-      <sheetName val="L1-1资产负债表"/>
-      <sheetName val="Y3-2 06企业会计制度附注"/>
-      <sheetName val="Y0-1报告准备表（无需打印）"/>
-      <sheetName val="销售费用Dy"/>
-      <sheetName val="主数据"/>
-      <sheetName val="VM"/>
-      <sheetName val="天合与太阳时代的往来余额(天合账面)"/>
-      <sheetName val="181231科技&amp;凯博-其他应付"/>
-      <sheetName val="2021应收账面数"/>
-      <sheetName val="2021工程账面数"/>
-      <sheetName val="评估结论"/>
-      <sheetName val="FIRE Parameters"/>
-      <sheetName val="G2TempSheet"/>
-      <sheetName val="损益表"/>
-      <sheetName val="_810余额表"/>
-      <sheetName val="qtr local"/>
-      <sheetName val="A_1"/>
-      <sheetName val="备注"/>
-      <sheetName val="工程量"/>
-      <sheetName val="服务"/>
-      <sheetName val="1梁家5-1-1房建"/>
-      <sheetName val="1梁家5-1-2构筑"/>
-      <sheetName val="p &amp; lx"/>
-      <sheetName val="3-9其他应收"/>
-      <sheetName val="9-3应付帐款"/>
-      <sheetName val="Director"/>
-      <sheetName val="3-1-2银存"/>
-      <sheetName val="3-1-3其他货币"/>
-      <sheetName val="10-1长借"/>
-      <sheetName val="10-2应付债券"/>
-      <sheetName val="10-3长期应付款"/>
-      <sheetName val="10-4住房周转金"/>
-      <sheetName val="10-5其他长期负债"/>
-      <sheetName val="10-6递延税款贷项"/>
-      <sheetName val="3-10存货汇总"/>
-      <sheetName val="3-12待处理流损"/>
-      <sheetName val="3-13一年长债"/>
-      <sheetName val="3-14其他流资"/>
-      <sheetName val="3-2短投汇总"/>
-      <sheetName val="3-5应收股利"/>
-      <sheetName val="3-6应收利息"/>
-      <sheetName val="3-7预付帐款"/>
-      <sheetName val="3-8应收补贴"/>
-      <sheetName val="长投汇总"/>
-      <sheetName val="6-2其他无形"/>
-      <sheetName val="7-1开办费"/>
-      <sheetName val="7-2长期待摊"/>
-      <sheetName val="8-1其他长期"/>
-      <sheetName val="8-2递税借项"/>
-      <sheetName val="9-1短期借款"/>
-      <sheetName val="9-10应付利润"/>
-      <sheetName val="9-11其他应交"/>
-      <sheetName val="9-12预提"/>
-      <sheetName val="9-13一年内长债"/>
-      <sheetName val="9-14其他流负"/>
-      <sheetName val="9-2应付票据"/>
-      <sheetName val="9-4预收帐款"/>
-      <sheetName val="9-5代销商品款"/>
-      <sheetName val="9-6其他应付款"/>
-      <sheetName val="9-7应付工资"/>
-      <sheetName val="9-8应付福利费"/>
-      <sheetName val="9-9应交税金"/>
-      <sheetName val="梁家5-1-1房建"/>
-      <sheetName val="XLR_NoRangeSheet"/>
-      <sheetName val="累计折旧测算表"/>
-      <sheetName val="Alternative"/>
-      <sheetName val="统计"/>
-      <sheetName val="长期股权投资审定表"/>
-      <sheetName val="10K4"/>
-      <sheetName val="工企资产负债表"/>
-      <sheetName val="出租开发产品明细"/>
-      <sheetName val="预付款项Dy"/>
-      <sheetName val="预收款项Dy"/>
-      <sheetName val="Sales for 2001"/>
-      <sheetName val="IPQC-9 二次烧结"/>
-      <sheetName val="上缴管理费明细"/>
-      <sheetName val="服务部待报废"/>
-      <sheetName val="VAS TB"/>
-      <sheetName val="frm销售合同-Sub"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1" refreshError="1"/>
-      <sheetData sheetId="2"/>
-      <sheetData sheetId="3"/>
-      <sheetData sheetId="4" refreshError="1"/>
-      <sheetData sheetId="5"/>
-      <sheetData sheetId="6"/>
-      <sheetData sheetId="7"/>
-      <sheetData sheetId="8" refreshError="1"/>
-      <sheetData sheetId="9" refreshError="1"/>
-      <sheetData sheetId="10" refreshError="1"/>
-      <sheetData sheetId="11" refreshError="1"/>
-      <sheetData sheetId="12" refreshError="1"/>
-      <sheetData sheetId="13" refreshError="1"/>
-      <sheetData sheetId="14" refreshError="1"/>
-      <sheetData sheetId="15" refreshError="1"/>
-      <sheetData sheetId="16" refreshError="1"/>
-      <sheetData sheetId="17" refreshError="1"/>
-      <sheetData sheetId="18" refreshError="1"/>
-      <sheetData sheetId="19" refreshError="1"/>
-      <sheetData sheetId="20" refreshError="1"/>
-      <sheetData sheetId="21" refreshError="1"/>
-      <sheetData sheetId="22" refreshError="1"/>
-      <sheetData sheetId="23" refreshError="1"/>
-      <sheetData sheetId="24" refreshError="1"/>
-      <sheetData sheetId="25" refreshError="1"/>
-      <sheetData sheetId="26" refreshError="1"/>
-      <sheetData sheetId="27" refreshError="1"/>
-      <sheetData sheetId="28" refreshError="1"/>
-      <sheetData sheetId="29" refreshError="1"/>
-      <sheetData sheetId="30" refreshError="1"/>
-      <sheetData sheetId="31" refreshError="1"/>
-      <sheetData sheetId="32" refreshError="1"/>
-      <sheetData sheetId="33" refreshError="1"/>
-      <sheetData sheetId="34" refreshError="1"/>
-      <sheetData sheetId="35" refreshError="1"/>
-      <sheetData sheetId="36" refreshError="1"/>
-      <sheetData sheetId="37" refreshError="1"/>
-      <sheetData sheetId="38" refreshError="1"/>
-      <sheetData sheetId="39" refreshError="1"/>
-      <sheetData sheetId="40" refreshError="1"/>
-      <sheetData sheetId="41" refreshError="1"/>
-      <sheetData sheetId="42" refreshError="1"/>
-      <sheetData sheetId="43" refreshError="1"/>
-      <sheetData sheetId="44" refreshError="1"/>
-      <sheetData sheetId="45" refreshError="1"/>
-      <sheetData sheetId="46" refreshError="1"/>
-      <sheetData sheetId="47" refreshError="1"/>
-      <sheetData sheetId="48" refreshError="1"/>
-      <sheetData sheetId="49" refreshError="1"/>
-      <sheetData sheetId="50" refreshError="1"/>
-      <sheetData sheetId="51" refreshError="1"/>
-      <sheetData sheetId="52" refreshError="1"/>
-      <sheetData sheetId="53" refreshError="1"/>
-      <sheetData sheetId="54" refreshError="1"/>
-      <sheetData sheetId="55" refreshError="1"/>
-      <sheetData sheetId="56" refreshError="1"/>
-      <sheetData sheetId="57" refreshError="1"/>
-      <sheetData sheetId="58" refreshError="1"/>
-      <sheetData sheetId="59" refreshError="1"/>
-      <sheetData sheetId="60" refreshError="1"/>
-      <sheetData sheetId="61" refreshError="1"/>
-      <sheetData sheetId="62" refreshError="1"/>
-      <sheetData sheetId="63" refreshError="1"/>
-      <sheetData sheetId="64" refreshError="1"/>
-      <sheetData sheetId="65" refreshError="1"/>
-      <sheetData sheetId="66" refreshError="1"/>
-      <sheetData sheetId="67" refreshError="1"/>
-      <sheetData sheetId="68" refreshError="1"/>
-      <sheetData sheetId="69" refreshError="1"/>
-      <sheetData sheetId="70" refreshError="1"/>
-      <sheetData sheetId="71" refreshError="1"/>
-      <sheetData sheetId="72" refreshError="1"/>
-      <sheetData sheetId="73" refreshError="1"/>
-      <sheetData sheetId="74" refreshError="1"/>
-      <sheetData sheetId="75" refreshError="1"/>
-      <sheetData sheetId="76" refreshError="1"/>
-      <sheetData sheetId="77" refreshError="1"/>
-      <sheetData sheetId="78" refreshError="1"/>
-      <sheetData sheetId="79" refreshError="1"/>
-      <sheetData sheetId="80" refreshError="1"/>
-      <sheetData sheetId="81" refreshError="1"/>
-      <sheetData sheetId="82" refreshError="1"/>
-      <sheetData sheetId="83" refreshError="1"/>
-      <sheetData sheetId="84" refreshError="1"/>
-      <sheetData sheetId="85" refreshError="1"/>
-      <sheetData sheetId="86" refreshError="1"/>
-      <sheetData sheetId="87" refreshError="1"/>
-      <sheetData sheetId="88" refreshError="1"/>
-      <sheetData sheetId="89" refreshError="1"/>
-      <sheetData sheetId="90" refreshError="1"/>
-      <sheetData sheetId="91" refreshError="1"/>
-      <sheetData sheetId="92" refreshError="1"/>
-      <sheetData sheetId="93" refreshError="1"/>
-      <sheetData sheetId="94" refreshError="1"/>
-      <sheetData sheetId="95" refreshError="1"/>
-      <sheetData sheetId="96" refreshError="1"/>
-      <sheetData sheetId="97" refreshError="1"/>
-      <sheetData sheetId="98" refreshError="1"/>
-      <sheetData sheetId="99" refreshError="1"/>
-      <sheetData sheetId="100" refreshError="1"/>
-      <sheetData sheetId="101" refreshError="1"/>
-      <sheetData sheetId="102" refreshError="1"/>
-      <sheetData sheetId="103" refreshError="1"/>
-      <sheetData sheetId="104" refreshError="1"/>
-      <sheetData sheetId="105" refreshError="1"/>
-      <sheetData sheetId="106" refreshError="1"/>
-      <sheetData sheetId="107" refreshError="1"/>
-      <sheetData sheetId="108" refreshError="1"/>
-      <sheetData sheetId="109" refreshError="1"/>
-      <sheetData sheetId="110" refreshError="1"/>
-      <sheetData sheetId="111" refreshError="1"/>
-      <sheetData sheetId="112" refreshError="1"/>
-      <sheetData sheetId="113" refreshError="1"/>
-      <sheetData sheetId="114" refreshError="1"/>
-      <sheetData sheetId="115" refreshError="1"/>
-      <sheetData sheetId="116" refreshError="1"/>
-      <sheetData sheetId="117" refreshError="1"/>
-      <sheetData sheetId="118" refreshError="1"/>
-      <sheetData sheetId="119" refreshError="1"/>
-      <sheetData sheetId="120" refreshError="1"/>
-      <sheetData sheetId="121" refreshError="1"/>
-      <sheetData sheetId="122" refreshError="1"/>
-      <sheetData sheetId="123" refreshError="1"/>
-      <sheetData sheetId="124" refreshError="1"/>
-      <sheetData sheetId="125" refreshError="1"/>
-      <sheetData sheetId="126" refreshError="1"/>
-      <sheetData sheetId="127" refreshError="1"/>
-      <sheetData sheetId="128" refreshError="1"/>
-      <sheetData sheetId="129" refreshError="1"/>
-      <sheetData sheetId="130" refreshError="1"/>
-      <sheetData sheetId="131" refreshError="1"/>
-      <sheetData sheetId="132" refreshError="1"/>
-      <sheetData sheetId="133" refreshError="1"/>
-      <sheetData sheetId="134" refreshError="1"/>
-      <sheetData sheetId="135" refreshError="1"/>
-      <sheetData sheetId="136" refreshError="1"/>
-      <sheetData sheetId="137" refreshError="1"/>
-      <sheetData sheetId="138" refreshError="1"/>
-      <sheetData sheetId="139" refreshError="1"/>
-      <sheetData sheetId="140" refreshError="1"/>
-      <sheetData sheetId="141" refreshError="1"/>
-      <sheetData sheetId="142" refreshError="1"/>
-      <sheetData sheetId="143" refreshError="1"/>
-      <sheetData sheetId="144" refreshError="1"/>
-      <sheetData sheetId="145" refreshError="1"/>
-      <sheetData sheetId="146" refreshError="1"/>
-      <sheetData sheetId="147" refreshError="1"/>
-      <sheetData sheetId="148" refreshError="1"/>
-      <sheetData sheetId="149" refreshError="1"/>
-      <sheetData sheetId="150" refreshError="1"/>
-      <sheetData sheetId="151" refreshError="1"/>
-      <sheetData sheetId="152" refreshError="1"/>
-      <sheetData sheetId="153" refreshError="1"/>
-      <sheetData sheetId="154" refreshError="1"/>
-      <sheetData sheetId="155" refreshError="1"/>
-      <sheetData sheetId="156" refreshError="1"/>
-      <sheetData sheetId="157" refreshError="1"/>
-      <sheetData sheetId="158" refreshError="1"/>
-      <sheetData sheetId="159" refreshError="1"/>
-      <sheetData sheetId="160" refreshError="1"/>
-      <sheetData sheetId="161" refreshError="1"/>
-      <sheetData sheetId="162" refreshError="1"/>
-      <sheetData sheetId="163" refreshError="1"/>
-      <sheetData sheetId="164" refreshError="1"/>
-      <sheetData sheetId="165" refreshError="1"/>
-      <sheetData sheetId="166" refreshError="1"/>
-      <sheetData sheetId="167" refreshError="1"/>
-      <sheetData sheetId="168" refreshError="1"/>
-      <sheetData sheetId="169" refreshError="1"/>
-      <sheetData sheetId="170" refreshError="1"/>
-      <sheetData sheetId="171" refreshError="1"/>
-      <sheetData sheetId="172" refreshError="1"/>
-      <sheetData sheetId="173" refreshError="1"/>
-      <sheetData sheetId="174" refreshError="1"/>
-      <sheetData sheetId="175" refreshError="1"/>
-      <sheetData sheetId="176" refreshError="1"/>
-      <sheetData sheetId="177" refreshError="1"/>
-      <sheetData sheetId="178" refreshError="1"/>
-      <sheetData sheetId="179" refreshError="1"/>
-      <sheetData sheetId="180" refreshError="1"/>
-      <sheetData sheetId="181" refreshError="1"/>
-      <sheetData sheetId="182" refreshError="1"/>
-      <sheetData sheetId="183" refreshError="1"/>
-      <sheetData sheetId="184" refreshError="1"/>
-      <sheetData sheetId="185" refreshError="1"/>
-      <sheetData sheetId="186" refreshError="1"/>
-      <sheetData sheetId="187" refreshError="1"/>
-      <sheetData sheetId="188" refreshError="1"/>
-      <sheetData sheetId="189" refreshError="1"/>
-      <sheetData sheetId="190" refreshError="1"/>
-      <sheetData sheetId="191" refreshError="1"/>
-      <sheetData sheetId="192" refreshError="1"/>
-      <sheetData sheetId="193" refreshError="1"/>
-      <sheetData sheetId="194" refreshError="1"/>
-      <sheetData sheetId="195" refreshError="1"/>
-      <sheetData sheetId="196" refreshError="1"/>
-      <sheetData sheetId="197" refreshError="1"/>
-      <sheetData sheetId="198" refreshError="1"/>
-      <sheetData sheetId="199" refreshError="1"/>
-      <sheetData sheetId="200" refreshError="1"/>
-      <sheetData sheetId="201" refreshError="1"/>
-      <sheetData sheetId="202" refreshError="1"/>
-      <sheetData sheetId="203" refreshError="1"/>
-      <sheetData sheetId="204" refreshError="1"/>
-      <sheetData sheetId="205" refreshError="1"/>
-      <sheetData sheetId="206" refreshError="1"/>
-      <sheetData sheetId="207" refreshError="1"/>
-      <sheetData sheetId="208" refreshError="1"/>
-      <sheetData sheetId="209" refreshError="1"/>
-      <sheetData sheetId="210" refreshError="1"/>
-      <sheetData sheetId="211" refreshError="1"/>
-      <sheetData sheetId="212" refreshError="1"/>
-      <sheetData sheetId="213" refreshError="1"/>
-      <sheetData sheetId="214" refreshError="1"/>
-      <sheetData sheetId="215" refreshError="1"/>
-      <sheetData sheetId="216" refreshError="1"/>
-      <sheetData sheetId="217" refreshError="1"/>
-      <sheetData sheetId="218" refreshError="1"/>
-      <sheetData sheetId="219" refreshError="1"/>
-      <sheetData sheetId="220" refreshError="1"/>
-      <sheetData sheetId="221" refreshError="1"/>
-      <sheetData sheetId="222" refreshError="1"/>
-      <sheetData sheetId="223" refreshError="1"/>
-      <sheetData sheetId="224" refreshError="1"/>
-      <sheetData sheetId="225" refreshError="1"/>
-      <sheetData sheetId="226" refreshError="1"/>
-      <sheetData sheetId="227" refreshError="1"/>
-      <sheetData sheetId="228" refreshError="1"/>
-      <sheetData sheetId="229" refreshError="1"/>
-      <sheetData sheetId="230" refreshError="1"/>
-      <sheetData sheetId="231" refreshError="1"/>
-      <sheetData sheetId="232" refreshError="1"/>
-      <sheetData sheetId="233" refreshError="1"/>
-      <sheetData sheetId="234" refreshError="1"/>
-      <sheetData sheetId="235" refreshError="1"/>
-      <sheetData sheetId="236" refreshError="1"/>
-      <sheetData sheetId="237" refreshError="1"/>
-      <sheetData sheetId="238" refreshError="1"/>
-      <sheetData sheetId="239" refreshError="1"/>
-      <sheetData sheetId="240" refreshError="1"/>
-      <sheetData sheetId="241" refreshError="1"/>
-      <sheetData sheetId="242" refreshError="1"/>
-      <sheetData sheetId="243" refreshError="1"/>
-      <sheetData sheetId="244" refreshError="1"/>
-      <sheetData sheetId="245" refreshError="1"/>
-      <sheetData sheetId="246" refreshError="1"/>
-      <sheetData sheetId="247" refreshError="1"/>
-      <sheetData sheetId="248" refreshError="1"/>
-      <sheetData sheetId="249" refreshError="1"/>
-      <sheetData sheetId="250" refreshError="1"/>
-      <sheetData sheetId="251" refreshError="1"/>
-      <sheetData sheetId="252" refreshError="1"/>
-      <sheetData sheetId="253" refreshError="1"/>
-      <sheetData sheetId="254" refreshError="1"/>
-      <sheetData sheetId="255" refreshError="1"/>
-      <sheetData sheetId="256" refreshError="1"/>
-      <sheetData sheetId="257" refreshError="1"/>
-      <sheetData sheetId="258" refreshError="1"/>
-      <sheetData sheetId="259" refreshError="1"/>
-      <sheetData sheetId="260" refreshError="1"/>
-      <sheetData sheetId="261" refreshError="1"/>
-      <sheetData sheetId="262" refreshError="1"/>
-      <sheetData sheetId="263" refreshError="1"/>
-      <sheetData sheetId="264" refreshError="1"/>
-      <sheetData sheetId="265" refreshError="1"/>
-      <sheetData sheetId="266" refreshError="1"/>
-      <sheetData sheetId="267" refreshError="1"/>
-      <sheetData sheetId="268" refreshError="1"/>
-      <sheetData sheetId="269" refreshError="1"/>
-      <sheetData sheetId="270" refreshError="1"/>
-      <sheetData sheetId="271" refreshError="1"/>
-      <sheetData sheetId="272" refreshError="1"/>
-      <sheetData sheetId="273" refreshError="1"/>
-      <sheetData sheetId="274" refreshError="1"/>
-      <sheetData sheetId="275" refreshError="1"/>
-      <sheetData sheetId="276" refreshError="1"/>
-      <sheetData sheetId="277" refreshError="1"/>
-      <sheetData sheetId="278" refreshError="1"/>
-      <sheetData sheetId="279" refreshError="1"/>
-      <sheetData sheetId="280" refreshError="1"/>
-      <sheetData sheetId="281" refreshError="1"/>
-      <sheetData sheetId="282" refreshError="1"/>
-      <sheetData sheetId="283" refreshError="1"/>
-      <sheetData sheetId="284" refreshError="1"/>
-      <sheetData sheetId="285" refreshError="1"/>
-      <sheetData sheetId="286" refreshError="1"/>
-      <sheetData sheetId="287" refreshError="1"/>
-      <sheetData sheetId="288" refreshError="1"/>
-      <sheetData sheetId="289" refreshError="1"/>
-      <sheetData sheetId="290" refreshError="1"/>
-      <sheetData sheetId="291" refreshError="1"/>
-      <sheetData sheetId="292" refreshError="1"/>
-      <sheetData sheetId="293" refreshError="1"/>
-      <sheetData sheetId="294" refreshError="1"/>
-      <sheetData sheetId="295" refreshError="1"/>
-      <sheetData sheetId="296" refreshError="1"/>
-      <sheetData sheetId="297" refreshError="1"/>
-      <sheetData sheetId="298" refreshError="1"/>
-      <sheetData sheetId="299" refreshError="1"/>
-      <sheetData sheetId="300" refreshError="1"/>
-      <sheetData sheetId="301" refreshError="1"/>
-      <sheetData sheetId="302" refreshError="1"/>
-      <sheetData sheetId="303" refreshError="1"/>
-      <sheetData sheetId="304" refreshError="1"/>
-      <sheetData sheetId="305" refreshError="1"/>
-      <sheetData sheetId="306" refreshError="1"/>
-      <sheetData sheetId="307" refreshError="1"/>
-      <sheetData sheetId="308" refreshError="1"/>
-      <sheetData sheetId="309" refreshError="1"/>
-      <sheetData sheetId="310" refreshError="1"/>
-      <sheetData sheetId="311" refreshError="1"/>
-      <sheetData sheetId="312" refreshError="1"/>
-      <sheetData sheetId="313" refreshError="1"/>
-      <sheetData sheetId="314" refreshError="1"/>
-      <sheetData sheetId="315" refreshError="1"/>
-      <sheetData sheetId="316" refreshError="1"/>
-      <sheetData sheetId="317" refreshError="1"/>
-      <sheetData sheetId="318" refreshError="1"/>
-      <sheetData sheetId="319" refreshError="1"/>
-      <sheetData sheetId="320" refreshError="1"/>
-      <sheetData sheetId="321" refreshError="1"/>
-      <sheetData sheetId="322" refreshError="1"/>
-      <sheetData sheetId="323" refreshError="1"/>
-      <sheetData sheetId="324" refreshError="1"/>
-      <sheetData sheetId="325" refreshError="1"/>
-      <sheetData sheetId="326" refreshError="1"/>
-      <sheetData sheetId="327" refreshError="1"/>
-      <sheetData sheetId="328" refreshError="1"/>
-      <sheetData sheetId="329" refreshError="1"/>
-      <sheetData sheetId="330" refreshError="1"/>
-      <sheetData sheetId="331" refreshError="1"/>
-      <sheetData sheetId="332" refreshError="1"/>
-      <sheetData sheetId="333" refreshError="1"/>
-      <sheetData sheetId="334" refreshError="1"/>
-      <sheetData sheetId="335" refreshError="1"/>
-      <sheetData sheetId="336" refreshError="1"/>
-      <sheetData sheetId="337" refreshError="1"/>
-      <sheetData sheetId="338" refreshError="1"/>
-      <sheetData sheetId="339" refreshError="1"/>
-      <sheetData sheetId="340" refreshError="1"/>
-      <sheetData sheetId="341" refreshError="1"/>
-      <sheetData sheetId="342" refreshError="1"/>
-      <sheetData sheetId="343" refreshError="1"/>
-      <sheetData sheetId="344" refreshError="1"/>
-      <sheetData sheetId="345" refreshError="1"/>
-      <sheetData sheetId="346" refreshError="1"/>
-      <sheetData sheetId="347" refreshError="1"/>
-      <sheetData sheetId="348" refreshError="1"/>
-      <sheetData sheetId="349" refreshError="1"/>
-      <sheetData sheetId="350" refreshError="1"/>
-      <sheetData sheetId="351" refreshError="1"/>
-      <sheetData sheetId="352" refreshError="1"/>
-      <sheetData sheetId="353" refreshError="1"/>
-      <sheetData sheetId="354" refreshError="1"/>
-      <sheetData sheetId="355" refreshError="1"/>
-      <sheetData sheetId="356" refreshError="1"/>
-      <sheetData sheetId="357" refreshError="1"/>
-      <sheetData sheetId="358" refreshError="1"/>
-      <sheetData sheetId="359" refreshError="1"/>
-      <sheetData sheetId="360" refreshError="1"/>
-      <sheetData sheetId="361" refreshError="1"/>
-      <sheetData sheetId="362" refreshError="1"/>
-      <sheetData sheetId="363" refreshError="1"/>
-      <sheetData sheetId="364" refreshError="1"/>
-      <sheetData sheetId="365" refreshError="1"/>
-      <sheetData sheetId="366" refreshError="1"/>
-      <sheetData sheetId="367" refreshError="1"/>
-      <sheetData sheetId="368" refreshError="1"/>
-      <sheetData sheetId="369" refreshError="1"/>
-      <sheetData sheetId="370" refreshError="1"/>
-      <sheetData sheetId="371" refreshError="1"/>
-      <sheetData sheetId="372" refreshError="1"/>
-      <sheetData sheetId="373" refreshError="1"/>
-      <sheetData sheetId="374" refreshError="1"/>
-      <sheetData sheetId="375" refreshError="1"/>
-      <sheetData sheetId="376" refreshError="1"/>
-      <sheetData sheetId="377" refreshError="1"/>
-      <sheetData sheetId="378" refreshError="1"/>
-      <sheetData sheetId="379" refreshError="1"/>
-      <sheetData sheetId="380" refreshError="1"/>
-      <sheetData sheetId="381" refreshError="1"/>
-      <sheetData sheetId="382" refreshError="1"/>
-      <sheetData sheetId="383" refreshError="1"/>
-      <sheetData sheetId="384" refreshError="1"/>
-      <sheetData sheetId="385" refreshError="1"/>
-      <sheetData sheetId="386" refreshError="1"/>
-      <sheetData sheetId="387" refreshError="1"/>
-      <sheetData sheetId="388" refreshError="1"/>
-      <sheetData sheetId="389" refreshError="1"/>
-      <sheetData sheetId="390" refreshError="1"/>
-      <sheetData sheetId="391" refreshError="1"/>
-      <sheetData sheetId="392" refreshError="1"/>
-      <sheetData sheetId="393" refreshError="1"/>
-      <sheetData sheetId="394" refreshError="1"/>
-      <sheetData sheetId="395" refreshError="1"/>
-      <sheetData sheetId="396" refreshError="1"/>
-      <sheetData sheetId="397" refreshError="1"/>
-      <sheetData sheetId="398" refreshError="1"/>
-      <sheetData sheetId="399" refreshError="1"/>
-      <sheetData sheetId="400" refreshError="1"/>
-      <sheetData sheetId="401" refreshError="1"/>
-      <sheetData sheetId="402" refreshError="1"/>
-      <sheetData sheetId="403" refreshError="1"/>
-      <sheetData sheetId="404" refreshError="1"/>
-      <sheetData sheetId="405" refreshError="1"/>
-      <sheetData sheetId="406" refreshError="1"/>
-      <sheetData sheetId="407" refreshError="1"/>
-      <sheetData sheetId="408" refreshError="1"/>
-      <sheetData sheetId="409" refreshError="1"/>
-      <sheetData sheetId="410" refreshError="1"/>
-      <sheetData sheetId="411" refreshError="1"/>
-      <sheetData sheetId="412" refreshError="1"/>
-      <sheetData sheetId="413" refreshError="1"/>
-      <sheetData sheetId="414" refreshError="1"/>
-      <sheetData sheetId="415" refreshError="1"/>
-      <sheetData sheetId="416" refreshError="1"/>
-      <sheetData sheetId="417" refreshError="1"/>
-      <sheetData sheetId="418" refreshError="1"/>
-      <sheetData sheetId="419" refreshError="1"/>
-      <sheetData sheetId="420" refreshError="1"/>
-      <sheetData sheetId="421" refreshError="1"/>
-      <sheetData sheetId="422" refreshError="1"/>
-      <sheetData sheetId="423" refreshError="1"/>
-      <sheetData sheetId="424" refreshError="1"/>
-      <sheetData sheetId="425" refreshError="1"/>
-      <sheetData sheetId="426" refreshError="1"/>
-      <sheetData sheetId="427" refreshError="1"/>
-      <sheetData sheetId="428" refreshError="1"/>
-      <sheetData sheetId="429" refreshError="1"/>
-      <sheetData sheetId="430" refreshError="1"/>
-      <sheetData sheetId="431" refreshError="1"/>
-      <sheetData sheetId="432" refreshError="1"/>
-      <sheetData sheetId="433" refreshError="1"/>
-      <sheetData sheetId="434" refreshError="1"/>
-      <sheetData sheetId="435" refreshError="1"/>
-      <sheetData sheetId="436" refreshError="1"/>
-      <sheetData sheetId="437" refreshError="1"/>
-      <sheetData sheetId="438" refreshError="1"/>
-      <sheetData sheetId="439" refreshError="1"/>
-      <sheetData sheetId="440" refreshError="1"/>
-      <sheetData sheetId="441" refreshError="1"/>
-      <sheetData sheetId="442" refreshError="1"/>
-      <sheetData sheetId="443" refreshError="1"/>
-      <sheetData sheetId="444" refreshError="1"/>
-      <sheetData sheetId="445" refreshError="1"/>
-      <sheetData sheetId="446" refreshError="1"/>
-      <sheetData sheetId="447" refreshError="1"/>
-      <sheetData sheetId="448" refreshError="1"/>
-      <sheetData sheetId="449" refreshError="1"/>
-      <sheetData sheetId="450" refreshError="1"/>
-      <sheetData sheetId="451" refreshError="1"/>
-      <sheetData sheetId="452" refreshError="1"/>
-      <sheetData sheetId="453" refreshError="1"/>
-      <sheetData sheetId="454" refreshError="1"/>
-      <sheetData sheetId="455" refreshError="1"/>
-      <sheetData sheetId="456" refreshError="1"/>
-      <sheetData sheetId="457" refreshError="1"/>
-      <sheetData sheetId="458" refreshError="1"/>
-      <sheetData sheetId="459" refreshError="1"/>
-      <sheetData sheetId="460" refreshError="1"/>
-      <sheetData sheetId="461" refreshError="1"/>
-      <sheetData sheetId="462" refreshError="1"/>
-      <sheetData sheetId="463" refreshError="1"/>
-      <sheetData sheetId="464" refreshError="1"/>
-      <sheetData sheetId="465" refreshError="1"/>
-      <sheetData sheetId="466" refreshError="1"/>
-      <sheetData sheetId="467" refreshError="1"/>
-      <sheetData sheetId="468" refreshError="1"/>
-      <sheetData sheetId="469" refreshError="1"/>
-      <sheetData sheetId="470" refreshError="1"/>
-      <sheetData sheetId="471" refreshError="1"/>
-      <sheetData sheetId="472" refreshError="1"/>
-      <sheetData sheetId="473" refreshError="1"/>
-      <sheetData sheetId="474" refreshError="1"/>
-      <sheetData sheetId="475" refreshError="1"/>
-      <sheetData sheetId="476" refreshError="1"/>
-      <sheetData sheetId="477" refreshError="1"/>
-      <sheetData sheetId="478" refreshError="1"/>
-      <sheetData sheetId="479" refreshError="1"/>
-      <sheetData sheetId="480" refreshError="1"/>
-      <sheetData sheetId="481" refreshError="1"/>
-      <sheetData sheetId="482" refreshError="1"/>
-      <sheetData sheetId="483" refreshError="1"/>
-      <sheetData sheetId="484" refreshError="1"/>
-      <sheetData sheetId="485" refreshError="1"/>
-      <sheetData sheetId="486" refreshError="1"/>
-      <sheetData sheetId="487" refreshError="1"/>
-      <sheetData sheetId="488" refreshError="1"/>
-      <sheetData sheetId="489" refreshError="1"/>
-      <sheetData sheetId="490" refreshError="1"/>
-      <sheetData sheetId="491" refreshError="1"/>
-      <sheetData sheetId="492" refreshError="1"/>
-      <sheetData sheetId="493" refreshError="1"/>
-      <sheetData sheetId="494" refreshError="1"/>
-      <sheetData sheetId="495" refreshError="1"/>
-      <sheetData sheetId="496" refreshError="1"/>
-      <sheetData sheetId="497" refreshError="1"/>
-      <sheetData sheetId="498" refreshError="1"/>
-      <sheetData sheetId="499" refreshError="1"/>
-      <sheetData sheetId="500" refreshError="1"/>
-      <sheetData sheetId="501" refreshError="1"/>
-      <sheetData sheetId="502" refreshError="1"/>
-      <sheetData sheetId="503" refreshError="1"/>
-      <sheetData sheetId="504" refreshError="1"/>
-      <sheetData sheetId="505" refreshError="1"/>
-      <sheetData sheetId="506" refreshError="1"/>
-      <sheetData sheetId="507" refreshError="1"/>
-      <sheetData sheetId="508" refreshError="1"/>
-      <sheetData sheetId="509" refreshError="1"/>
-      <sheetData sheetId="510" refreshError="1"/>
-      <sheetData sheetId="511" refreshError="1"/>
-      <sheetData sheetId="512" refreshError="1"/>
-      <sheetData sheetId="513" refreshError="1"/>
-      <sheetData sheetId="514" refreshError="1"/>
-      <sheetData sheetId="515" refreshError="1"/>
-      <sheetData sheetId="516" refreshError="1"/>
-      <sheetData sheetId="517" refreshError="1"/>
-      <sheetData sheetId="518" refreshError="1"/>
-      <sheetData sheetId="519" refreshError="1"/>
-      <sheetData sheetId="520" refreshError="1"/>
-      <sheetData sheetId="521" refreshError="1"/>
-      <sheetData sheetId="522" refreshError="1"/>
-      <sheetData sheetId="523" refreshError="1"/>
-      <sheetData sheetId="524" refreshError="1"/>
-      <sheetData sheetId="525" refreshError="1"/>
-      <sheetData sheetId="526" refreshError="1"/>
-      <sheetData sheetId="527" refreshError="1"/>
-      <sheetData sheetId="528" refreshError="1"/>
-      <sheetData sheetId="529" refreshError="1"/>
-      <sheetData sheetId="530" refreshError="1"/>
-      <sheetData sheetId="531" refreshError="1"/>
-      <sheetData sheetId="532" refreshError="1"/>
-      <sheetData sheetId="533" refreshError="1"/>
-      <sheetData sheetId="534" refreshError="1"/>
-      <sheetData sheetId="535" refreshError="1"/>
-      <sheetData sheetId="536" refreshError="1"/>
-      <sheetData sheetId="537" refreshError="1"/>
-      <sheetData sheetId="538" refreshError="1"/>
-      <sheetData sheetId="539" refreshError="1"/>
-      <sheetData sheetId="540" refreshError="1"/>
-      <sheetData sheetId="541" refreshError="1"/>
-      <sheetData sheetId="542" refreshError="1"/>
-      <sheetData sheetId="543" refreshError="1"/>
-      <sheetData sheetId="544" refreshError="1"/>
-      <sheetData sheetId="545" refreshError="1"/>
-      <sheetData sheetId="546" refreshError="1"/>
-      <sheetData sheetId="547" refreshError="1"/>
-      <sheetData sheetId="548" refreshError="1"/>
-      <sheetData sheetId="549" refreshError="1"/>
-      <sheetData sheetId="550" refreshError="1"/>
-      <sheetData sheetId="551" refreshError="1"/>
-      <sheetData sheetId="552" refreshError="1"/>
-      <sheetData sheetId="553" refreshError="1"/>
-      <sheetData sheetId="554" refreshError="1"/>
-      <sheetData sheetId="555" refreshError="1"/>
-      <sheetData sheetId="556" refreshError="1"/>
-      <sheetData sheetId="557" refreshError="1"/>
-      <sheetData sheetId="558" refreshError="1"/>
-      <sheetData sheetId="559" refreshError="1"/>
-      <sheetData sheetId="560" refreshError="1"/>
-      <sheetData sheetId="561" refreshError="1"/>
-      <sheetData sheetId="562" refreshError="1"/>
-      <sheetData sheetId="563" refreshError="1"/>
-      <sheetData sheetId="564" refreshError="1"/>
-      <sheetData sheetId="565" refreshError="1"/>
-      <sheetData sheetId="566" refreshError="1"/>
-      <sheetData sheetId="567" refreshError="1"/>
-      <sheetData sheetId="568" refreshError="1"/>
-      <sheetData sheetId="569" refreshError="1"/>
-      <sheetData sheetId="570" refreshError="1"/>
-      <sheetData sheetId="571" refreshError="1"/>
-      <sheetData sheetId="572" refreshError="1"/>
-      <sheetData sheetId="573" refreshError="1"/>
-      <sheetData sheetId="574" refreshError="1"/>
-      <sheetData sheetId="575" refreshError="1"/>
-      <sheetData sheetId="576" refreshError="1"/>
-      <sheetData sheetId="577" refreshError="1"/>
-      <sheetData sheetId="578" refreshError="1"/>
-      <sheetData sheetId="579" refreshError="1"/>
-      <sheetData sheetId="580" refreshError="1"/>
-      <sheetData sheetId="581" refreshError="1"/>
-      <sheetData sheetId="582" refreshError="1"/>
-      <sheetData sheetId="583" refreshError="1"/>
-      <sheetData sheetId="584" refreshError="1"/>
-      <sheetData sheetId="585" refreshError="1"/>
-      <sheetData sheetId="586" refreshError="1"/>
-      <sheetData sheetId="587" refreshError="1"/>
-      <sheetData sheetId="588" refreshError="1"/>
-      <sheetData sheetId="589" refreshError="1"/>
-      <sheetData sheetId="590" refreshError="1"/>
-      <sheetData sheetId="591" refreshError="1"/>
-      <sheetData sheetId="592" refreshError="1"/>
-      <sheetData sheetId="593" refreshError="1"/>
-      <sheetData sheetId="594" refreshError="1"/>
-      <sheetData sheetId="595" refreshError="1"/>
-      <sheetData sheetId="596" refreshError="1"/>
-      <sheetData sheetId="597" refreshError="1"/>
-      <sheetData sheetId="598" refreshError="1"/>
-      <sheetData sheetId="599" refreshError="1"/>
-      <sheetData sheetId="600" refreshError="1"/>
-      <sheetData sheetId="601" refreshError="1"/>
-      <sheetData sheetId="602" refreshError="1"/>
-      <sheetData sheetId="603" refreshError="1"/>
-      <sheetData sheetId="604" refreshError="1"/>
-      <sheetData sheetId="605" refreshError="1"/>
-      <sheetData sheetId="606" refreshError="1"/>
-      <sheetData sheetId="607" refreshError="1"/>
-      <sheetData sheetId="608" refreshError="1"/>
-      <sheetData sheetId="609" refreshError="1"/>
-      <sheetData sheetId="610" refreshError="1"/>
-      <sheetData sheetId="611" refreshError="1"/>
-      <sheetData sheetId="612" refreshError="1"/>
-      <sheetData sheetId="613" refreshError="1"/>
-      <sheetData sheetId="614" refreshError="1"/>
-      <sheetData sheetId="615" refreshError="1"/>
-      <sheetData sheetId="616" refreshError="1"/>
-      <sheetData sheetId="617" refreshError="1"/>
-      <sheetData sheetId="618" refreshError="1"/>
-      <sheetData sheetId="619" refreshError="1"/>
-      <sheetData sheetId="620" refreshError="1"/>
-      <sheetData sheetId="621" refreshError="1"/>
-      <sheetData sheetId="622" refreshError="1"/>
-      <sheetData sheetId="623" refreshError="1"/>
-      <sheetData sheetId="624" refreshError="1"/>
-      <sheetData sheetId="625" refreshError="1"/>
-      <sheetData sheetId="626" refreshError="1"/>
-      <sheetData sheetId="627" refreshError="1"/>
-      <sheetData sheetId="628" refreshError="1"/>
-      <sheetData sheetId="629" refreshError="1"/>
-      <sheetData sheetId="630" refreshError="1"/>
-      <sheetData sheetId="631" refreshError="1"/>
-      <sheetData sheetId="632" refreshError="1"/>
-      <sheetData sheetId="633" refreshError="1"/>
-      <sheetData sheetId="634" refreshError="1"/>
-      <sheetData sheetId="635" refreshError="1"/>
-      <sheetData sheetId="636" refreshError="1"/>
-      <sheetData sheetId="637" refreshError="1"/>
-      <sheetData sheetId="638" refreshError="1"/>
-      <sheetData sheetId="639" refreshError="1"/>
-      <sheetData sheetId="640" refreshError="1"/>
-      <sheetData sheetId="641" refreshError="1"/>
-      <sheetData sheetId="642" refreshError="1"/>
-      <sheetData sheetId="643" refreshError="1"/>
-      <sheetData sheetId="644" refreshError="1"/>
-      <sheetData sheetId="645" refreshError="1"/>
-      <sheetData sheetId="646" refreshError="1"/>
-      <sheetData sheetId="647" refreshError="1"/>
-      <sheetData sheetId="648" refreshError="1"/>
-      <sheetData sheetId="649" refreshError="1"/>
-      <sheetData sheetId="650" refreshError="1"/>
-      <sheetData sheetId="651" refreshError="1"/>
-      <sheetData sheetId="652" refreshError="1"/>
-      <sheetData sheetId="653" refreshError="1"/>
-      <sheetData sheetId="654" refreshError="1"/>
-      <sheetData sheetId="655" refreshError="1"/>
-      <sheetData sheetId="656" refreshError="1"/>
-      <sheetData sheetId="657" refreshError="1"/>
-      <sheetData sheetId="658" refreshError="1"/>
-      <sheetData sheetId="659" refreshError="1"/>
-      <sheetData sheetId="660" refreshError="1"/>
-      <sheetData sheetId="661" refreshError="1"/>
-      <sheetData sheetId="662" refreshError="1"/>
-      <sheetData sheetId="663" refreshError="1"/>
-      <sheetData sheetId="664" refreshError="1"/>
-      <sheetData sheetId="665" refreshError="1"/>
-      <sheetData sheetId="666" refreshError="1"/>
-      <sheetData sheetId="667" refreshError="1"/>
-      <sheetData sheetId="668" refreshError="1"/>
-      <sheetData sheetId="669" refreshError="1"/>
-      <sheetData sheetId="670" refreshError="1"/>
-      <sheetData sheetId="671" refreshError="1"/>
-      <sheetData sheetId="672" refreshError="1"/>
-      <sheetData sheetId="673" refreshError="1"/>
-      <sheetData sheetId="674" refreshError="1"/>
-      <sheetData sheetId="675" refreshError="1"/>
-      <sheetData sheetId="676" refreshError="1"/>
-      <sheetData sheetId="677" refreshError="1"/>
-      <sheetData sheetId="678" refreshError="1"/>
-      <sheetData sheetId="679" refreshError="1"/>
-      <sheetData sheetId="680" refreshError="1"/>
-      <sheetData sheetId="681" refreshError="1"/>
-      <sheetData sheetId="682" refreshError="1"/>
-      <sheetData sheetId="683" refreshError="1"/>
-      <sheetData sheetId="684" refreshError="1"/>
-      <sheetData sheetId="685" refreshError="1"/>
-      <sheetData sheetId="686" refreshError="1"/>
-      <sheetData sheetId="687" refreshError="1"/>
-      <sheetData sheetId="688" refreshError="1"/>
-      <sheetData sheetId="689" refreshError="1"/>
-      <sheetData sheetId="690" refreshError="1"/>
-      <sheetData sheetId="691" refreshError="1"/>
-      <sheetData sheetId="692" refreshError="1"/>
-      <sheetData sheetId="693" refreshError="1"/>
-      <sheetData sheetId="694" refreshError="1"/>
-      <sheetData sheetId="695" refreshError="1"/>
-      <sheetData sheetId="696" refreshError="1"/>
-      <sheetData sheetId="697" refreshError="1"/>
-      <sheetData sheetId="698" refreshError="1"/>
-      <sheetData sheetId="699" refreshError="1"/>
-      <sheetData sheetId="700" refreshError="1"/>
-      <sheetData sheetId="701" refreshError="1"/>
-      <sheetData sheetId="702" refreshError="1"/>
-      <sheetData sheetId="703" refreshError="1"/>
-      <sheetData sheetId="704" refreshError="1"/>
-      <sheetData sheetId="705" refreshError="1"/>
-      <sheetData sheetId="706" refreshError="1"/>
-      <sheetData sheetId="707" refreshError="1"/>
-      <sheetData sheetId="708" refreshError="1"/>
-      <sheetData sheetId="709" refreshError="1"/>
-      <sheetData sheetId="710" refreshError="1"/>
-      <sheetData sheetId="711" refreshError="1"/>
-      <sheetData sheetId="712" refreshError="1"/>
-      <sheetData sheetId="713" refreshError="1"/>
-      <sheetData sheetId="714" refreshError="1"/>
-      <sheetData sheetId="715" refreshError="1"/>
-      <sheetData sheetId="716" refreshError="1"/>
-      <sheetData sheetId="717" refreshError="1"/>
-      <sheetData sheetId="718" refreshError="1"/>
-      <sheetData sheetId="719" refreshError="1"/>
-      <sheetData sheetId="720" refreshError="1"/>
-      <sheetData sheetId="721" refreshError="1"/>
-      <sheetData sheetId="722" refreshError="1"/>
-      <sheetData sheetId="723" refreshError="1"/>
-      <sheetData sheetId="724" refreshError="1"/>
-      <sheetData sheetId="725" refreshError="1"/>
-      <sheetData sheetId="726" refreshError="1"/>
-      <sheetData sheetId="727" refreshError="1"/>
-      <sheetData sheetId="728" refreshError="1"/>
-      <sheetData sheetId="729" refreshError="1"/>
-      <sheetData sheetId="730" refreshError="1"/>
-      <sheetData sheetId="731" refreshError="1"/>
-      <sheetData sheetId="732" refreshError="1"/>
-      <sheetData sheetId="733" refreshError="1"/>
-      <sheetData sheetId="734" refreshError="1"/>
-      <sheetData sheetId="735" refreshError="1"/>
-      <sheetData sheetId="736" refreshError="1"/>
-      <sheetData sheetId="737" refreshError="1"/>
-      <sheetData sheetId="738" refreshError="1"/>
-      <sheetData sheetId="739" refreshError="1"/>
-      <sheetData sheetId="740" refreshError="1"/>
-      <sheetData sheetId="741" refreshError="1"/>
-      <sheetData sheetId="742" refreshError="1"/>
-      <sheetData sheetId="743" refreshError="1"/>
-      <sheetData sheetId="744" refreshError="1"/>
-      <sheetData sheetId="745" refreshError="1"/>
-      <sheetData sheetId="746" refreshError="1"/>
-      <sheetData sheetId="747" refreshError="1"/>
-      <sheetData sheetId="748" refreshError="1"/>
-      <sheetData sheetId="749" refreshError="1"/>
-      <sheetData sheetId="750" refreshError="1"/>
-      <sheetData sheetId="751" refreshError="1"/>
-      <sheetData sheetId="752" refreshError="1"/>
-      <sheetData sheetId="753" refreshError="1"/>
-      <sheetData sheetId="754" refreshError="1"/>
-      <sheetData sheetId="755" refreshError="1"/>
-      <sheetData sheetId="756" refreshError="1"/>
-      <sheetData sheetId="757" refreshError="1"/>
-      <sheetData sheetId="758" refreshError="1"/>
-      <sheetData sheetId="759" refreshError="1"/>
-      <sheetData sheetId="760" refreshError="1"/>
-      <sheetData sheetId="761" refreshError="1"/>
-      <sheetData sheetId="762" refreshError="1"/>
-      <sheetData sheetId="763" refreshError="1"/>
-      <sheetData sheetId="764" refreshError="1"/>
-      <sheetData sheetId="765" refreshError="1"/>
-      <sheetData sheetId="766" refreshError="1"/>
-      <sheetData sheetId="767" refreshError="1"/>
-      <sheetData sheetId="768" refreshError="1"/>
-      <sheetData sheetId="769" refreshError="1"/>
-      <sheetData sheetId="770" refreshError="1"/>
-      <sheetData sheetId="771" refreshError="1"/>
-      <sheetData sheetId="772" refreshError="1"/>
-      <sheetData sheetId="773" refreshError="1"/>
-      <sheetData sheetId="774" refreshError="1"/>
-      <sheetData sheetId="775" refreshError="1"/>
-      <sheetData sheetId="776" refreshError="1"/>
-      <sheetData sheetId="777" refreshError="1"/>
-      <sheetData sheetId="778" refreshError="1"/>
-      <sheetData sheetId="779" refreshError="1"/>
-      <sheetData sheetId="780" refreshError="1"/>
-      <sheetData sheetId="781" refreshError="1"/>
-      <sheetData sheetId="782" refreshError="1"/>
-      <sheetData sheetId="783" refreshError="1"/>
-      <sheetData sheetId="784" refreshError="1"/>
-      <sheetData sheetId="785" refreshError="1"/>
-      <sheetData sheetId="786" refreshError="1"/>
-      <sheetData sheetId="787" refreshError="1"/>
-      <sheetData sheetId="788" refreshError="1"/>
-      <sheetData sheetId="789" refreshError="1"/>
-      <sheetData sheetId="790" refreshError="1"/>
-      <sheetData sheetId="791" refreshError="1"/>
-      <sheetData sheetId="792" refreshError="1"/>
-      <sheetData sheetId="793" refreshError="1"/>
-      <sheetData sheetId="794" refreshError="1"/>
-      <sheetData sheetId="795" refreshError="1"/>
-      <sheetData sheetId="796" refreshError="1"/>
-      <sheetData sheetId="797" refreshError="1"/>
-      <sheetData sheetId="798" refreshError="1"/>
-      <sheetData sheetId="799" refreshError="1"/>
-      <sheetData sheetId="800" refreshError="1"/>
-      <sheetData sheetId="801" refreshError="1"/>
-      <sheetData sheetId="802" refreshError="1"/>
-      <sheetData sheetId="803" refreshError="1"/>
-      <sheetData sheetId="804" refreshError="1"/>
-      <sheetData sheetId="805" refreshError="1"/>
-      <sheetData sheetId="806" refreshError="1"/>
-      <sheetData sheetId="807" refreshError="1"/>
-      <sheetData sheetId="808" refreshError="1"/>
-      <sheetData sheetId="809" refreshError="1"/>
-      <sheetData sheetId="810" refreshError="1"/>
-      <sheetData sheetId="811" refreshError="1"/>
-      <sheetData sheetId="812" refreshError="1"/>
-      <sheetData sheetId="813" refreshError="1"/>
-      <sheetData sheetId="814" refreshError="1"/>
-      <sheetData sheetId="815" refreshError="1"/>
-      <sheetData sheetId="816" refreshError="1"/>
-      <sheetData sheetId="817" refreshError="1"/>
-      <sheetData sheetId="818" refreshError="1"/>
-      <sheetData sheetId="819" refreshError="1"/>
-      <sheetData sheetId="820" refreshError="1"/>
-      <sheetData sheetId="821" refreshError="1"/>
-      <sheetData sheetId="822" refreshError="1"/>
-      <sheetData sheetId="823" refreshError="1"/>
-      <sheetData sheetId="824" refreshError="1"/>
-      <sheetData sheetId="825" refreshError="1"/>
-      <sheetData sheetId="826" refreshError="1"/>
-      <sheetData sheetId="827" refreshError="1"/>
-      <sheetData sheetId="828" refreshError="1"/>
-      <sheetData sheetId="829" refreshError="1"/>
-      <sheetData sheetId="830" refreshError="1"/>
-      <sheetData sheetId="831" refreshError="1"/>
-      <sheetData sheetId="832" refreshError="1"/>
-      <sheetData sheetId="833" refreshError="1"/>
-      <sheetData sheetId="834" refreshError="1"/>
-      <sheetData sheetId="835" refreshError="1"/>
-      <sheetData sheetId="836" refreshError="1"/>
-      <sheetData sheetId="837" refreshError="1"/>
-      <sheetData sheetId="838" refreshError="1"/>
-      <sheetData sheetId="839" refreshError="1"/>
-      <sheetData sheetId="840" refreshError="1"/>
-      <sheetData sheetId="841" refreshError="1"/>
-      <sheetData sheetId="842" refreshError="1"/>
-      <sheetData sheetId="843" refreshError="1"/>
-      <sheetData sheetId="844" refreshError="1"/>
-      <sheetData sheetId="845" refreshError="1"/>
-      <sheetData sheetId="846" refreshError="1"/>
-      <sheetData sheetId="847" refreshError="1"/>
-      <sheetData sheetId="848" refreshError="1"/>
-      <sheetData sheetId="849" refreshError="1"/>
-      <sheetData sheetId="850" refreshError="1"/>
-      <sheetData sheetId="851" refreshError="1"/>
-      <sheetData sheetId="852" refreshError="1"/>
-      <sheetData sheetId="853" refreshError="1"/>
-      <sheetData sheetId="854" refreshError="1"/>
-      <sheetData sheetId="855" refreshError="1"/>
-      <sheetData sheetId="856" refreshError="1"/>
-      <sheetData sheetId="857" refreshError="1"/>
-      <sheetData sheetId="858" refreshError="1"/>
-      <sheetData sheetId="859" refreshError="1"/>
-      <sheetData sheetId="860" refreshError="1"/>
-      <sheetData sheetId="861" refreshError="1"/>
-      <sheetData sheetId="862" refreshError="1"/>
-      <sheetData sheetId="863" refreshError="1"/>
-      <sheetData sheetId="864" refreshError="1"/>
-      <sheetData sheetId="865" refreshError="1"/>
-      <sheetData sheetId="866" refreshError="1"/>
-      <sheetData sheetId="867" refreshError="1"/>
-      <sheetData sheetId="868" refreshError="1"/>
-      <sheetData sheetId="869" refreshError="1"/>
-      <sheetData sheetId="870" refreshError="1"/>
-      <sheetData sheetId="871" refreshError="1"/>
-      <sheetData sheetId="872" refreshError="1"/>
-      <sheetData sheetId="873" refreshError="1"/>
-      <sheetData sheetId="874" refreshError="1"/>
-      <sheetData sheetId="875" refreshError="1"/>
-      <sheetData sheetId="876" refreshError="1"/>
-      <sheetData sheetId="877" refreshError="1"/>
-      <sheetData sheetId="878" refreshError="1"/>
-      <sheetData sheetId="879" refreshError="1"/>
-      <sheetData sheetId="880" refreshError="1"/>
-      <sheetData sheetId="881" refreshError="1"/>
-      <sheetData sheetId="882" refreshError="1"/>
-      <sheetData sheetId="883" refreshError="1"/>
-      <sheetData sheetId="884" refreshError="1"/>
-      <sheetData sheetId="885" refreshError="1"/>
-      <sheetData sheetId="886" refreshError="1"/>
-      <sheetData sheetId="887" refreshError="1"/>
-      <sheetData sheetId="888" refreshError="1"/>
-      <sheetData sheetId="889" refreshError="1"/>
-      <sheetData sheetId="890" refreshError="1"/>
-      <sheetData sheetId="891" refreshError="1"/>
-      <sheetData sheetId="892" refreshError="1"/>
-      <sheetData sheetId="893" refreshError="1"/>
-      <sheetData sheetId="894" refreshError="1"/>
-      <sheetData sheetId="895" refreshError="1"/>
-      <sheetData sheetId="896" refreshError="1"/>
-      <sheetData sheetId="897" refreshError="1"/>
-      <sheetData sheetId="898" refreshError="1"/>
-      <sheetData sheetId="899" refreshError="1"/>
-      <sheetData sheetId="900" refreshError="1"/>
-      <sheetData sheetId="901" refreshError="1"/>
-      <sheetData sheetId="902" refreshError="1"/>
-      <sheetData sheetId="903" refreshError="1"/>
-      <sheetData sheetId="904" refreshError="1"/>
-      <sheetData sheetId="905" refreshError="1"/>
-      <sheetData sheetId="906" refreshError="1"/>
-      <sheetData sheetId="907" refreshError="1"/>
-      <sheetData sheetId="908" refreshError="1"/>
-      <sheetData sheetId="909" refreshError="1"/>
-      <sheetData sheetId="910" refreshError="1"/>
-      <sheetData sheetId="911" refreshError="1"/>
-      <sheetData sheetId="912" refreshError="1"/>
-      <sheetData sheetId="913" refreshError="1"/>
-      <sheetData sheetId="914" refreshError="1"/>
-      <sheetData sheetId="915" refreshError="1"/>
-      <sheetData sheetId="916" refreshError="1"/>
-      <sheetData sheetId="917" refreshError="1"/>
-      <sheetData sheetId="918" refreshError="1"/>
-      <sheetData sheetId="919" refreshError="1"/>
-      <sheetData sheetId="920" refreshError="1"/>
-      <sheetData sheetId="921" refreshError="1"/>
-      <sheetData sheetId="922" refreshError="1"/>
-      <sheetData sheetId="923" refreshError="1"/>
-      <sheetData sheetId="924" refreshError="1"/>
-      <sheetData sheetId="925" refreshError="1"/>
-      <sheetData sheetId="926" refreshError="1"/>
-      <sheetData sheetId="927" refreshError="1"/>
-      <sheetData sheetId="928" refreshError="1"/>
-      <sheetData sheetId="929" refreshError="1"/>
-      <sheetData sheetId="930" refreshError="1"/>
-      <sheetData sheetId="931" refreshError="1"/>
-      <sheetData sheetId="932" refreshError="1"/>
-      <sheetData sheetId="933" refreshError="1"/>
-      <sheetData sheetId="934" refreshError="1"/>
-      <sheetData sheetId="935" refreshError="1"/>
-      <sheetData sheetId="936" refreshError="1"/>
-      <sheetData sheetId="937" refreshError="1"/>
-      <sheetData sheetId="938" refreshError="1"/>
-      <sheetData sheetId="939" refreshError="1"/>
-      <sheetData sheetId="940" refreshError="1"/>
-      <sheetData sheetId="941" refreshError="1"/>
-      <sheetData sheetId="942" refreshError="1"/>
-      <sheetData sheetId="943" refreshError="1"/>
-      <sheetData sheetId="944" refreshError="1"/>
-      <sheetData sheetId="945" refreshError="1"/>
-      <sheetData sheetId="946" refreshError="1"/>
-      <sheetData sheetId="947" refreshError="1"/>
-      <sheetData sheetId="948" refreshError="1"/>
-      <sheetData sheetId="949" refreshError="1"/>
-      <sheetData sheetId="950" refreshError="1"/>
-      <sheetData sheetId="951" refreshError="1"/>
-      <sheetData sheetId="952" refreshError="1"/>
-      <sheetData sheetId="953" refreshError="1"/>
-      <sheetData sheetId="954" refreshError="1"/>
-      <sheetData sheetId="955" refreshError="1"/>
-      <sheetData sheetId="956" refreshError="1"/>
-      <sheetData sheetId="957" refreshError="1"/>
-      <sheetData sheetId="958" refreshError="1"/>
-      <sheetData sheetId="959" refreshError="1"/>
-      <sheetData sheetId="960" refreshError="1"/>
-      <sheetData sheetId="961" refreshError="1"/>
-      <sheetData sheetId="962" refreshError="1"/>
-      <sheetData sheetId="963" refreshError="1"/>
-      <sheetData sheetId="964" refreshError="1"/>
-      <sheetData sheetId="965" refreshError="1"/>
-      <sheetData sheetId="966" refreshError="1"/>
-      <sheetData sheetId="967" refreshError="1"/>
-      <sheetData sheetId="968" refreshError="1"/>
-      <sheetData sheetId="969" refreshError="1"/>
-      <sheetData sheetId="970" refreshError="1"/>
-      <sheetData sheetId="971" refreshError="1"/>
-      <sheetData sheetId="972" refreshError="1"/>
-      <sheetData sheetId="973" refreshError="1"/>
-      <sheetData sheetId="974" refreshError="1"/>
-      <sheetData sheetId="975" refreshError="1"/>
-      <sheetData sheetId="976" refreshError="1"/>
-      <sheetData sheetId="977" refreshError="1"/>
-      <sheetData sheetId="978" refreshError="1"/>
-      <sheetData sheetId="979" refreshError="1"/>
-      <sheetData sheetId="980" refreshError="1"/>
-      <sheetData sheetId="981" refreshError="1"/>
-      <sheetData sheetId="982" refreshError="1"/>
-      <sheetData sheetId="983" refreshError="1"/>
-      <sheetData sheetId="984" refreshError="1"/>
-      <sheetData sheetId="985" refreshError="1"/>
-      <sheetData sheetId="986" refreshError="1"/>
-      <sheetData sheetId="987" refreshError="1"/>
-      <sheetData sheetId="988" refreshError="1"/>
-      <sheetData sheetId="989" refreshError="1"/>
-      <sheetData sheetId="990" refreshError="1"/>
-      <sheetData sheetId="991" refreshError="1"/>
-      <sheetData sheetId="992" refreshError="1"/>
-      <sheetData sheetId="993" refreshError="1"/>
-      <sheetData sheetId="994" refreshError="1"/>
-      <sheetData sheetId="995" refreshError="1"/>
-      <sheetData sheetId="996" refreshError="1"/>
-      <sheetData sheetId="997" refreshError="1"/>
-      <sheetData sheetId="998" refreshError="1"/>
-      <sheetData sheetId="999" refreshError="1"/>
-      <sheetData sheetId="1000" refreshError="1"/>
-      <sheetData sheetId="1001" refreshError="1"/>
-      <sheetData sheetId="1002" refreshError="1"/>
-      <sheetData sheetId="1003" refreshError="1"/>
-      <sheetData sheetId="1004" refreshError="1"/>
-      <sheetData sheetId="1005" refreshError="1"/>
-      <sheetData sheetId="1006" refreshError="1"/>
-      <sheetData sheetId="1007" refreshError="1"/>
-      <sheetData sheetId="1008" refreshError="1"/>
-      <sheetData sheetId="1009" refreshError="1"/>
-      <sheetData sheetId="1010" refreshError="1"/>
-      <sheetData sheetId="1011" refreshError="1"/>
-      <sheetData sheetId="1012" refreshError="1"/>
-      <sheetData sheetId="1013" refreshError="1"/>
-      <sheetData sheetId="1014" refreshError="1"/>
-      <sheetData sheetId="1015" refreshError="1"/>
-      <sheetData sheetId="1016" refreshError="1"/>
-      <sheetData sheetId="1017" refreshError="1"/>
-      <sheetData sheetId="1018" refreshError="1"/>
-      <sheetData sheetId="1019" refreshError="1"/>
-      <sheetData sheetId="1020" refreshError="1"/>
-      <sheetData sheetId="1021" refreshError="1"/>
-      <sheetData sheetId="1022" refreshError="1"/>
-      <sheetData sheetId="1023" refreshError="1"/>
-      <sheetData sheetId="1024" refreshError="1"/>
-      <sheetData sheetId="1025" refreshError="1"/>
-      <sheetData sheetId="1026" refreshError="1"/>
-      <sheetData sheetId="1027" refreshError="1"/>
-      <sheetData sheetId="1028" refreshError="1"/>
-      <sheetData sheetId="1029" refreshError="1"/>
-      <sheetData sheetId="1030" refreshError="1"/>
-      <sheetData sheetId="1031" refreshError="1"/>
-      <sheetData sheetId="1032" refreshError="1"/>
-      <sheetData sheetId="1033" refreshError="1"/>
-      <sheetData sheetId="1034" refreshError="1"/>
-      <sheetData sheetId="1035" refreshError="1"/>
-      <sheetData sheetId="1036" refreshError="1"/>
-      <sheetData sheetId="1037" refreshError="1"/>
-      <sheetData sheetId="1038" refreshError="1"/>
-      <sheetData sheetId="1039" refreshError="1"/>
-      <sheetData sheetId="1040" refreshError="1"/>
-      <sheetData sheetId="1041"/>
-      <sheetData sheetId="1042" refreshError="1"/>
-      <sheetData sheetId="1043" refreshError="1"/>
-      <sheetData sheetId="1044" refreshError="1"/>
-      <sheetData sheetId="1045" refreshError="1"/>
-      <sheetData sheetId="1046" refreshError="1"/>
-      <sheetData sheetId="1047" refreshError="1"/>
-      <sheetData sheetId="1048" refreshError="1"/>
-      <sheetData sheetId="1049" refreshError="1"/>
-      <sheetData sheetId="1050" refreshError="1"/>
-      <sheetData sheetId="1051" refreshError="1"/>
-      <sheetData sheetId="1052" refreshError="1"/>
-      <sheetData sheetId="1053" refreshError="1"/>
-      <sheetData sheetId="1054" refreshError="1"/>
-      <sheetData sheetId="1055" refreshError="1"/>
-      <sheetData sheetId="1056" refreshError="1"/>
-      <sheetData sheetId="1057" refreshError="1"/>
-      <sheetData sheetId="1058" refreshError="1"/>
-      <sheetData sheetId="1059" refreshError="1"/>
-      <sheetData sheetId="1060" refreshError="1"/>
-      <sheetData sheetId="1061" refreshError="1"/>
-      <sheetData sheetId="1062" refreshError="1"/>
-      <sheetData sheetId="1063" refreshError="1"/>
-      <sheetData sheetId="1064" refreshError="1"/>
-      <sheetData sheetId="1065" refreshError="1"/>
-      <sheetData sheetId="1066" refreshError="1"/>
-      <sheetData sheetId="1067" refreshError="1"/>
-      <sheetData sheetId="1068" refreshError="1"/>
-      <sheetData sheetId="1069" refreshError="1"/>
-      <sheetData sheetId="1070" refreshError="1"/>
-      <sheetData sheetId="1071" refreshError="1"/>
-      <sheetData sheetId="1072" refreshError="1"/>
-      <sheetData sheetId="1073" refreshError="1"/>
-      <sheetData sheetId="1074" refreshError="1"/>
-      <sheetData sheetId="1075" refreshError="1"/>
-      <sheetData sheetId="1076" refreshError="1"/>
-      <sheetData sheetId="1077" refreshError="1"/>
-      <sheetData sheetId="1078" refreshError="1"/>
-      <sheetData sheetId="1079" refreshError="1"/>
-      <sheetData sheetId="1080" refreshError="1"/>
-      <sheetData sheetId="1081" refreshError="1"/>
-      <sheetData sheetId="1082" refreshError="1"/>
-      <sheetData sheetId="1083" refreshError="1"/>
-      <sheetData sheetId="1084" refreshError="1"/>
-      <sheetData sheetId="1085" refreshError="1"/>
-      <sheetData sheetId="1086" refreshError="1"/>
-      <sheetData sheetId="1087" refreshError="1"/>
-      <sheetData sheetId="1088" refreshError="1"/>
-      <sheetData sheetId="1089" refreshError="1"/>
-      <sheetData sheetId="1090" refreshError="1"/>
-      <sheetData sheetId="1091" refreshError="1"/>
-      <sheetData sheetId="1092" refreshError="1"/>
-      <sheetData sheetId="1093" refreshError="1"/>
-      <sheetData sheetId="1094" refreshError="1"/>
-      <sheetData sheetId="1095" refreshError="1"/>
-      <sheetData sheetId="1096" refreshError="1"/>
-      <sheetData sheetId="1097" refreshError="1"/>
-      <sheetData sheetId="1098" refreshError="1"/>
-      <sheetData sheetId="1099" refreshError="1"/>
-      <sheetData sheetId="1100" refreshError="1"/>
-      <sheetData sheetId="1101" refreshError="1"/>
-      <sheetData sheetId="1102" refreshError="1"/>
-      <sheetData sheetId="1103" refreshError="1"/>
-      <sheetData sheetId="1104" refreshError="1"/>
-      <sheetData sheetId="1105" refreshError="1"/>
-      <sheetData sheetId="1106" refreshError="1"/>
-      <sheetData sheetId="1107" refreshError="1"/>
-      <sheetData sheetId="1108" refreshError="1"/>
-      <sheetData sheetId="1109" refreshError="1"/>
-      <sheetData sheetId="1110" refreshError="1"/>
-      <sheetData sheetId="1111" refreshError="1"/>
-      <sheetData sheetId="1112" refreshError="1"/>
-      <sheetData sheetId="1113" refreshError="1"/>
-      <sheetData sheetId="1114" refreshError="1"/>
-      <sheetData sheetId="1115" refreshError="1"/>
-      <sheetData sheetId="1116" refreshError="1"/>
-      <sheetData sheetId="1117" refreshError="1"/>
-      <sheetData sheetId="1118" refreshError="1"/>
-      <sheetData sheetId="1119" refreshError="1"/>
-      <sheetData sheetId="1120" refreshError="1"/>
-      <sheetData sheetId="1121" refreshError="1"/>
-      <sheetData sheetId="1122" refreshError="1"/>
-      <sheetData sheetId="1123" refreshError="1"/>
-      <sheetData sheetId="1124" refreshError="1"/>
-      <sheetData sheetId="1125" refreshError="1"/>
-      <sheetData sheetId="1126" refreshError="1"/>
-      <sheetData sheetId="1127" refreshError="1"/>
-      <sheetData sheetId="1128" refreshError="1"/>
-      <sheetData sheetId="1129" refreshError="1"/>
-      <sheetData sheetId="1130" refreshError="1"/>
-      <sheetData sheetId="1131" refreshError="1"/>
-      <sheetData sheetId="1132" refreshError="1"/>
-      <sheetData sheetId="1133" refreshError="1"/>
-      <sheetData sheetId="1134" refreshError="1"/>
-      <sheetData sheetId="1135" refreshError="1"/>
-      <sheetData sheetId="1136" refreshError="1"/>
-      <sheetData sheetId="1137" refreshError="1"/>
-      <sheetData sheetId="1138" refreshError="1"/>
-      <sheetData sheetId="1139" refreshError="1"/>
-      <sheetData sheetId="1140" refreshError="1"/>
-      <sheetData sheetId="1141" refreshError="1"/>
-      <sheetData sheetId="1142" refreshError="1"/>
-      <sheetData sheetId="1143" refreshError="1"/>
-      <sheetData sheetId="1144" refreshError="1"/>
-      <sheetData sheetId="1145" refreshError="1"/>
-      <sheetData sheetId="1146" refreshError="1"/>
-      <sheetData sheetId="1147" refreshError="1"/>
-      <sheetData sheetId="1148" refreshError="1"/>
-      <sheetData sheetId="1149" refreshError="1"/>
-      <sheetData sheetId="1150" refreshError="1"/>
-      <sheetData sheetId="1151" refreshError="1"/>
-      <sheetData sheetId="1152" refreshError="1"/>
-      <sheetData sheetId="1153" refreshError="1"/>
-      <sheetData sheetId="1154" refreshError="1"/>
-      <sheetData sheetId="1155" refreshError="1"/>
-      <sheetData sheetId="1156" refreshError="1"/>
-      <sheetData sheetId="1157" refreshError="1"/>
-      <sheetData sheetId="1158" refreshError="1"/>
-      <sheetData sheetId="1159" refreshError="1"/>
-      <sheetData sheetId="1160" refreshError="1"/>
-      <sheetData sheetId="1161" refreshError="1"/>
-      <sheetData sheetId="1162" refreshError="1"/>
-      <sheetData sheetId="1163" refreshError="1"/>
-      <sheetData sheetId="1164" refreshError="1"/>
-      <sheetData sheetId="1165" refreshError="1"/>
-      <sheetData sheetId="1166" refreshError="1"/>
-      <sheetData sheetId="1167" refreshError="1"/>
-      <sheetData sheetId="1168" refreshError="1"/>
-      <sheetData sheetId="1169" refreshError="1"/>
-      <sheetData sheetId="1170" refreshError="1"/>
-      <sheetData sheetId="1171" refreshError="1"/>
-      <sheetData sheetId="1172" refreshError="1"/>
-      <sheetData sheetId="1173" refreshError="1"/>
-      <sheetData sheetId="1174" refreshError="1"/>
-      <sheetData sheetId="1175" refreshError="1"/>
-      <sheetData sheetId="1176" refreshError="1"/>
-      <sheetData sheetId="1177" refreshError="1"/>
-      <sheetData sheetId="1178" refreshError="1"/>
-      <sheetData sheetId="1179" refreshError="1"/>
-      <sheetData sheetId="1180" refreshError="1"/>
-      <sheetData sheetId="1181" refreshError="1"/>
-      <sheetData sheetId="1182" refreshError="1"/>
-      <sheetData sheetId="1183" refreshError="1"/>
-      <sheetData sheetId="1184" refreshError="1"/>
-      <sheetData sheetId="1185" refreshError="1"/>
-      <sheetData sheetId="1186" refreshError="1"/>
-      <sheetData sheetId="1187" refreshError="1"/>
-      <sheetData sheetId="1188" refreshError="1"/>
-      <sheetData sheetId="1189" refreshError="1"/>
-      <sheetData sheetId="1190" refreshError="1"/>
-      <sheetData sheetId="1191" refreshError="1"/>
-      <sheetData sheetId="1192" refreshError="1"/>
-      <sheetData sheetId="1193" refreshError="1"/>
-      <sheetData sheetId="1194" refreshError="1"/>
-      <sheetData sheetId="1195" refreshError="1"/>
-      <sheetData sheetId="1196" refreshError="1"/>
-      <sheetData sheetId="1197" refreshError="1"/>
-      <sheetData sheetId="1198" refreshError="1"/>
-      <sheetData sheetId="1199" refreshError="1"/>
-      <sheetData sheetId="1200" refreshError="1"/>
-      <sheetData sheetId="1201" refreshError="1"/>
-      <sheetData sheetId="1202" refreshError="1"/>
-      <sheetData sheetId="1203" refreshError="1"/>
-      <sheetData sheetId="1204" refreshError="1"/>
-      <sheetData sheetId="1205" refreshError="1"/>
-      <sheetData sheetId="1206" refreshError="1"/>
-      <sheetData sheetId="1207" refreshError="1"/>
-      <sheetData sheetId="1208" refreshError="1"/>
-      <sheetData sheetId="1209" refreshError="1"/>
-      <sheetData sheetId="1210" refreshError="1"/>
-      <sheetData sheetId="1211" refreshError="1"/>
-      <sheetData sheetId="1212" refreshError="1"/>
-      <sheetData sheetId="1213" refreshError="1"/>
-      <sheetData sheetId="1214" refreshError="1"/>
-      <sheetData sheetId="1215" refreshError="1"/>
-      <sheetData sheetId="1216" refreshError="1"/>
-      <sheetData sheetId="1217" refreshError="1"/>
-      <sheetData sheetId="1218" refreshError="1"/>
-      <sheetData sheetId="1219" refreshError="1"/>
-      <sheetData sheetId="1220" refreshError="1"/>
-      <sheetData sheetId="1221" refreshError="1"/>
-      <sheetData sheetId="1222" refreshError="1"/>
-      <sheetData sheetId="1223" refreshError="1"/>
-      <sheetData sheetId="1224" refreshError="1"/>
-      <sheetData sheetId="1225" refreshError="1"/>
-      <sheetData sheetId="1226" refreshError="1"/>
-      <sheetData sheetId="1227" refreshError="1"/>
-      <sheetData sheetId="1228" refreshError="1"/>
-      <sheetData sheetId="1229" refreshError="1"/>
-      <sheetData sheetId="1230" refreshError="1"/>
-      <sheetData sheetId="1231" refreshError="1"/>
-      <sheetData sheetId="1232" refreshError="1"/>
-      <sheetData sheetId="1233" refreshError="1"/>
-      <sheetData sheetId="1234" refreshError="1"/>
-      <sheetData sheetId="1235" refreshError="1"/>
-      <sheetData sheetId="1236" refreshError="1"/>
-      <sheetData sheetId="1237" refreshError="1"/>
-      <sheetData sheetId="1238" refreshError="1"/>
-      <sheetData sheetId="1239" refreshError="1"/>
-      <sheetData sheetId="1240" refreshError="1"/>
-      <sheetData sheetId="1241" refreshError="1"/>
-      <sheetData sheetId="1242" refreshError="1"/>
-      <sheetData sheetId="1243" refreshError="1"/>
-      <sheetData sheetId="1244" refreshError="1"/>
-      <sheetData sheetId="1245" refreshError="1"/>
-      <sheetData sheetId="1246" refreshError="1"/>
-      <sheetData sheetId="1247" refreshError="1"/>
-      <sheetData sheetId="1248" refreshError="1"/>
-      <sheetData sheetId="1249" refreshError="1"/>
-      <sheetData sheetId="1250" refreshError="1"/>
-      <sheetData sheetId="1251" refreshError="1"/>
-      <sheetData sheetId="1252" refreshError="1"/>
-      <sheetData sheetId="1253" refreshError="1"/>
-      <sheetData sheetId="1254" refreshError="1"/>
-      <sheetData sheetId="1255" refreshError="1"/>
-      <sheetData sheetId="1256" refreshError="1"/>
-      <sheetData sheetId="1257" refreshError="1"/>
-      <sheetData sheetId="1258" refreshError="1"/>
-      <sheetData sheetId="1259" refreshError="1"/>
-      <sheetData sheetId="1260" refreshError="1"/>
-      <sheetData sheetId="1261" refreshError="1"/>
-      <sheetData sheetId="1262"/>
-      <sheetData sheetId="1263" refreshError="1"/>
-      <sheetData sheetId="1264" refreshError="1"/>
-      <sheetData sheetId="1265" refreshError="1"/>
-      <sheetData sheetId="1266" refreshError="1"/>
-      <sheetData sheetId="1267" refreshError="1"/>
-      <sheetData sheetId="1268" refreshError="1"/>
-      <sheetData sheetId="1269" refreshError="1"/>
-      <sheetData sheetId="1270" refreshError="1"/>
-      <sheetData sheetId="1271" refreshError="1"/>
-      <sheetData sheetId="1272" refreshError="1"/>
-      <sheetData sheetId="1273" refreshError="1"/>
-      <sheetData sheetId="1274" refreshError="1"/>
-      <sheetData sheetId="1275" refreshError="1"/>
-      <sheetData sheetId="1276" refreshError="1"/>
-      <sheetData sheetId="1277" refreshError="1"/>
-      <sheetData sheetId="1278" refreshError="1"/>
-      <sheetData sheetId="1279" refreshError="1"/>
-      <sheetData sheetId="1280" refreshError="1"/>
-      <sheetData sheetId="1281" refreshError="1"/>
-      <sheetData sheetId="1282" refreshError="1"/>
-      <sheetData sheetId="1283" refreshError="1"/>
-      <sheetData sheetId="1284" refreshError="1"/>
-      <sheetData sheetId="1285" refreshError="1"/>
-      <sheetData sheetId="1286" refreshError="1"/>
-      <sheetData sheetId="1287" refreshError="1"/>
-      <sheetData sheetId="1288" refreshError="1"/>
-      <sheetData sheetId="1289" refreshError="1"/>
-      <sheetData sheetId="1290" refreshError="1"/>
-      <sheetData sheetId="1291" refreshError="1"/>
-      <sheetData sheetId="1292" refreshError="1"/>
-      <sheetData sheetId="1293" refreshError="1"/>
-      <sheetData sheetId="1294" refreshError="1"/>
-      <sheetData sheetId="1295" refreshError="1"/>
-      <sheetData sheetId="1296" refreshError="1"/>
-      <sheetData sheetId="1297" refreshError="1"/>
-      <sheetData sheetId="1298" refreshError="1"/>
-      <sheetData sheetId="1299" refreshError="1"/>
-      <sheetData sheetId="1300" refreshError="1"/>
-      <sheetData sheetId="1301" refreshError="1"/>
-      <sheetData sheetId="1302" refreshError="1"/>
-      <sheetData sheetId="1303" refreshError="1"/>
-      <sheetData sheetId="1304" refreshError="1"/>
-      <sheetData sheetId="1305" refreshError="1"/>
-      <sheetData sheetId="1306" refreshError="1"/>
-      <sheetData sheetId="1307" refreshError="1"/>
-      <sheetData sheetId="1308" refreshError="1"/>
-      <sheetData sheetId="1309" refreshError="1"/>
-      <sheetData sheetId="1310" refreshError="1"/>
-      <sheetData sheetId="1311" refreshError="1"/>
-      <sheetData sheetId="1312" refreshError="1"/>
-      <sheetData sheetId="1313" refreshError="1"/>
-      <sheetData sheetId="1314" refreshError="1"/>
-      <sheetData sheetId="1315" refreshError="1"/>
-      <sheetData sheetId="1316" refreshError="1"/>
-      <sheetData sheetId="1317" refreshError="1"/>
-      <sheetData sheetId="1318" refreshError="1"/>
-      <sheetData sheetId="1319" refreshError="1"/>
-      <sheetData sheetId="1320" refreshError="1"/>
-      <sheetData sheetId="1321" refreshError="1"/>
-      <sheetData sheetId="1322" refreshError="1"/>
-      <sheetData sheetId="1323" refreshError="1"/>
-      <sheetData sheetId="1324" refreshError="1"/>
-      <sheetData sheetId="1325" refreshError="1"/>
-      <sheetData sheetId="1326" refreshError="1"/>
-      <sheetData sheetId="1327" refreshError="1"/>
-      <sheetData sheetId="1328" refreshError="1"/>
-      <sheetData sheetId="1329" refreshError="1"/>
-      <sheetData sheetId="1330" refreshError="1"/>
-      <sheetData sheetId="1331" refreshError="1"/>
-      <sheetData sheetId="1332" refreshError="1"/>
-      <sheetData sheetId="1333" refreshError="1"/>
-      <sheetData sheetId="1334" refreshError="1"/>
-      <sheetData sheetId="1335" refreshError="1"/>
-      <sheetData sheetId="1336" refreshError="1"/>
-      <sheetData sheetId="1337" refreshError="1"/>
-      <sheetData sheetId="1338" refreshError="1"/>
-      <sheetData sheetId="1339" refreshError="1"/>
-      <sheetData sheetId="1340" refreshError="1"/>
-      <sheetData sheetId="1341" refreshError="1"/>
-      <sheetData sheetId="1342" refreshError="1"/>
-      <sheetData sheetId="1343" refreshError="1"/>
-      <sheetData sheetId="1344" refreshError="1"/>
-      <sheetData sheetId="1345" refreshError="1"/>
-      <sheetData sheetId="1346" refreshError="1"/>
-      <sheetData sheetId="1347" refreshError="1"/>
-      <sheetData sheetId="1348" refreshError="1"/>
-      <sheetData sheetId="1349" refreshError="1"/>
-      <sheetData sheetId="1350" refreshError="1"/>
-      <sheetData sheetId="1351" refreshError="1"/>
-      <sheetData sheetId="1352" refreshError="1"/>
-      <sheetData sheetId="1353" refreshError="1"/>
-      <sheetData sheetId="1354" refreshError="1"/>
-      <sheetData sheetId="1355" refreshError="1"/>
-      <sheetData sheetId="1356" refreshError="1"/>
-      <sheetData sheetId="1357" refreshError="1"/>
-      <sheetData sheetId="1358" refreshError="1"/>
-      <sheetData sheetId="1359" refreshError="1"/>
-      <sheetData sheetId="1360" refreshError="1"/>
-      <sheetData sheetId="1361" refreshError="1"/>
-      <sheetData sheetId="1362" refreshError="1"/>
-      <sheetData sheetId="1363" refreshError="1"/>
-      <sheetData sheetId="1364" refreshError="1"/>
-      <sheetData sheetId="1365" refreshError="1"/>
-      <sheetData sheetId="1366" refreshError="1"/>
-      <sheetData sheetId="1367" refreshError="1"/>
-      <sheetData sheetId="1368" refreshError="1"/>
-      <sheetData sheetId="1369" refreshError="1"/>
-      <sheetData sheetId="1370" refreshError="1"/>
-      <sheetData sheetId="1371" refreshError="1"/>
-      <sheetData sheetId="1372" refreshError="1"/>
-      <sheetData sheetId="1373" refreshError="1"/>
-      <sheetData sheetId="1374" refreshError="1"/>
-      <sheetData sheetId="1375" refreshError="1"/>
-      <sheetData sheetId="1376" refreshError="1"/>
-      <sheetData sheetId="1377" refreshError="1"/>
-      <sheetData sheetId="1378" refreshError="1"/>
-      <sheetData sheetId="1379" refreshError="1"/>
-      <sheetData sheetId="1380" refreshError="1"/>
-      <sheetData sheetId="1381" refreshError="1"/>
-      <sheetData sheetId="1382" refreshError="1"/>
-      <sheetData sheetId="1383" refreshError="1"/>
-      <sheetData sheetId="1384" refreshError="1"/>
-      <sheetData sheetId="1385" refreshError="1"/>
-      <sheetData sheetId="1386" refreshError="1"/>
-      <sheetData sheetId="1387" refreshError="1"/>
-      <sheetData sheetId="1388" refreshError="1"/>
-      <sheetData sheetId="1389" refreshError="1"/>
-      <sheetData sheetId="1390" refreshError="1"/>
-      <sheetData sheetId="1391" refreshError="1"/>
-      <sheetData sheetId="1392" refreshError="1"/>
-      <sheetData sheetId="1393" refreshError="1"/>
-      <sheetData sheetId="1394" refreshError="1"/>
-      <sheetData sheetId="1395" refreshError="1"/>
-      <sheetData sheetId="1396" refreshError="1"/>
-      <sheetData sheetId="1397" refreshError="1"/>
-      <sheetData sheetId="1398" refreshError="1"/>
-      <sheetData sheetId="1399" refreshError="1"/>
-      <sheetData sheetId="1400" refreshError="1"/>
-      <sheetData sheetId="1401"/>
-      <sheetData sheetId="1402" refreshError="1"/>
-      <sheetData sheetId="1403" refreshError="1"/>
-      <sheetData sheetId="1404" refreshError="1"/>
-      <sheetData sheetId="1405" refreshError="1"/>
-      <sheetData sheetId="1406" refreshError="1"/>
-      <sheetData sheetId="1407" refreshError="1"/>
-      <sheetData sheetId="1408" refreshError="1"/>
-      <sheetData sheetId="1409" refreshError="1"/>
-      <sheetData sheetId="1410" refreshError="1"/>
-      <sheetData sheetId="1411" refreshError="1"/>
-      <sheetData sheetId="1412" refreshError="1"/>
-      <sheetData sheetId="1413" refreshError="1"/>
-      <sheetData sheetId="1414" refreshError="1"/>
-      <sheetData sheetId="1415" refreshError="1"/>
-      <sheetData sheetId="1416"/>
-      <sheetData sheetId="1417" refreshError="1"/>
-      <sheetData sheetId="1418" refreshError="1"/>
-      <sheetData sheetId="1419" refreshError="1"/>
-      <sheetData sheetId="1420" refreshError="1"/>
-      <sheetData sheetId="1421" refreshError="1"/>
-      <sheetData sheetId="1422" refreshError="1"/>
-      <sheetData sheetId="1423" refreshError="1"/>
-      <sheetData sheetId="1424" refreshError="1"/>
-      <sheetData sheetId="1425" refreshError="1"/>
-      <sheetData sheetId="1426" refreshError="1"/>
-      <sheetData sheetId="1427" refreshError="1"/>
-      <sheetData sheetId="1428" refreshError="1"/>
-      <sheetData sheetId="1429" refreshError="1"/>
-      <sheetData sheetId="1430" refreshError="1"/>
-      <sheetData sheetId="1431" refreshError="1"/>
-      <sheetData sheetId="1432" refreshError="1"/>
-      <sheetData sheetId="1433" refreshError="1"/>
-      <sheetData sheetId="1434" refreshError="1"/>
-      <sheetData sheetId="1435" refreshError="1"/>
-      <sheetData sheetId="1436" refreshError="1"/>
-      <sheetData sheetId="1437" refreshError="1"/>
-      <sheetData sheetId="1438" refreshError="1"/>
-      <sheetData sheetId="1439" refreshError="1"/>
-      <sheetData sheetId="1440" refreshError="1"/>
-      <sheetData sheetId="1441" refreshError="1"/>
-      <sheetData sheetId="1442" refreshError="1"/>
-      <sheetData sheetId="1443" refreshError="1"/>
-      <sheetData sheetId="1444" refreshError="1"/>
-      <sheetData sheetId="1445" refreshError="1"/>
-      <sheetData sheetId="1446" refreshError="1"/>
-      <sheetData sheetId="1447" refreshError="1"/>
-      <sheetData sheetId="1448" refreshError="1"/>
-      <sheetData sheetId="1449" refreshError="1"/>
-      <sheetData sheetId="1450" refreshError="1"/>
-      <sheetData sheetId="1451" refreshError="1"/>
-      <sheetData sheetId="1452" refreshError="1"/>
-      <sheetData sheetId="1453" refreshError="1"/>
-      <sheetData sheetId="1454" refreshError="1"/>
-      <sheetData sheetId="1455" refreshError="1"/>
-      <sheetData sheetId="1456" refreshError="1"/>
-      <sheetData sheetId="1457" refreshError="1"/>
-      <sheetData sheetId="1458" refreshError="1"/>
-      <sheetData sheetId="1459" refreshError="1"/>
-      <sheetData sheetId="1460" refreshError="1"/>
-      <sheetData sheetId="1461" refreshError="1"/>
-      <sheetData sheetId="1462" refreshError="1"/>
-      <sheetData sheetId="1463" refreshError="1"/>
-      <sheetData sheetId="1464" refreshError="1"/>
-      <sheetData sheetId="1465" refreshError="1"/>
-      <sheetData sheetId="1466" refreshError="1"/>
-      <sheetData sheetId="1467" refreshError="1"/>
-      <sheetData sheetId="1468"/>
-      <sheetData sheetId="1469" refreshError="1"/>
-      <sheetData sheetId="1470" refreshError="1"/>
-      <sheetData sheetId="1471" refreshError="1"/>
-      <sheetData sheetId="1472" refreshError="1"/>
-      <sheetData sheetId="1473" refreshError="1"/>
-      <sheetData sheetId="1474" refreshError="1"/>
-      <sheetData sheetId="1475" refreshError="1"/>
-      <sheetData sheetId="1476" refreshError="1"/>
-      <sheetData sheetId="1477"/>
-      <sheetData sheetId="1478" refreshError="1"/>
-      <sheetData sheetId="1479" refreshError="1"/>
-      <sheetData sheetId="1480" refreshError="1"/>
-      <sheetData sheetId="1481" refreshError="1"/>
-      <sheetData sheetId="1482" refreshError="1"/>
-      <sheetData sheetId="1483" refreshError="1"/>
-      <sheetData sheetId="1484" refreshError="1"/>
-      <sheetData sheetId="1485" refreshError="1"/>
-      <sheetData sheetId="1486" refreshError="1"/>
-      <sheetData sheetId="1487" refreshError="1"/>
-      <sheetData sheetId="1488" refreshError="1"/>
-      <sheetData sheetId="1489" refreshError="1"/>
-      <sheetData sheetId="1490" refreshError="1"/>
-      <sheetData sheetId="1491" refreshError="1"/>
-      <sheetData sheetId="1492" refreshError="1"/>
-      <sheetData sheetId="1493" refreshError="1"/>
-      <sheetData sheetId="1494" refreshError="1"/>
-      <sheetData sheetId="1495" refreshError="1"/>
-      <sheetData sheetId="1496" refreshError="1"/>
-      <sheetData sheetId="1497" refreshError="1"/>
-      <sheetData sheetId="1498" refreshError="1"/>
-      <sheetData sheetId="1499" refreshError="1"/>
-      <sheetData sheetId="1500" refreshError="1"/>
-      <sheetData sheetId="1501" refreshError="1"/>
-      <sheetData sheetId="1502" refreshError="1"/>
-      <sheetData sheetId="1503" refreshError="1"/>
-      <sheetData sheetId="1504" refreshError="1"/>
-      <sheetData sheetId="1505" refreshError="1"/>
-      <sheetData sheetId="1506" refreshError="1"/>
-      <sheetData sheetId="1507" refreshError="1"/>
-      <sheetData sheetId="1508" refreshError="1"/>
-      <sheetData sheetId="1509" refreshError="1"/>
-      <sheetData sheetId="1510" refreshError="1"/>
-      <sheetData sheetId="1511" refreshError="1"/>
-      <sheetData sheetId="1512" refreshError="1"/>
-      <sheetData sheetId="1513" refreshError="1"/>
-      <sheetData sheetId="1514" refreshError="1"/>
-      <sheetData sheetId="1515"/>
-      <sheetData sheetId="1516" refreshError="1"/>
-      <sheetData sheetId="1517" refreshError="1"/>
-      <sheetData sheetId="1518"/>
-      <sheetData sheetId="1519" refreshError="1"/>
-      <sheetData sheetId="1520" refreshError="1"/>
-      <sheetData sheetId="1521" refreshError="1"/>
-      <sheetData sheetId="1522" refreshError="1"/>
-      <sheetData sheetId="1523"/>
-      <sheetData sheetId="1524" refreshError="1"/>
-      <sheetData sheetId="1525" refreshError="1"/>
-      <sheetData sheetId="1526" refreshError="1"/>
-      <sheetData sheetId="1527" refreshError="1"/>
-      <sheetData sheetId="1528" refreshError="1"/>
-      <sheetData sheetId="1529" refreshError="1"/>
-      <sheetData sheetId="1530" refreshError="1"/>
-      <sheetData sheetId="1531" refreshError="1"/>
-      <sheetData sheetId="1532" refreshError="1"/>
-      <sheetData sheetId="1533" refreshError="1"/>
-      <sheetData sheetId="1534" refreshError="1"/>
-      <sheetData sheetId="1535" refreshError="1"/>
-      <sheetData sheetId="1536" refreshError="1"/>
-      <sheetData sheetId="1537" refreshError="1"/>
-      <sheetData sheetId="1538" refreshError="1"/>
-      <sheetData sheetId="1539" refreshError="1"/>
-      <sheetData sheetId="1540" refreshError="1"/>
-      <sheetData sheetId="1541" refreshError="1"/>
-      <sheetData sheetId="1542" refreshError="1"/>
-      <sheetData sheetId="1543" refreshError="1"/>
-      <sheetData sheetId="1544" refreshError="1"/>
-      <sheetData sheetId="1545" refreshError="1"/>
-      <sheetData sheetId="1546" refreshError="1"/>
-      <sheetData sheetId="1547" refreshError="1"/>
-      <sheetData sheetId="1548" refreshError="1"/>
-      <sheetData sheetId="1549" refreshError="1"/>
-      <sheetData sheetId="1550" refreshError="1"/>
-      <sheetData sheetId="1551" refreshError="1"/>
-      <sheetData sheetId="1552" refreshError="1"/>
-      <sheetData sheetId="1553" refreshError="1"/>
-      <sheetData sheetId="1554" refreshError="1"/>
-      <sheetData sheetId="1555" refreshError="1"/>
-      <sheetData sheetId="1556" refreshError="1"/>
-      <sheetData sheetId="1557" refreshError="1"/>
-      <sheetData sheetId="1558" refreshError="1"/>
-      <sheetData sheetId="1559" refreshError="1"/>
-      <sheetData sheetId="1560"/>
-      <sheetData sheetId="1561"/>
-      <sheetData sheetId="1562" refreshError="1"/>
-      <sheetData sheetId="1563" refreshError="1"/>
-      <sheetData sheetId="1564"/>
-      <sheetData sheetId="1565" refreshError="1"/>
-      <sheetData sheetId="1566" refreshError="1"/>
-      <sheetData sheetId="1567" refreshError="1"/>
-      <sheetData sheetId="1568" refreshError="1"/>
-      <sheetData sheetId="1569" refreshError="1"/>
-      <sheetData sheetId="1570" refreshError="1"/>
-      <sheetData sheetId="1571" refreshError="1"/>
-      <sheetData sheetId="1572" refreshError="1"/>
-      <sheetData sheetId="1573" refreshError="1"/>
-      <sheetData sheetId="1574" refreshError="1"/>
-      <sheetData sheetId="1575" refreshError="1"/>
-      <sheetData sheetId="1576" refreshError="1"/>
-      <sheetData sheetId="1577" refreshError="1"/>
-      <sheetData sheetId="1578" refreshError="1"/>
-      <sheetData sheetId="1579" refreshError="1"/>
-      <sheetData sheetId="1580" refreshError="1"/>
-      <sheetData sheetId="1581" refreshError="1"/>
-      <sheetData sheetId="1582"/>
-      <sheetData sheetId="1583" refreshError="1"/>
-      <sheetData sheetId="1584" refreshError="1"/>
-      <sheetData sheetId="1585" refreshError="1"/>
-      <sheetData sheetId="1586" refreshError="1"/>
-      <sheetData sheetId="1587" refreshError="1"/>
-      <sheetData sheetId="1588" refreshError="1"/>
-      <sheetData sheetId="1589" refreshError="1"/>
-      <sheetData sheetId="1590" refreshError="1"/>
-      <sheetData sheetId="1591" refreshError="1"/>
-      <sheetData sheetId="1592" refreshError="1"/>
-      <sheetData sheetId="1593" refreshError="1"/>
-      <sheetData sheetId="1594" refreshError="1"/>
-      <sheetData sheetId="1595" refreshError="1"/>
-      <sheetData sheetId="1596" refreshError="1"/>
-      <sheetData sheetId="1597" refreshError="1"/>
-      <sheetData sheetId="1598" refreshError="1"/>
-      <sheetData sheetId="1599" refreshError="1"/>
-      <sheetData sheetId="1600" refreshError="1"/>
-      <sheetData sheetId="1601" refreshError="1"/>
-      <sheetData sheetId="1602" refreshError="1"/>
-      <sheetData sheetId="1603" refreshError="1"/>
-      <sheetData sheetId="1604" refreshError="1"/>
-      <sheetData sheetId="1605" refreshError="1"/>
-      <sheetData sheetId="1606" refreshError="1"/>
-      <sheetData sheetId="1607" refreshError="1"/>
-      <sheetData sheetId="1608" refreshError="1"/>
-      <sheetData sheetId="1609" refreshError="1"/>
-      <sheetData sheetId="1610" refreshError="1"/>
-      <sheetData sheetId="1611" refreshError="1"/>
-      <sheetData sheetId="1612" refreshError="1"/>
-      <sheetData sheetId="1613" refreshError="1"/>
-      <sheetData sheetId="1614" refreshError="1"/>
-      <sheetData sheetId="1615" refreshError="1"/>
-      <sheetData sheetId="1616" refreshError="1"/>
-      <sheetData sheetId="1617" refreshError="1"/>
-      <sheetData sheetId="1618" refreshError="1"/>
-      <sheetData sheetId="1619" refreshError="1"/>
-      <sheetData sheetId="1620" refreshError="1"/>
-      <sheetData sheetId="1621" refreshError="1"/>
-      <sheetData sheetId="1622" refreshError="1"/>
-      <sheetData sheetId="1623" refreshError="1"/>
-      <sheetData sheetId="1624" refreshError="1"/>
-      <sheetData sheetId="1625" refreshError="1"/>
-      <sheetData sheetId="1626" refreshError="1"/>
-      <sheetData sheetId="1627" refreshError="1"/>
-      <sheetData sheetId="1628" refreshError="1"/>
-      <sheetData sheetId="1629" refreshError="1"/>
-      <sheetData sheetId="1630" refreshError="1"/>
-      <sheetData sheetId="1631" refreshError="1"/>
-      <sheetData sheetId="1632" refreshError="1"/>
-      <sheetData sheetId="1633" refreshError="1"/>
-      <sheetData sheetId="1634" refreshError="1"/>
-      <sheetData sheetId="1635" refreshError="1"/>
-      <sheetData sheetId="1636" refreshError="1"/>
-      <sheetData sheetId="1637" refreshError="1"/>
-      <sheetData sheetId="1638" refreshError="1"/>
-      <sheetData sheetId="1639" refreshError="1"/>
-      <sheetData sheetId="1640" refreshError="1"/>
-      <sheetData sheetId="1641" refreshError="1"/>
-      <sheetData sheetId="1642" refreshError="1"/>
-      <sheetData sheetId="1643" refreshError="1"/>
-      <sheetData sheetId="1644" refreshError="1"/>
-      <sheetData sheetId="1645" refreshError="1"/>
-      <sheetData sheetId="1646" refreshError="1"/>
-      <sheetData sheetId="1647" refreshError="1"/>
-      <sheetData sheetId="1648" refreshError="1"/>
-      <sheetData sheetId="1649" refreshError="1"/>
-      <sheetData sheetId="1650" refreshError="1"/>
-      <sheetData sheetId="1651" refreshError="1"/>
-      <sheetData sheetId="1652" refreshError="1"/>
-      <sheetData sheetId="1653" refreshError="1"/>
-      <sheetData sheetId="1654" refreshError="1"/>
-      <sheetData sheetId="1655" refreshError="1"/>
-      <sheetData sheetId="1656" refreshError="1"/>
-      <sheetData sheetId="1657" refreshError="1"/>
-      <sheetData sheetId="1658" refreshError="1"/>
-      <sheetData sheetId="1659" refreshError="1"/>
-      <sheetData sheetId="1660" refreshError="1"/>
-      <sheetData sheetId="1661" refreshError="1"/>
-      <sheetData sheetId="1662" refreshError="1"/>
-      <sheetData sheetId="1663" refreshError="1"/>
-      <sheetData sheetId="1664" refreshError="1"/>
-      <sheetData sheetId="1665" refreshError="1"/>
-      <sheetData sheetId="1666" refreshError="1"/>
-      <sheetData sheetId="1667" refreshError="1"/>
-      <sheetData sheetId="1668" refreshError="1"/>
-      <sheetData sheetId="1669" refreshError="1"/>
-      <sheetData sheetId="1670" refreshError="1"/>
-      <sheetData sheetId="1671" refreshError="1"/>
-      <sheetData sheetId="1672" refreshError="1"/>
-      <sheetData sheetId="1673" refreshError="1"/>
-      <sheetData sheetId="1674" refreshError="1"/>
-      <sheetData sheetId="1675" refreshError="1"/>
-      <sheetData sheetId="1676" refreshError="1"/>
-      <sheetData sheetId="1677" refreshError="1"/>
-      <sheetData sheetId="1678" refreshError="1"/>
-      <sheetData sheetId="1679" refreshError="1"/>
-      <sheetData sheetId="1680" refreshError="1"/>
-      <sheetData sheetId="1681" refreshError="1"/>
-      <sheetData sheetId="1682" refreshError="1"/>
-      <sheetData sheetId="1683" refreshError="1"/>
-      <sheetData sheetId="1684" refreshError="1"/>
-      <sheetData sheetId="1685" refreshError="1"/>
-      <sheetData sheetId="1686" refreshError="1"/>
-      <sheetData sheetId="1687" refreshError="1"/>
-      <sheetData sheetId="1688" refreshError="1"/>
-      <sheetData sheetId="1689" refreshError="1"/>
-      <sheetData sheetId="1690" refreshError="1"/>
-      <sheetData sheetId="1691" refreshError="1"/>
-      <sheetData sheetId="1692" refreshError="1"/>
-      <sheetData sheetId="1693" refreshError="1"/>
-      <sheetData sheetId="1694" refreshError="1"/>
-      <sheetData sheetId="1695" refreshError="1"/>
-      <sheetData sheetId="1696" refreshError="1"/>
-      <sheetData sheetId="1697" refreshError="1"/>
-      <sheetData sheetId="1698" refreshError="1"/>
-      <sheetData sheetId="1699" refreshError="1"/>
-      <sheetData sheetId="1700" refreshError="1"/>
-      <sheetData sheetId="1701" refreshError="1"/>
-      <sheetData sheetId="1702" refreshError="1"/>
-      <sheetData sheetId="1703" refreshError="1"/>
-      <sheetData sheetId="1704" refreshError="1"/>
-      <sheetData sheetId="1705" refreshError="1"/>
-      <sheetData sheetId="1706" refreshError="1"/>
-      <sheetData sheetId="1707" refreshError="1"/>
-      <sheetData sheetId="1708" refreshError="1"/>
-      <sheetData sheetId="1709" refreshError="1"/>
-      <sheetData sheetId="1710" refreshError="1"/>
-      <sheetData sheetId="1711" refreshError="1"/>
-      <sheetData sheetId="1712" refreshError="1"/>
-      <sheetData sheetId="1713" refreshError="1"/>
-      <sheetData sheetId="1714" refreshError="1"/>
-      <sheetData sheetId="1715" refreshError="1"/>
-      <sheetData sheetId="1716" refreshError="1"/>
-      <sheetData sheetId="1717" refreshError="1"/>
-      <sheetData sheetId="1718" refreshError="1"/>
-      <sheetData sheetId="1719" refreshError="1"/>
-      <sheetData sheetId="1720" refreshError="1"/>
-      <sheetData sheetId="1721" refreshError="1"/>
-      <sheetData sheetId="1722" refreshError="1"/>
-      <sheetData sheetId="1723" refreshError="1"/>
-      <sheetData sheetId="1724" refreshError="1"/>
-      <sheetData sheetId="1725" refreshError="1"/>
-      <sheetData sheetId="1726" refreshError="1"/>
-      <sheetData sheetId="1727" refreshError="1"/>
-      <sheetData sheetId="1728" refreshError="1"/>
-      <sheetData sheetId="1729" refreshError="1"/>
-      <sheetData sheetId="1730" refreshError="1"/>
-      <sheetData sheetId="1731" refreshError="1"/>
-      <sheetData sheetId="1732" refreshError="1"/>
-      <sheetData sheetId="1733" refreshError="1"/>
-      <sheetData sheetId="1734" refreshError="1"/>
-      <sheetData sheetId="1735" refreshError="1"/>
-      <sheetData sheetId="1736" refreshError="1"/>
-      <sheetData sheetId="1737" refreshError="1"/>
-      <sheetData sheetId="1738" refreshError="1"/>
-      <sheetData sheetId="1739" refreshError="1"/>
-      <sheetData sheetId="1740" refreshError="1"/>
-      <sheetData sheetId="1741" refreshError="1"/>
-      <sheetData sheetId="1742" refreshError="1"/>
-      <sheetData sheetId="1743" refreshError="1"/>
-      <sheetData sheetId="1744"/>
-      <sheetData sheetId="1745" refreshError="1"/>
-      <sheetData sheetId="1746" refreshError="1"/>
-      <sheetData sheetId="1747" refreshError="1"/>
-      <sheetData sheetId="1748" refreshError="1"/>
-      <sheetData sheetId="1749" refreshError="1"/>
-      <sheetData sheetId="1750" refreshError="1"/>
-      <sheetData sheetId="1751" refreshError="1"/>
-      <sheetData sheetId="1752" refreshError="1"/>
-      <sheetData sheetId="1753" refreshError="1"/>
-      <sheetData sheetId="1754" refreshError="1"/>
-      <sheetData sheetId="1755" refreshError="1"/>
-      <sheetData sheetId="1756" refreshError="1"/>
-      <sheetData sheetId="1757" refreshError="1"/>
-      <sheetData sheetId="1758" refreshError="1"/>
-      <sheetData sheetId="1759" refreshError="1"/>
-      <sheetData sheetId="1760" refreshError="1"/>
-      <sheetData sheetId="1761" refreshError="1"/>
-      <sheetData sheetId="1762" refreshError="1"/>
-      <sheetData sheetId="1763"/>
-      <sheetData sheetId="1764"/>
-      <sheetData sheetId="1765" refreshError="1"/>
-      <sheetData sheetId="1766" refreshError="1"/>
-      <sheetData sheetId="1767" refreshError="1"/>
-      <sheetData sheetId="1768" refreshError="1"/>
-      <sheetData sheetId="1769" refreshError="1"/>
-      <sheetData sheetId="1770" refreshError="1"/>
-      <sheetData sheetId="1771" refreshError="1"/>
-      <sheetData sheetId="1772" refreshError="1"/>
-      <sheetData sheetId="1773" refreshError="1"/>
-      <sheetData sheetId="1774" refreshError="1"/>
-      <sheetData sheetId="1775" refreshError="1"/>
-      <sheetData sheetId="1776" refreshError="1"/>
-      <sheetData sheetId="1777" refreshError="1"/>
-      <sheetData sheetId="1778" refreshError="1"/>
-      <sheetData sheetId="1779" refreshError="1"/>
-      <sheetData sheetId="1780" refreshError="1"/>
-      <sheetData sheetId="1781" refreshError="1"/>
-      <sheetData sheetId="1782" refreshError="1"/>
-      <sheetData sheetId="1783" refreshError="1"/>
-      <sheetData sheetId="1784" refreshError="1"/>
-      <sheetData sheetId="1785" refreshError="1"/>
-      <sheetData sheetId="1786" refreshError="1"/>
-      <sheetData sheetId="1787" refreshError="1"/>
-      <sheetData sheetId="1788" refreshError="1"/>
-      <sheetData sheetId="1789" refreshError="1"/>
-      <sheetData sheetId="1790" refreshError="1"/>
-      <sheetData sheetId="1791" refreshError="1"/>
-      <sheetData sheetId="1792" refreshError="1"/>
-      <sheetData sheetId="1793" refreshError="1"/>
-      <sheetData sheetId="1794" refreshError="1"/>
-      <sheetData sheetId="1795" refreshError="1"/>
-      <sheetData sheetId="1796" refreshError="1"/>
-      <sheetData sheetId="1797" refreshError="1"/>
-      <sheetData sheetId="1798" refreshError="1"/>
-      <sheetData sheetId="1799" refreshError="1"/>
-      <sheetData sheetId="1800" refreshError="1"/>
-      <sheetData sheetId="1801" refreshError="1"/>
-      <sheetData sheetId="1802" refreshError="1"/>
-      <sheetData sheetId="1803" refreshError="1"/>
-      <sheetData sheetId="1804" refreshError="1"/>
-      <sheetData sheetId="1805" refreshError="1"/>
-      <sheetData sheetId="1806" refreshError="1"/>
-      <sheetData sheetId="1807" refreshError="1"/>
-      <sheetData sheetId="1808" refreshError="1"/>
-      <sheetData sheetId="1809" refreshError="1"/>
-      <sheetData sheetId="1810" refreshError="1"/>
-      <sheetData sheetId="1811" refreshError="1"/>
-      <sheetData sheetId="1812" refreshError="1"/>
-      <sheetData sheetId="1813" refreshError="1"/>
-      <sheetData sheetId="1814" refreshError="1"/>
-      <sheetData sheetId="1815" refreshError="1"/>
-      <sheetData sheetId="1816" refreshError="1"/>
-      <sheetData sheetId="1817" refreshError="1"/>
-      <sheetData sheetId="1818" refreshError="1"/>
-      <sheetData sheetId="1819" refreshError="1"/>
-      <sheetData sheetId="1820" refreshError="1"/>
-      <sheetData sheetId="1821" refreshError="1"/>
-      <sheetData sheetId="1822" refreshError="1"/>
-      <sheetData sheetId="1823" refreshError="1"/>
-      <sheetData sheetId="1824" refreshError="1"/>
-      <sheetData sheetId="1825" refreshError="1"/>
-      <sheetData sheetId="1826" refreshError="1"/>
-      <sheetData sheetId="1827" refreshError="1"/>
-      <sheetData sheetId="1828" refreshError="1"/>
-      <sheetData sheetId="1829" refreshError="1"/>
-      <sheetData sheetId="1830" refreshError="1"/>
-      <sheetData sheetId="1831" refreshError="1"/>
-      <sheetData sheetId="1832" refreshError="1"/>
-      <sheetData sheetId="1833" refreshError="1"/>
-      <sheetData sheetId="1834" refreshError="1"/>
-      <sheetData sheetId="1835" refreshError="1"/>
-      <sheetData sheetId="1836" refreshError="1"/>
-      <sheetData sheetId="1837" refreshError="1"/>
-      <sheetData sheetId="1838" refreshError="1"/>
-      <sheetData sheetId="1839" refreshError="1"/>
-      <sheetData sheetId="1840" refreshError="1"/>
-      <sheetData sheetId="1841" refreshError="1"/>
-      <sheetData sheetId="1842" refreshError="1"/>
-      <sheetData sheetId="1843" refreshError="1"/>
-      <sheetData sheetId="1844" refreshError="1"/>
-      <sheetData sheetId="1845" refreshError="1"/>
-      <sheetData sheetId="1846" refreshError="1"/>
-      <sheetData sheetId="1847" refreshError="1"/>
-      <sheetData sheetId="1848" refreshError="1"/>
-      <sheetData sheetId="1849" refreshError="1"/>
-      <sheetData sheetId="1850" refreshError="1"/>
-      <sheetData sheetId="1851" refreshError="1"/>
-      <sheetData sheetId="1852" refreshError="1"/>
-      <sheetData sheetId="1853" refreshError="1"/>
-      <sheetData sheetId="1854" refreshError="1"/>
-      <sheetData sheetId="1855" refreshError="1"/>
-      <sheetData sheetId="1856" refreshError="1"/>
-      <sheetData sheetId="1857" refreshError="1"/>
-      <sheetData sheetId="1858" refreshError="1"/>
-      <sheetData sheetId="1859" refreshError="1"/>
-      <sheetData sheetId="1860" refreshError="1"/>
-      <sheetData sheetId="1861" refreshError="1"/>
-      <sheetData sheetId="1862" refreshError="1"/>
-      <sheetData sheetId="1863" refreshError="1"/>
-      <sheetData sheetId="1864" refreshError="1"/>
-      <sheetData sheetId="1865" refreshError="1"/>
-      <sheetData sheetId="1866" refreshError="1"/>
-      <sheetData sheetId="1867" refreshError="1"/>
-      <sheetData sheetId="1868" refreshError="1"/>
-      <sheetData sheetId="1869" refreshError="1"/>
-      <sheetData sheetId="1870" refreshError="1"/>
-      <sheetData sheetId="1871" refreshError="1"/>
-      <sheetData sheetId="1872" refreshError="1"/>
-      <sheetData sheetId="1873" refreshError="1"/>
-      <sheetData sheetId="1874" refreshError="1"/>
-      <sheetData sheetId="1875" refreshError="1"/>
-      <sheetData sheetId="1876" refreshError="1"/>
-      <sheetData sheetId="1877" refreshError="1"/>
-      <sheetData sheetId="1878" refreshError="1"/>
-      <sheetData sheetId="1879" refreshError="1"/>
-      <sheetData sheetId="1880" refreshError="1"/>
-      <sheetData sheetId="1881" refreshError="1"/>
-      <sheetData sheetId="1882" refreshError="1"/>
-      <sheetData sheetId="1883" refreshError="1"/>
-      <sheetData sheetId="1884" refreshError="1"/>
-      <sheetData sheetId="1885" refreshError="1"/>
-      <sheetData sheetId="1886" refreshError="1"/>
-      <sheetData sheetId="1887" refreshError="1"/>
-      <sheetData sheetId="1888" refreshError="1"/>
-      <sheetData sheetId="1889" refreshError="1"/>
-      <sheetData sheetId="1890" refreshError="1"/>
-      <sheetData sheetId="1891" refreshError="1"/>
-      <sheetData sheetId="1892" refreshError="1"/>
-      <sheetData sheetId="1893" refreshError="1"/>
-      <sheetData sheetId="1894" refreshError="1"/>
-      <sheetData sheetId="1895" refreshError="1"/>
-      <sheetData sheetId="1896" refreshError="1"/>
-      <sheetData sheetId="1897" refreshError="1"/>
-      <sheetData sheetId="1898" refreshError="1"/>
-      <sheetData sheetId="1899" refreshError="1"/>
-      <sheetData sheetId="1900" refreshError="1"/>
-      <sheetData sheetId="1901" refreshError="1"/>
-      <sheetData sheetId="1902" refreshError="1"/>
-      <sheetData sheetId="1903" refreshError="1"/>
-      <sheetData sheetId="1904" refreshError="1"/>
-      <sheetData sheetId="1905" refreshError="1"/>
-      <sheetData sheetId="1906" refreshError="1"/>
-      <sheetData sheetId="1907" refreshError="1"/>
-      <sheetData sheetId="1908" refreshError="1"/>
-      <sheetData sheetId="1909" refreshError="1"/>
-      <sheetData sheetId="1910" refreshError="1"/>
-      <sheetData sheetId="1911" refreshError="1"/>
-      <sheetData sheetId="1912" refreshError="1"/>
-      <sheetData sheetId="1913" refreshError="1"/>
-      <sheetData sheetId="1914" refreshError="1"/>
-      <sheetData sheetId="1915" refreshError="1"/>
-      <sheetData sheetId="1916" refreshError="1"/>
-      <sheetData sheetId="1917" refreshError="1"/>
-      <sheetData sheetId="1918" refreshError="1"/>
-      <sheetData sheetId="1919" refreshError="1"/>
-      <sheetData sheetId="1920" refreshError="1"/>
-      <sheetData sheetId="1921" refreshError="1"/>
-      <sheetData sheetId="1922" refreshError="1"/>
-      <sheetData sheetId="1923" refreshError="1"/>
-      <sheetData sheetId="1924" refreshError="1"/>
-      <sheetData sheetId="1925" refreshError="1"/>
-      <sheetData sheetId="1926" refreshError="1"/>
-      <sheetData sheetId="1927" refreshError="1"/>
-      <sheetData sheetId="1928" refreshError="1"/>
-      <sheetData sheetId="1929" refreshError="1"/>
-      <sheetData sheetId="1930" refreshError="1"/>
-      <sheetData sheetId="1931" refreshError="1"/>
-      <sheetData sheetId="1932" refreshError="1"/>
-      <sheetData sheetId="1933" refreshError="1"/>
-      <sheetData sheetId="1934" refreshError="1"/>
-      <sheetData sheetId="1935" refreshError="1"/>
-      <sheetData sheetId="1936" refreshError="1"/>
-      <sheetData sheetId="1937" refreshError="1"/>
-      <sheetData sheetId="1938" refreshError="1"/>
-      <sheetData sheetId="1939" refreshError="1"/>
-      <sheetData sheetId="1940" refreshError="1"/>
-      <sheetData sheetId="1941" refreshError="1"/>
-      <sheetData sheetId="1942" refreshError="1"/>
-      <sheetData sheetId="1943" refreshError="1"/>
-      <sheetData sheetId="1944" refreshError="1"/>
-      <sheetData sheetId="1945" refreshError="1"/>
-      <sheetData sheetId="1946" refreshError="1"/>
-      <sheetData sheetId="1947" refreshError="1"/>
-      <sheetData sheetId="1948" refreshError="1"/>
-      <sheetData sheetId="1949" refreshError="1"/>
-      <sheetData sheetId="1950" refreshError="1"/>
-      <sheetData sheetId="1951" refreshError="1"/>
-      <sheetData sheetId="1952" refreshError="1"/>
-      <sheetData sheetId="1953" refreshError="1"/>
-      <sheetData sheetId="1954" refreshError="1"/>
-      <sheetData sheetId="1955" refreshError="1"/>
-      <sheetData sheetId="1956" refreshError="1"/>
-      <sheetData sheetId="1957" refreshError="1"/>
-      <sheetData sheetId="1958" refreshError="1"/>
-      <sheetData sheetId="1959" refreshError="1"/>
-      <sheetData sheetId="1960" refreshError="1"/>
-      <sheetData sheetId="1961" refreshError="1"/>
-      <sheetData sheetId="1962" refreshError="1"/>
-      <sheetData sheetId="1963" refreshError="1"/>
-      <sheetData sheetId="1964" refreshError="1"/>
-      <sheetData sheetId="1965" refreshError="1"/>
-      <sheetData sheetId="1966" refreshError="1"/>
-      <sheetData sheetId="1967" refreshError="1"/>
-      <sheetData sheetId="1968" refreshError="1"/>
-      <sheetData sheetId="1969" refreshError="1"/>
-      <sheetData sheetId="1970" refreshError="1"/>
-      <sheetData sheetId="1971" refreshError="1"/>
-      <sheetData sheetId="1972" refreshError="1"/>
-      <sheetData sheetId="1973" refreshError="1"/>
-      <sheetData sheetId="1974" refreshError="1"/>
-      <sheetData sheetId="1975" refreshError="1"/>
-      <sheetData sheetId="1976" refreshError="1"/>
-      <sheetData sheetId="1977" refreshError="1"/>
-      <sheetData sheetId="1978" refreshError="1"/>
-      <sheetData sheetId="1979" refreshError="1"/>
-      <sheetData sheetId="1980" refreshError="1"/>
-      <sheetData sheetId="1981" refreshError="1"/>
-      <sheetData sheetId="1982" refreshError="1"/>
-      <sheetData sheetId="1983" refreshError="1"/>
-      <sheetData sheetId="1984" refreshError="1"/>
-      <sheetData sheetId="1985" refreshError="1"/>
-      <sheetData sheetId="1986" refreshError="1"/>
-      <sheetData sheetId="1987" refreshError="1"/>
-      <sheetData sheetId="1988" refreshError="1"/>
-      <sheetData sheetId="1989" refreshError="1"/>
-      <sheetData sheetId="1990" refreshError="1"/>
-      <sheetData sheetId="1991" refreshError="1"/>
-      <sheetData sheetId="1992" refreshError="1"/>
-      <sheetData sheetId="1993" refreshError="1"/>
-      <sheetData sheetId="1994" refreshError="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="breakdown"/>
-      <sheetName val="2004"/>
-      <sheetName val="test on帐面补差"/>
-      <sheetName val="XREF"/>
-      <sheetName val="Tickmarks"/>
-      <sheetName val="企业表一"/>
-      <sheetName val="M-5C"/>
-      <sheetName val="M-5A"/>
-      <sheetName val="科目表"/>
-      <sheetName val="机关财务营业费用"/>
-      <sheetName val="存栏2"/>
-      <sheetName val="索引"/>
-      <sheetName val="生产成本账"/>
-      <sheetName val="系统参数设置"/>
-      <sheetName val="固定资产清单"/>
-      <sheetName val="示范99tzfl"/>
-      <sheetName val="#REF!"/>
-      <sheetName val="明细科目余额表"/>
-      <sheetName val="现金明细（勿删）"/>
-      <sheetName val="本期报表"/>
-      <sheetName val="XL4Poppy"/>
-      <sheetName val="1"/>
-      <sheetName val="2"/>
-      <sheetName val="3"/>
-      <sheetName val="4"/>
-      <sheetName val="5"/>
-      <sheetName val="6"/>
-      <sheetName val="7"/>
-      <sheetName val="8"/>
-      <sheetName val="9"/>
-      <sheetName val="10"/>
-      <sheetName val="11"/>
-      <sheetName val="12"/>
-      <sheetName val="1-12"/>
-      <sheetName val="3 (2)"/>
-      <sheetName val="4 (2)"/>
-      <sheetName val="5 (2)"/>
-      <sheetName val="6 (2)"/>
-      <sheetName val="7 (2)"/>
-      <sheetName val="8 (2)"/>
-      <sheetName val="9 (2)"/>
-      <sheetName val="10 (2)"/>
-      <sheetName val="11 (2)"/>
-      <sheetName val="12 (2)"/>
-      <sheetName val="1 (2)"/>
-      <sheetName val="2 (2)"/>
-      <sheetName val="Raw materials"/>
-      <sheetName val="Investment Property"/>
-      <sheetName val="基本参数"/>
-      <sheetName val="W"/>
-      <sheetName val="生产成本"/>
-      <sheetName val="&lt;原报&gt;资产负债表"/>
-      <sheetName val="PER SALES ORG"/>
-      <sheetName val="Bilanz Aktiva"/>
-      <sheetName val="Bil.Zu-Abgang"/>
-      <sheetName val="Cash Flow"/>
-      <sheetName val="GuV"/>
-      <sheetName val="Bilanz Passiva"/>
-      <sheetName val="差异调整97"/>
-      <sheetName val="差异调整95"/>
-      <sheetName val="差异调整96"/>
-      <sheetName val="1－5月余额表"/>
-      <sheetName val="1－10月余额表"/>
-      <sheetName val="预付账款Dy"/>
-      <sheetName val="Source"/>
-      <sheetName val="Bal Sheet"/>
-      <sheetName val="DATA"/>
-      <sheetName val="UFPrn20061113135115"/>
-      <sheetName val="基本信息"/>
-      <sheetName val="35.1租赁明细"/>
-      <sheetName val="表头"/>
-      <sheetName val="PTC"/>
-      <sheetName val="资产负债表"/>
-      <sheetName val="YS02-02"/>
-      <sheetName val="P12 TB SZ"/>
-      <sheetName val="B"/>
-      <sheetName val="coding"/>
-      <sheetName val="基础数据"/>
-      <sheetName val="三兴2"/>
-      <sheetName val="Toolbox"/>
-      <sheetName val="Appendix"/>
-      <sheetName val="PRC BS"/>
-      <sheetName val="完"/>
-      <sheetName val="인사현황(부서)"/>
-      <sheetName val="Cover"/>
-      <sheetName val="营业费用测试"/>
-      <sheetName val="KKKKKKKK"/>
-      <sheetName val="管理费用(集团董事会)"/>
-      <sheetName val="C_301"/>
-      <sheetName val="C_311"/>
-      <sheetName val="C_318"/>
-      <sheetName val="Sheet1"/>
-      <sheetName val="委托加工材料"/>
-      <sheetName val="材料采购－原材料（购价）"/>
-      <sheetName val="核算项目余额表"/>
-      <sheetName val="应付账款"/>
-      <sheetName val="预提费用"/>
-      <sheetName val="清单12.31"/>
-      <sheetName val="材料采购-入库"/>
-      <sheetName val="原材料－其他"/>
-      <sheetName val="材料成本差异－运费等"/>
-      <sheetName val="数量对比"/>
-      <sheetName val="BALANCE SHEET"/>
-      <sheetName val="表头（请先填写+核心提示）"/>
-      <sheetName val="账面外销"/>
-      <sheetName val="应收账款余额表"/>
-      <sheetName val="所得税明细表"/>
-      <sheetName val="产销存"/>
-      <sheetName val="1-6累计销售"/>
-      <sheetName val="收入个月"/>
-      <sheetName val="累计产销存"/>
-      <sheetName val="AGRO-DATA"/>
-      <sheetName val="报表科目"/>
-      <sheetName val="应收账款贷方余额表"/>
-      <sheetName val="应收账款借方余额表"/>
-      <sheetName val=""/>
-      <sheetName val="STATPARA"/>
-      <sheetName val="Lead"/>
-      <sheetName val="CF"/>
-      <sheetName val="preBS"/>
-      <sheetName val="preCF"/>
-      <sheetName val="preIS"/>
-      <sheetName val="preCE"/>
-      <sheetName val="TB"/>
-      <sheetName val="标本-资产"/>
-      <sheetName val="主营业务成本Dy"/>
-      <sheetName val="分录"/>
-      <sheetName val="存货_包装物"/>
-      <sheetName val="存货_库存商品mx"/>
-      <sheetName val="存货_生产成本mx1"/>
-      <sheetName val="存货_委托加工物资mx"/>
-      <sheetName val="存货_制造费用Mx"/>
-      <sheetName val="应收账款"/>
-      <sheetName val="制造成本表"/>
-      <sheetName val="Summary"/>
-      <sheetName val="9000"/>
-      <sheetName val="9747"/>
-      <sheetName val="9577"/>
-      <sheetName val="COS breakdown"/>
-      <sheetName val="2-1主营业务收入查证表1"/>
-      <sheetName val="审计说明"/>
-      <sheetName val="FA-2"/>
-      <sheetName val="目錄"/>
-      <sheetName val="短期投资股票投资.dbf"/>
-      <sheetName val="短期投资国债投资.dbf"/>
-      <sheetName val="股票投资收益.dbf"/>
-      <sheetName val="其他货币海通.dbf"/>
-      <sheetName val="其他货币零领路.dbf"/>
-      <sheetName val="投资收益债券.dbf"/>
-      <sheetName val="选择键"/>
-      <sheetName val="有效性"/>
-      <sheetName val="总成本"/>
-      <sheetName val="UFPrn20030731121657"/>
-      <sheetName val="合并清单"/>
-      <sheetName val="Ex Diff"/>
-      <sheetName val="导引表"/>
-      <sheetName val="Control"/>
-      <sheetName val="长投测试"/>
-      <sheetName val="E1020"/>
-      <sheetName val="AR"/>
-      <sheetName val="福州路仓库(3)"/>
-      <sheetName val="物资采购-1"/>
-      <sheetName val="物资采购-2"/>
-      <sheetName val="祁连山路仓库(5)"/>
-      <sheetName val="特种储备物资"/>
-      <sheetName val="张江库"/>
-      <sheetName val="other lia"/>
-      <sheetName val="prepayment"/>
-      <sheetName val="related co"/>
-      <sheetName val="adm"/>
-      <sheetName val="sel"/>
-      <sheetName val="基本情况表"/>
-      <sheetName val="POWER ASSUMPTIONS"/>
-      <sheetName val="eqpmad2"/>
-      <sheetName val="1月"/>
-      <sheetName val="收入"/>
-      <sheetName val="说明"/>
-      <sheetName val="_x005f_x0000__x005f_x0000__x005f_x0000__x005f_x0000__x0"/>
-      <sheetName val="名称（勿删）"/>
-      <sheetName val="营业外收支明细"/>
-      <sheetName val="7-11销售"/>
-      <sheetName val="表头信息"/>
-      <sheetName val="gvl"/>
-      <sheetName val="Title"/>
-      <sheetName val="Understand the client"/>
-      <sheetName val="Bokslutsprocessen"/>
-      <sheetName val="Indata"/>
-      <sheetName val="CRA"/>
-      <sheetName val="材差5月份结转"/>
-      <sheetName val="生产成本6月份结转"/>
-      <sheetName val="库存商品项目账"/>
-      <sheetName val="Worksheet in 8240 COS breakdown"/>
-      <sheetName val="12进销存"/>
-      <sheetName val="5月"/>
-      <sheetName val="6月"/>
-      <sheetName val="上期报表"/>
-      <sheetName val="工程物资Dy"/>
-      <sheetName val="索引表"/>
-      <sheetName val="表头（请先填写）"/>
-      <sheetName val="US Codes"/>
-      <sheetName val="M3 - BS"/>
-      <sheetName val="M3 - PL"/>
-      <sheetName val="B-S"/>
-      <sheetName val="3库存"/>
-      <sheetName val="3收入"/>
-      <sheetName val="3成本"/>
-      <sheetName val="委托加工物资明细"/>
-      <sheetName val="专项买的固定资产"/>
-      <sheetName val="#REF"/>
-      <sheetName val="项目调整"/>
-      <sheetName val="剥离前"/>
-      <sheetName val="成本调整明细表"/>
-      <sheetName val="_x005f_x005f_x005f_x0000__x005f_x005f_x005f_x0000__x005"/>
-      <sheetName val="original"/>
-      <sheetName val="Erection"/>
-      <sheetName val="劳务费"/>
-      <sheetName val="折旧"/>
-      <sheetName val="工资"/>
-      <sheetName val="福利费"/>
-      <sheetName val="水电费"/>
-      <sheetName val="办公费"/>
-      <sheetName val="业务招待费"/>
-      <sheetName val="差"/>
-      <sheetName val="机"/>
-      <sheetName val="劳保"/>
-      <sheetName val="通迅费"/>
-      <sheetName val="修"/>
-      <sheetName val="营业外收入Dy"/>
-      <sheetName val="固定资产Dy"/>
-      <sheetName val="累计折旧Dy"/>
-      <sheetName val="银行存款Dy"/>
-      <sheetName val="应收利息Dy"/>
-      <sheetName val="短期投资Dy"/>
-      <sheetName val="货币资金Dy"/>
-      <sheetName val="参数"/>
-      <sheetName val="无形资产年末数构成"/>
-      <sheetName val="营业外支出"/>
-      <sheetName val="Currency"/>
-      <sheetName val="DropDown"/>
-      <sheetName val="Non-Statistical Sampling"/>
-      <sheetName val="现金"/>
-      <sheetName val="多级销售汇总表（备用）"/>
-      <sheetName val="Financ. Overview"/>
-      <sheetName val="China"/>
-      <sheetName val="Absol"/>
-      <sheetName val="降低额统计(会签)"/>
-      <sheetName val="2.대외공문"/>
-      <sheetName val="RD제품개발투자비(매가)"/>
-      <sheetName val="培训执行汇总"/>
-      <sheetName val="02考勤"/>
-      <sheetName val="项目"/>
-      <sheetName val="06汇总"/>
-      <sheetName val="8月乘用车分公司期间费用统计表"/>
-      <sheetName val="分产品销售收入、成本分析表"/>
-      <sheetName val="Sheet3"/>
-      <sheetName val="PRC-BS-SZ"/>
-      <sheetName val="Main"/>
-      <sheetName val="Income Statement"/>
-      <sheetName val="试算平衡表"/>
-      <sheetName val="其他应付款科目余额2005.12.31"/>
-      <sheetName val="订单"/>
-      <sheetName val="内部往来"/>
-      <sheetName val="中山低值"/>
-      <sheetName val="Sales Jul 99"/>
-      <sheetName val="RESULT"/>
-      <sheetName val="基本信息输入"/>
-      <sheetName val="审计分工配置表"/>
-      <sheetName val="UFPrn2003其他"/>
-      <sheetName val="COS SAR"/>
-      <sheetName val="Excess Calc"/>
-      <sheetName val="2005"/>
-      <sheetName val="2003"/>
-      <sheetName val="2002"/>
-      <sheetName val="2001"/>
-      <sheetName val="Summary-返利"/>
-      <sheetName val="返利收入青岛"/>
-      <sheetName val="返利收入-淄博"/>
-      <sheetName val="COS"/>
-      <sheetName val="SAR"/>
-      <sheetName val="PIT-cost"/>
-      <sheetName val="Major FG analysis"/>
-      <sheetName val="GP ratio"/>
-      <sheetName val="GP ratio Analysis"/>
-      <sheetName val="Consolidation"/>
-      <sheetName val="申友"/>
-      <sheetName val="Printing cost breakdown"/>
-      <sheetName val="Purchase"/>
-      <sheetName val="Excess Calc for ref"/>
-      <sheetName val="Breakdown 2005.12"/>
-      <sheetName val="累计销售"/>
-      <sheetName val="银行借款询证"/>
-      <sheetName val="基础信息"/>
-      <sheetName val="D4-封面"/>
-      <sheetName val="D41-封面"/>
-      <sheetName val="收入和成本对应表"/>
-      <sheetName val="主营业务明细表"/>
-      <sheetName val="_x005f_x0000__x005f_x0000__x005"/>
-      <sheetName val="工时统计"/>
-      <sheetName val="21710103"/>
-      <sheetName val="2171010501"/>
-      <sheetName val="2171010502"/>
-      <sheetName val="217102"/>
-      <sheetName val="流资汇总"/>
-      <sheetName val="披露表(国资)"/>
-      <sheetName val="sell"/>
-      <sheetName val="fin"/>
-      <sheetName val="Validation"/>
-      <sheetName val="_x005f_x005f_x005f_x005f_x005f_x005f_x005f_x0000__x005f"/>
-      <sheetName val="Plan"/>
-      <sheetName val="A"/>
-      <sheetName val="递延税款Dy"/>
-      <sheetName val="所得税Dy"/>
-      <sheetName val="股本Dy"/>
-      <sheetName val="资本公积Dy"/>
-      <sheetName val="盈余公积Dy"/>
-      <sheetName val="投资收益Dy"/>
-      <sheetName val="长期股权投资Dy"/>
-      <sheetName val="Payroll"/>
-      <sheetName val="逾龄"/>
-      <sheetName val="役龄"/>
-      <sheetName val="原材料"/>
-      <sheetName val="封面"/>
-      <sheetName val="院级设计"/>
-      <sheetName val="BS"/>
-      <sheetName val="CE"/>
-      <sheetName val="IS"/>
-      <sheetName val="FS"/>
-      <sheetName val="gl"/>
-      <sheetName val="C01-1"/>
-      <sheetName val="审计工作底稿目录"/>
-      <sheetName val="P1012001"/>
-      <sheetName val="cs"/>
-      <sheetName val="科目名称表"/>
-      <sheetName val="_x005f_x005f_x005f_x0000__x005f"/>
-      <sheetName val="A430"/>
-      <sheetName val="dep08"/>
-      <sheetName val="利润分析"/>
-      <sheetName val="资产负债分析"/>
-      <sheetName val="4-货币资金-现金"/>
-      <sheetName val="2006年TB"/>
-      <sheetName val="其他应收款明细表"/>
-      <sheetName val="补充信息"/>
-      <sheetName val="明细表D4-2-1（行业）"/>
-      <sheetName val="应交税费审定表"/>
-      <sheetName val="dxnsjtempsheet"/>
-      <sheetName val="销售6.13"/>
-      <sheetName val="役"/>
-      <sheetName val="应付账款明细BS.09 "/>
-      <sheetName val="CF附注"/>
-      <sheetName val="其他应付款Dy"/>
-      <sheetName val="附注汇总"/>
-      <sheetName val="细节测试审计抽样"/>
-      <sheetName val="长期借款Dy"/>
-      <sheetName val="原TB表"/>
-      <sheetName val="其他应收款Dy"/>
-      <sheetName val="货币资金审定表"/>
-      <sheetName val="试算"/>
-      <sheetName val="财务费用Dy"/>
-      <sheetName val="FX"/>
-      <sheetName val="Input_Hide"/>
-      <sheetName val="Oct"/>
-      <sheetName val="界面"/>
-      <sheetName val="1999TL"/>
-      <sheetName val="PL配賦明細"/>
-      <sheetName val="折旧表2006年1-6月"/>
-      <sheetName val="Spreadsheet"/>
-      <sheetName val="每月資料"/>
-      <sheetName val="T.B."/>
-      <sheetName val="Inhalt"/>
-      <sheetName val="2008.02T.B."/>
-      <sheetName val="whw5r"/>
-      <sheetName val="06"/>
-      <sheetName val="2008年2月"/>
-      <sheetName val="Index"/>
-      <sheetName val="MasterList"/>
-      <sheetName val="管理费用Dy"/>
-      <sheetName val="坏账准备_其他应收款Dy"/>
-      <sheetName val="其他应收款Mx"/>
-      <sheetName val="10-12"/>
-      <sheetName val="附表6"/>
-      <sheetName val="其他应收款分录表"/>
-      <sheetName val="Pre-operating Exp"/>
-      <sheetName val="Miscellaneous Exp."/>
-      <sheetName val="Rental 2002"/>
-      <sheetName val="Rental 2001"/>
-      <sheetName val="base"/>
-      <sheetName val="J&amp;Q"/>
-      <sheetName val="2005余额表"/>
-      <sheetName val="Mp-team 1"/>
-      <sheetName val="天合与太阳时代的往来余额(天合账面)"/>
-      <sheetName val="关联交易-存款"/>
-      <sheetName val="param"/>
-      <sheetName val="cov"/>
-      <sheetName val="ZI-1存货余额表 "/>
-      <sheetName val="ZI封面"/>
-      <sheetName val="ZI-0调整分录 "/>
-      <sheetName val="应付账款Dy"/>
-      <sheetName val="应付账款mx"/>
-      <sheetName val="待摊费用mx"/>
-      <sheetName val="固定资产减值准备mx"/>
-      <sheetName val="累计折旧mx"/>
-      <sheetName val="应付福利费mx"/>
-      <sheetName val="应付工资mx"/>
-      <sheetName val="预提费用mx"/>
-      <sheetName val="在建工程mx"/>
-      <sheetName val="制造费用mx"/>
-      <sheetName val="主营业务成本mx"/>
-      <sheetName val="应收账款Dy"/>
-      <sheetName val="UFPrn20080707101342"/>
-      <sheetName val="预付款项"/>
-      <sheetName val="其他应付款"/>
-      <sheetName val="其他应收款"/>
-      <sheetName val="报表格式"/>
-      <sheetName val="Consolidation TB"/>
-      <sheetName val="应收帐款"/>
-      <sheetName val="83套公房"/>
-      <sheetName val="固定资产审定表"/>
-      <sheetName val="固定资产减少检查表"/>
-      <sheetName val="固定资产盘点检查情况表"/>
-      <sheetName val="固定资产增加检查表"/>
-      <sheetName val="审定表"/>
-      <sheetName val="折旧计算检查表"/>
-      <sheetName val="长期股权投资明细表"/>
-      <sheetName val="无形资产凭证抽查表"/>
-      <sheetName val="枚举字典"/>
-      <sheetName val="吴江评估增值摊销"/>
-      <sheetName val="青岛泰信评估增值摊销"/>
-      <sheetName val="石油设备评估增值摊销"/>
-      <sheetName val="未实现毛利"/>
-      <sheetName val="Equity Movement"/>
-      <sheetName val="非经常性损益"/>
-      <sheetName val="MI"/>
-      <sheetName val="NFC TB"/>
-      <sheetName val="其他货币资金.dbf"/>
-      <sheetName val="银行存款.dbf"/>
-      <sheetName val="吴江"/>
-      <sheetName val="UFPrn20031203195053"/>
-      <sheetName val="_x0000__x0000__x0000__x0000__x0"/>
-      <sheetName val="提足折旧"/>
-      <sheetName val="_x005f_x005f_x005f_x005f_x005f_x005f_x005f_x005f_x005f_x005f_"/>
-      <sheetName val="_x005f_x005f_x005f_x005f_"/>
-      <sheetName val="财务成本"/>
-      <sheetName val="SysNavigation"/>
-      <sheetName val="BlsPrvOpv"/>
-      <sheetName val="其他应付款 "/>
-      <sheetName val="项目信息"/>
-      <sheetName val="生产成本及销售成本倒轧表"/>
-      <sheetName val="低值易耗品"/>
-      <sheetName val="loan database"/>
-      <sheetName val="试算2019"/>
-      <sheetName val="邻酮定乙酚发出测试"/>
-      <sheetName val="ACCOUNT LIST"/>
-      <sheetName val="HEADER"/>
-      <sheetName val="E1"/>
-      <sheetName val="Parameters"/>
-      <sheetName val="E-15"/>
-      <sheetName val="Ex. rate"/>
-      <sheetName val="Conversion to EUR"/>
-      <sheetName val="J300"/>
-      <sheetName val="mf-f"/>
-      <sheetName val="版权方2004年度频道分布总表"/>
-      <sheetName val="Input"/>
-      <sheetName val="TYPE"/>
-      <sheetName val="Actual (n)"/>
-      <sheetName val="报表项目列表"/>
-      <sheetName val="D3"/>
-      <sheetName val="报表项目"/>
-      <sheetName val="披露表(上市)"/>
-      <sheetName val="总公司2002.12.31"/>
-      <sheetName val="固定资产2006"/>
-      <sheetName val="Chart of Account"/>
-      <sheetName val="应付帐款"/>
-      <sheetName val="Workings"/>
-      <sheetName val="BDbilling"/>
-      <sheetName val="目录"/>
-      <sheetName val="库存商品"/>
-      <sheetName val="名称"/>
-      <sheetName val="存货Dy"/>
-      <sheetName val="BNWXVLNN"/>
-      <sheetName val="敏感参数"/>
-      <sheetName val="_x005f_x0000__x005f"/>
-      <sheetName val="广州库"/>
-      <sheetName val="_x005f_x005f_x005f_x0000__x005f_x005f_x005f_x0000__x0_2"/>
-      <sheetName val="Sheet2"/>
-      <sheetName val="4-2长投债券"/>
-      <sheetName val="3流资汇总"/>
-      <sheetName val="M2"/>
-      <sheetName val="专项应付款Dy"/>
-      <sheetName val="营业外支出Dy"/>
-      <sheetName val="应收账款Mx"/>
-      <sheetName val="Director"/>
-      <sheetName val="p.5, bank int income"/>
-      <sheetName val="Menu"/>
-      <sheetName val="conWP"/>
-      <sheetName val="conBS"/>
-      <sheetName val="conCE"/>
-      <sheetName val="conCF"/>
-      <sheetName val="conIS"/>
-      <sheetName val="母公司TB"/>
-      <sheetName val="_"/>
-      <sheetName val="主菜单"/>
-      <sheetName val="校对"/>
-      <sheetName val="AJE23#"/>
-      <sheetName val="FLdeleted"/>
-      <sheetName val="存货_库存商品Dy"/>
-      <sheetName val="长期股权投资Mx"/>
-      <sheetName val="应付福利费Dy"/>
-      <sheetName val="UFPrn20040104084034"/>
-      <sheetName val="_x005f_x0000__x005f_x0000__x005f_x0000__x005f_x0000___2"/>
-      <sheetName val="关键控制测试表"/>
-      <sheetName val="科目余额表"/>
-      <sheetName val="房屋类"/>
-      <sheetName val="合并"/>
-      <sheetName val="UFPrn20031114182129"/>
-      <sheetName val="27-7"/>
-      <sheetName val="管理费用明细表(2001年)"/>
-      <sheetName val="帐务资料"/>
-      <sheetName val="电子"/>
-      <sheetName val="未安排订单（集团）"/>
-      <sheetName val="工企资产负债表"/>
-      <sheetName val="暂估"/>
-      <sheetName val="凭证核对内容"/>
-      <sheetName val="_x0000__x0000__x005"/>
-      <sheetName val="PRC 13"/>
-      <sheetName val="二级明细"/>
-      <sheetName val="其他应收-导出"/>
-      <sheetName val="隐藏页"/>
-      <sheetName val="发出计价汇总－库存商品"/>
-      <sheetName val="Administration"/>
-      <sheetName val="master"/>
-      <sheetName val="房屋及建筑物"/>
-      <sheetName val="Traduction"/>
-      <sheetName val="Catalogo Roca 1Oct'01"/>
-      <sheetName val="_5081"/>
-      <sheetName val="企业编码"/>
-      <sheetName val="Open"/>
-      <sheetName val="R&amp;P"/>
-      <sheetName val="Energy Variance"/>
-      <sheetName val="Section"/>
-      <sheetName val="TT04"/>
-      <sheetName val="Profit and Loss"/>
-      <sheetName val="申报表封面"/>
-      <sheetName val="基础条件"/>
-      <sheetName val="ENT"/>
-      <sheetName val="FTHL"/>
-      <sheetName val="GX"/>
-      <sheetName val="IN"/>
-      <sheetName val="ITCD"/>
-      <sheetName val="LVLT"/>
-      <sheetName val="MFNX"/>
-      <sheetName val="NOPT"/>
-      <sheetName val="TCM"/>
-      <sheetName val="TSIX"/>
-      <sheetName val="WCG"/>
-      <sheetName val="Added Detail List"/>
-      <sheetName val="1_12月"/>
-      <sheetName val="11月"/>
-      <sheetName val="12月"/>
-      <sheetName val="PS"/>
-      <sheetName val="01"/>
-      <sheetName val="010"/>
-      <sheetName val="011"/>
-      <sheetName val="012"/>
-      <sheetName val="02"/>
-      <sheetName val="03"/>
-      <sheetName val="04"/>
-      <sheetName val="05"/>
-      <sheetName val="07"/>
-      <sheetName val="08"/>
-      <sheetName val="09"/>
-      <sheetName val="总账余额"/>
-      <sheetName val="调整分录"/>
-      <sheetName val="调整分录汇总"/>
-      <sheetName val="F101"/>
-      <sheetName val="I151-10"/>
-      <sheetName val="TB2005"/>
-      <sheetName val="A.R 01"/>
-      <sheetName val="17应付票据明细表"/>
-      <sheetName val="列表"/>
-      <sheetName val="科目名称"/>
-      <sheetName val="应付账款明细表"/>
-      <sheetName val="List"/>
-      <sheetName val="Ref"/>
-      <sheetName val="This year-Budget-20092010"/>
-      <sheetName val="FA"/>
-      <sheetName val="GZ4-1审定表"/>
-      <sheetName val="BT 03"/>
-      <sheetName val="BT 02"/>
-      <sheetName val="BT 01"/>
-      <sheetName val="FF-6"/>
-      <sheetName val="EJE-PRC"/>
-      <sheetName val="EJE-HK"/>
-      <sheetName val="明细台帐"/>
-      <sheetName val="固定资产(原表)"/>
-      <sheetName val="Economic evaluation - FY98 base"/>
-      <sheetName val="AFEMAI"/>
-      <sheetName val="Detail Loan Move. &amp; Listing"/>
-      <sheetName val="原材料发出计价测试-OK"/>
-      <sheetName val="审定表L2"/>
-      <sheetName val="选择报表"/>
-      <sheetName val="KEY"/>
-      <sheetName val="ES Table"/>
-      <sheetName val="材料"/>
-      <sheetName val="外销"/>
-      <sheetName val="AP"/>
-      <sheetName val="NPBOC"/>
-      <sheetName val="NPIC"/>
-      <sheetName val="余额表"/>
-      <sheetName val="PPE"/>
-      <sheetName val="Labor cost"/>
-      <sheetName val="04收发存汇总表"/>
-      <sheetName val="应收帐龄OK"/>
-      <sheetName val="外销涤布"/>
-      <sheetName val="业务登记表"/>
-      <sheetName val="Pfile"/>
-      <sheetName val="备忘录"/>
-      <sheetName val="05.7工资分析"/>
-      <sheetName val="2019财务收发存"/>
-      <sheetName val="2019库存收发存"/>
-      <sheetName val="_formula_"/>
-      <sheetName val="明细分类账"/>
-      <sheetName val="关联方—创斯达"/>
-      <sheetName val="关联方—东风汽车"/>
-      <sheetName val="1月固定资产清单"/>
-      <sheetName val="库存商品余额表.dbf"/>
-      <sheetName val="08现金流量底稿"/>
-      <sheetName val="09现金流量底稿"/>
-      <sheetName val="Collateral"/>
-      <sheetName val="Disposition"/>
-      <sheetName val="控制测试样本量"/>
-      <sheetName val="广告费和业务宣传费表"/>
-      <sheetName val="资产减值准备表"/>
-      <sheetName val="工资薪金表"/>
-      <sheetName val="投资收益表"/>
-      <sheetName val="附件(excel）"/>
-      <sheetName val="业务招待费表"/>
-      <sheetName val="利润及分配表"/>
-      <sheetName val="资产方"/>
-      <sheetName val="减值准备表"/>
-      <sheetName val="负债方"/>
-      <sheetName val="表2.1_自查情况汇总表（按税种）"/>
-      <sheetName val="2003本部资产负债试算表"/>
-      <sheetName val="2003本部利润及利润分配表试算表"/>
-      <sheetName val="301主营收入 "/>
-      <sheetName val="307销售费用"/>
-      <sheetName val="316营外收入"/>
-      <sheetName val="306税金附加"/>
-      <sheetName val="DTCT"/>
-      <sheetName val="GiaVL"/>
-      <sheetName val="Thuc thanh"/>
-      <sheetName val="财务费用表"/>
-      <sheetName val="营业外支出表"/>
-      <sheetName val="视同销售成本表"/>
-      <sheetName val="管理费用表"/>
-      <sheetName val="利息支出表"/>
-      <sheetName val="其他业务支出表"/>
-      <sheetName val="生产成本表"/>
-      <sheetName val="成本费用表"/>
-      <sheetName val="制造费用表"/>
-      <sheetName val="G.1R-Shou COP Gf"/>
-      <sheetName val="原材料收发"/>
-      <sheetName val="分录汇总表"/>
-      <sheetName val="#511BkRec"/>
-      <sheetName val="#511-SEPT97"/>
-      <sheetName val="#511-OCT97"/>
-      <sheetName val="#511-NOV97"/>
-      <sheetName val="#511-DEC97"/>
-      <sheetName val="NRV2"/>
-      <sheetName val="dentaltable"/>
-      <sheetName val="E15-AFL"/>
-      <sheetName val="CODE"/>
-      <sheetName val="BKD"/>
-      <sheetName val="dm"/>
-      <sheetName val="MB51"/>
-      <sheetName val="nada"/>
-      <sheetName val="Nov,01"/>
-      <sheetName val="Category"/>
-      <sheetName val="明细表"/>
-      <sheetName val="08.8"/>
-      <sheetName val="TB表"/>
-      <sheetName val="科目余额表1"/>
-      <sheetName val="xbase"/>
-      <sheetName val="现金流量表"/>
-      <sheetName val="Dept"/>
-      <sheetName val="JA#1"/>
-      <sheetName val="JA#2&amp;5"/>
-      <sheetName val="A3"/>
-      <sheetName val="选择选项"/>
-      <sheetName val="Holidays"/>
-      <sheetName val="C4-"/>
-      <sheetName val="工程汇总表"/>
-      <sheetName val="Non-Statistical Sampling Master"/>
-      <sheetName val="2013年合并试算"/>
-      <sheetName val="销售预测表"/>
-      <sheetName val="信息说明"/>
-      <sheetName val="4.科目余额表（末级）"/>
-      <sheetName val="其他业务利润"/>
-      <sheetName val="其他材料收入重复"/>
-      <sheetName val="其他材料收入账"/>
-      <sheetName val="预收"/>
-      <sheetName val="A投资指标"/>
-      <sheetName val="Z控制表"/>
-      <sheetName val="K流量表过渡"/>
-      <sheetName val="O售价敏感分析"/>
-      <sheetName val="给排水工程量计算书"/>
-      <sheetName val="2004电器设备"/>
-      <sheetName val="2004电子设备"/>
-      <sheetName val="2004房屋建筑物"/>
-      <sheetName val="2004家具"/>
-      <sheetName val="2004通用设备"/>
-      <sheetName val="2004土地"/>
-      <sheetName val="2004仪器仪表"/>
-      <sheetName val="2004运输设备"/>
-      <sheetName val="2004专用设备"/>
-      <sheetName val="存货跌价准备Dy"/>
-      <sheetName val="基本生产成本"/>
-      <sheetName val="销售出库序时簿"/>
-      <sheetName val="F1"/>
-      <sheetName val="应收款项审定表"/>
-      <sheetName val="T  B"/>
-      <sheetName val="信息"/>
-      <sheetName val="坏账准备计算表"/>
-      <sheetName val="功能范围"/>
-      <sheetName val="2.1.CM6150(导入)"/>
-      <sheetName val="tot"/>
-      <sheetName val=" "/>
-      <sheetName val="Sheet9"/>
-      <sheetName val="上报资产负债表"/>
-      <sheetName val="上报损益表"/>
-      <sheetName val="现金流量表（月报）"/>
-      <sheetName val="补充表"/>
-      <sheetName val="2013调整分录"/>
-      <sheetName val="2012调整分录"/>
-      <sheetName val="项目索引"/>
-      <sheetName val="2009调整分录"/>
-      <sheetName val="Macro1"/>
-      <sheetName val="외주현황.wq1"/>
-      <sheetName val="생산"/>
-      <sheetName val="진도현황"/>
-      <sheetName val="自定义名称"/>
-      <sheetName val="ARP-U501"/>
-      <sheetName val="Sales for 2001"/>
-      <sheetName val="ws9"/>
-      <sheetName val="INVDAYS"/>
-      <sheetName val="_x005f_x0000__x005f_x0000__x0_2"/>
-      <sheetName val="Within"/>
-      <sheetName val="accounting"/>
-      <sheetName val="非保稅"/>
-      <sheetName val="工资表"/>
-      <sheetName val="个人所得税表"/>
-      <sheetName val="薪酬标准"/>
-      <sheetName val="人员信息表"/>
-      <sheetName val="员工银行账号明细表"/>
-      <sheetName val="Logic"/>
-      <sheetName val="入库分类"/>
-      <sheetName val="其他应收款坏账准备"/>
-      <sheetName val="全年折旧"/>
-      <sheetName val="SP"/>
-      <sheetName val="合并2"/>
-      <sheetName val="GT_Custom"/>
-      <sheetName val="CONSOL"/>
-      <sheetName val="序时账"/>
-      <sheetName val="开发成本审核表"/>
-      <sheetName val="固定资产及折旧审核表"/>
-      <sheetName val="坏帐准备金审核表"/>
-      <sheetName val="长期待摊费用摊销审核表"/>
-      <sheetName val="无形资产摊销审核表"/>
-      <sheetName val="投资审核表"/>
-      <sheetName val="Links"/>
-      <sheetName val="库存股Dy"/>
-      <sheetName val="时间设置"/>
-      <sheetName val="成本日报(4-10)"/>
-      <sheetName val="凤一"/>
-      <sheetName val="交易性金融资产Dy"/>
-      <sheetName val="应付票据Dy"/>
-      <sheetName val="VV"/>
-      <sheetName val="YH1"/>
-      <sheetName val="1461（12.6）"/>
-      <sheetName val="选项清单列表（不归档）"/>
-      <sheetName val="9200"/>
-      <sheetName val="起"/>
-      <sheetName val="止"/>
-      <sheetName val="合并试算表"/>
-      <sheetName val="dklx"/>
-      <sheetName val="应付职工薪酬14"/>
-      <sheetName val="应交税费15"/>
-      <sheetName val="Part_Datum"/>
-      <sheetName val="CAUDIT"/>
-      <sheetName val="ARP"/>
-      <sheetName val="风险分类"/>
-      <sheetName val="表头和填表说明"/>
-      <sheetName val="关联方"/>
-      <sheetName val="K1 Tax computation"/>
-      <sheetName val="外地"/>
-      <sheetName val="坯布"/>
-      <sheetName val="表二十九1（01）"/>
-      <sheetName val="UFPrn20050217103510"/>
-      <sheetName val="明细表2017"/>
-      <sheetName val="_x005f_x005f_x005f_x005f_x005f_x005f_x005f_x005f_"/>
-      <sheetName val="余额表李"/>
-      <sheetName val="科目代码"/>
-      <sheetName val="银行存款核对表"/>
-      <sheetName val="Sheet1 (11)"/>
-      <sheetName val="科目清单"/>
-      <sheetName val="固定资产折旧表"/>
-      <sheetName val="会计科目表"/>
-      <sheetName val="审计标识"/>
-      <sheetName val="ｻﾌﾟﾗｲﾔｰﾘｽﾄ"/>
-      <sheetName val="Rental PIT"/>
-      <sheetName val="Sample test"/>
-      <sheetName val="Business tax PIT"/>
-      <sheetName val="Professional fee"/>
-      <sheetName val="九、开发成本G2-2-9"/>
-      <sheetName val="八、开发产品G2-2-8"/>
-      <sheetName val="四、自制半成品明细表G2-2-4"/>
-      <sheetName val="七、发出商品G2-2-7"/>
-      <sheetName val="一、原材料明细表G2-2-1"/>
-      <sheetName val="二、材料采购、在途物资明细表G2-2-2"/>
-      <sheetName val="三、周转材料、低值易耗品，包装物明细表G2-2-3"/>
-      <sheetName val="六、库存商品明细表G2-2-6"/>
-      <sheetName val="福利费1"/>
-      <sheetName val="营业费用02"/>
-      <sheetName val="799"/>
-      <sheetName val="存货明细汇总表"/>
-      <sheetName val="G2-2存货明细汇总表"/>
-      <sheetName val="上年PL审定"/>
-      <sheetName val="补贴收入明细表"/>
-      <sheetName val="A2-1试算"/>
-      <sheetName val="待摊费用明细表"/>
-      <sheetName val="长期借款明细表1"/>
-      <sheetName val="末"/>
-      <sheetName val="截至2004年10月31日存货材料清单"/>
-      <sheetName val="TONGKE-HT"/>
-      <sheetName val="代码"/>
-      <sheetName val="dropdowns"/>
-      <sheetName val="_x005f_x005f_"/>
-      <sheetName val="MUS"/>
-      <sheetName val="报表项目名称"/>
-      <sheetName val="move"/>
-      <sheetName val="General"/>
-      <sheetName val="Planning"/>
-      <sheetName val="Individually Significant Items"/>
-      <sheetName val="Summary (Quanzhou)"/>
-      <sheetName val="Summary (Shenyang standalone) "/>
-      <sheetName val="首页"/>
-      <sheetName val="参数维护"/>
-      <sheetName val="N2720 当期非经常性损益明细表"/>
-      <sheetName val="Summary (Wuhan)"/>
-      <sheetName val="Setting"/>
-      <sheetName val="General "/>
-      <sheetName val="Lists"/>
-      <sheetName val="Elements"/>
-      <sheetName val="30.09.2017"/>
-      <sheetName val="SW-TEO"/>
-      <sheetName val="Malasia"/>
-      <sheetName val="103105"/>
-      <sheetName val="HR"/>
-      <sheetName val="利润表验证表"/>
-      <sheetName val="Prepaid expenses-Wendy"/>
-      <sheetName val="TB 1999-2000"/>
-      <sheetName val="Sheet4"/>
-      <sheetName val="研发项目"/>
-      <sheetName val="资金计划项目说明"/>
-      <sheetName val="生产入库04"/>
-      <sheetName val="현금경비중역"/>
-      <sheetName val="TCalc"/>
-      <sheetName val="Threshold Cal"/>
-      <sheetName val="작성양식"/>
-      <sheetName val="_x0000__x005f"/>
-      <sheetName val="_x0000__x0000__x0000__x0000___2"/>
-      <sheetName val="_x0000__x0000__x0_2"/>
-      <sheetName val="重要性水平"/>
-      <sheetName val="银行列表"/>
-      <sheetName val="收入明细－按客户"/>
-      <sheetName val="数量金额总账"/>
-      <sheetName val="销售费用Dy"/>
-      <sheetName val="J411"/>
-      <sheetName val="J412"/>
-      <sheetName val="Customize Your Loan Manager"/>
-      <sheetName val="Marco"/>
-      <sheetName val="C - Cash and Bank"/>
-      <sheetName val="A300"/>
-      <sheetName val="Group"/>
-      <sheetName val="07TB"/>
-      <sheetName val="AR Breakdown&amp;Aging"/>
-      <sheetName val="AP Breakdown &amp; Aging"/>
-      <sheetName val="测算表"/>
-      <sheetName val="坏账准备_预付账款Dy"/>
-      <sheetName val="清冊"/>
-      <sheetName val="JA"/>
-      <sheetName val="Dis."/>
-      <sheetName val="账户汇总表_2017年1月至12月_"/>
-      <sheetName val="应收账款明细表"/>
-      <sheetName val="Income tax reconciliation"/>
-      <sheetName val="销项税"/>
-      <sheetName val="能耗计算 OK "/>
-      <sheetName val="BKD-氢能"/>
-      <sheetName val="for disclosure"/>
-      <sheetName val="Final"/>
-      <sheetName val="2008 SPL"/>
-      <sheetName val="OB97LST"/>
-      <sheetName val="WIP(For Nick)"/>
-      <sheetName val="Admin"/>
-      <sheetName val="WO CONV"/>
-      <sheetName val="ACTINV"/>
-      <sheetName val="无形资产"/>
-      <sheetName val="长期待摊费用"/>
-      <sheetName val="应交税金"/>
-      <sheetName val="Detail P&amp;L"/>
-      <sheetName val="CAPEX-KEuro"/>
-      <sheetName val="code_note"/>
-      <sheetName val="数据模板1"/>
-      <sheetName val="1_主营业务收入"/>
-      <sheetName val="其他应收"/>
-      <sheetName val="应收"/>
-      <sheetName val="预付"/>
-      <sheetName val="其他非流动资产合并抵消明细"/>
-      <sheetName val="其他应收款－个人借款明细"/>
-      <sheetName val="2017_6_30记6号"/>
-      <sheetName val="Cashbook"/>
-      <sheetName val="期初应付帐款明细表G4-2 "/>
-      <sheetName val="科目"/>
-      <sheetName val="资产负债表利润及利润分配表"/>
-      <sheetName val="操作页"/>
-      <sheetName val="核算项目组合表"/>
-      <sheetName val="公司名称一览表"/>
-      <sheetName val="A140-10"/>
-      <sheetName val="其他应付款明细表M4-2 21"/>
-      <sheetName val="其他应付款明细表M4-2 20"/>
-      <sheetName val="2020年调整分录"/>
-      <sheetName val="2019年调整分录 "/>
-      <sheetName val="数据源"/>
-      <sheetName val="十一、消耗性生物资产G2-2-11"/>
-      <sheetName val="画底稿使用"/>
-      <sheetName val="原报表"/>
-      <sheetName val="调整后报表"/>
-      <sheetName val="收入成本审定表D4试剂"/>
-      <sheetName val="审计说明M4-0"/>
-      <sheetName val="库存商品库龄分析G2-3-3"/>
-      <sheetName val="Listen"/>
-      <sheetName val="Breakdown-本部"/>
-      <sheetName val="预付账款汇总表"/>
-      <sheetName val="审计调整"/>
-      <sheetName val="银行存款明细表"/>
-      <sheetName val="管理"/>
-      <sheetName val="P1"/>
-      <sheetName val="Bilanz"/>
-      <sheetName val="Personal"/>
-      <sheetName val="commentary"/>
-      <sheetName val="Cash of Company"/>
-      <sheetName val="tax payable"/>
-      <sheetName val="209zt"/>
-      <sheetName val="115zt"/>
-      <sheetName val="11901zt"/>
-      <sheetName val="EXP"/>
-      <sheetName val="B7-2-1应付账款余额表"/>
-      <sheetName val="主营成本"/>
-      <sheetName val="Start"/>
-      <sheetName val="初始设定"/>
-      <sheetName val="固定资产、累计折旧、减值准备明细表"/>
-      <sheetName val="现金流量1-10月"/>
-      <sheetName val="基础资料（B）"/>
-      <sheetName val="投资性房地产Dy"/>
-      <sheetName val="表5_2_3固定资产—电子设备"/>
-      <sheetName val="0609"/>
-      <sheetName val="发出商品替代"/>
-      <sheetName val="2007.11PPR管件单件测算"/>
-      <sheetName val="应付账款 (2)"/>
-      <sheetName val="Sheet140"/>
-      <sheetName val="预收账款明细表D3-2"/>
-      <sheetName val="J"/>
-      <sheetName val="应付股利Dy"/>
-      <sheetName val="预提费用Dy"/>
-      <sheetName val="2008年1月"/>
-      <sheetName val="2007年12月  "/>
-      <sheetName val="商保"/>
-      <sheetName val="现流表（附表）黄"/>
-      <sheetName val="3. Textile"/>
-      <sheetName val="6200B-32应付职工薪酬勾稽表T"/>
-      <sheetName val="冻品入库"/>
-      <sheetName val="鸡油车间"/>
-      <sheetName val="应交税金Dy"/>
-      <sheetName val="应收出口退税mx"/>
-      <sheetName val="其他应交款Dy"/>
-      <sheetName val="主营业务收入Dy"/>
-      <sheetName val="유통망계획"/>
-      <sheetName val="财务费用mx"/>
-      <sheetName val="其他应付款Mx"/>
-      <sheetName val="营业外支出Mx"/>
-      <sheetName val="未分配利润Dy"/>
-      <sheetName val="补贴收入Dy"/>
-      <sheetName val="坏账准备_应收账款Dy"/>
-      <sheetName val="预收账款Dy"/>
-      <sheetName val="坏账准备_应收账款Mx"/>
-      <sheetName val="Company"/>
-      <sheetName val="主营业务税金及附加Dy"/>
-      <sheetName val="其他业务利润Dy"/>
-      <sheetName val="营业费用Dy"/>
-      <sheetName val="应收票据Dy"/>
-      <sheetName val="程序表原始数据"/>
-      <sheetName val="个所税"/>
-      <sheetName val="企业所得税"/>
-      <sheetName val="票7)"/>
-      <sheetName val="无形资产Dy"/>
-      <sheetName val="无形资产减值准备Dy"/>
-      <sheetName val="应收补贴款Dy"/>
-      <sheetName val="其他流动资产Dy"/>
-      <sheetName val="内部往来Dy"/>
-      <sheetName val="长期待摊费用Dy"/>
-      <sheetName val="管理费用mx"/>
-      <sheetName val="6200B-8社保缴交人数核对"/>
-      <sheetName val="payroll "/>
-      <sheetName val="发生额 (2)"/>
-      <sheetName val="主营业务收入mx"/>
-      <sheetName val="TB98"/>
-      <sheetName val="FA3-5"/>
-      <sheetName val="FA3-4"/>
-      <sheetName val="TB MAR2004"/>
-      <sheetName val="生产成本Dy"/>
-      <sheetName val="原报调整分录"/>
-      <sheetName val="审计调整分录"/>
-      <sheetName val="已审CF"/>
-      <sheetName val="基础"/>
-      <sheetName val="conWP1"/>
-      <sheetName val="20071-10月原材料发出计价测试(不打)"/>
-      <sheetName val="投资收益Mx"/>
-      <sheetName val="200712"/>
-      <sheetName val="注释汇总"/>
-      <sheetName val="设备部房屋"/>
-      <sheetName val="definition"/>
-      <sheetName val="SW"/>
-      <sheetName val="JDMCode"/>
-      <sheetName val="PanelInfo"/>
-      <sheetName val="00 FG breakdown"/>
-      <sheetName val="01 FG breakdown"/>
-      <sheetName val="99 FG breakdown"/>
-      <sheetName val="电动车间"/>
-      <sheetName val="5132"/>
-      <sheetName val="披露表（上市）"/>
-      <sheetName val="科目余额表正式"/>
-      <sheetName val="Namelist"/>
-      <sheetName val="会计科目"/>
-      <sheetName val="审定_资产负债表"/>
-      <sheetName val="未审_资产负债表"/>
-      <sheetName val="Tfc&amp;toll asmptns"/>
-      <sheetName val="G1-1-1a AR-85A"/>
-      <sheetName val="浙江道之-机器设备"/>
-      <sheetName val="Dates"/>
-      <sheetName val="Sheet113"/>
-      <sheetName val="合并TB-19年"/>
-      <sheetName val="审计程序"/>
-      <sheetName val="披露表(上市)-2016"/>
-      <sheetName val="替代结果汇总表"/>
-      <sheetName val="固定资产"/>
-      <sheetName val="专项应付款Mx"/>
-      <sheetName val="应付工资Dy"/>
-      <sheetName val="UFPrn20071013211250"/>
-      <sheetName val="D4-1营业收入审定表"/>
-      <sheetName val="函证汇总表 G4-4-1"/>
-      <sheetName val="发货单列表"/>
-      <sheetName val="凭证测试（固硫）"/>
-      <sheetName val="应收(帐面数)"/>
-      <sheetName val="出租开发产品明细"/>
-      <sheetName val="Sheet132"/>
-      <sheetName val="Sheet555"/>
-      <sheetName val="Sheet659"/>
-      <sheetName val="Sheet703"/>
-      <sheetName val="補充資料-10030 asset list"/>
-      <sheetName val="新城资金明细"/>
-      <sheetName val="申鑫大厦租金明细"/>
-      <sheetName val="三林明细"/>
-      <sheetName val="东陆明细"/>
-      <sheetName val="D2-7本期应收结算单查验"/>
-      <sheetName val="2021明细表D2-2 "/>
-      <sheetName val="销售单价公允性"/>
-      <sheetName val="预收帐款"/>
-      <sheetName val="面积指标"/>
-      <sheetName val="酒店"/>
-      <sheetName val="P&amp;L Summary Page"/>
-      <sheetName val="应付(单位)关注"/>
-      <sheetName val="日照"/>
-      <sheetName val="德州"/>
-      <sheetName val="滨州"/>
-      <sheetName val="淄博"/>
-      <sheetName val="大鲁"/>
-      <sheetName val="威海"/>
-      <sheetName val="山东省互联网传媒集团应收账款（账龄统计）统计数据"/>
-      <sheetName val="张淑东"/>
-      <sheetName val="Master Data"/>
-      <sheetName val="含量"/>
-      <sheetName val="Sheet137"/>
-      <sheetName val="Sheet367"/>
-      <sheetName val="UFPrn20200415105500"/>
-      <sheetName val="ITEM"/>
-      <sheetName val="明细表J8-1"/>
-      <sheetName val="11、对外开证"/>
-      <sheetName val="财务费用"/>
-      <sheetName val="投资收益"/>
-      <sheetName val="B1-1001"/>
-      <sheetName val="资债比较原"/>
-      <sheetName val="Dropdown Category"/>
-      <sheetName val="98调整分录表"/>
-      <sheetName val="大楼分录"/>
-      <sheetName val="凤县折旧测算"/>
-      <sheetName val="Table"/>
-      <sheetName val="产品销售毛利表"/>
-      <sheetName val="苏州天山 - 待摊费用余额表明细"/>
-      <sheetName val="支出原材料"/>
-      <sheetName val="收入原料"/>
-      <sheetName val="tax comp"/>
-      <sheetName val="PY-pp"/>
-      <sheetName val="PRC 15"/>
-      <sheetName val="Sheet152"/>
-      <sheetName val="Sheet136"/>
-      <sheetName val="Word附注"/>
-      <sheetName val="2004年度应收账款分析"/>
-      <sheetName val="2020年"/>
-      <sheetName val="主营业务收入明细帐"/>
-      <sheetName val="五矿收入明细帐"/>
-      <sheetName val="现金流量表所需提供的资料"/>
-      <sheetName val="负债试算表"/>
-      <sheetName val="利润及利润分配表试算表"/>
-      <sheetName val="资产试算表"/>
-      <sheetName val="N3 PBT"/>
-      <sheetName val="固资明细"/>
-      <sheetName val="一级"/>
-      <sheetName val="办公设备"/>
-      <sheetName val="会计分录序时簿_2"/>
-      <sheetName val="表1.5"/>
-      <sheetName val="Sheet116"/>
-      <sheetName val="dtct cong"/>
-      <sheetName val="Book 1 Summary"/>
-      <sheetName val="P&amp;L"/>
-      <sheetName val="损益表"/>
-      <sheetName val="番禺管理"/>
-      <sheetName val="通力管理"/>
-      <sheetName val="股份销售费用"/>
-      <sheetName val="股份管理"/>
-      <sheetName val="安福管理"/>
-      <sheetName val="通力销售费用"/>
-      <sheetName val="Sheet112"/>
-      <sheetName val="Sheet615"/>
-      <sheetName val="Sheet616"/>
-      <sheetName val="22"/>
-      <sheetName val="M 67"/>
-      <sheetName val="THEME CODE"/>
-      <sheetName val="CR CODE"/>
-      <sheetName val="부서CODE"/>
-      <sheetName val="系统附加值表"/>
-      <sheetName val="员工工资"/>
-      <sheetName val="Permit"/>
-      <sheetName val="递延所得税负债Dy"/>
-      <sheetName val="主营业务收入审定表D4"/>
-      <sheetName val="明细表D4-2-2(品种）"/>
-      <sheetName val="明细表D4-2-3(地区）"/>
-      <sheetName val="收入毛利分析D4-3-1"/>
-      <sheetName val="月度毛利分析D4-3-2"/>
-      <sheetName val="重要产品毛利分析D4-3-3"/>
-      <sheetName val="重要指标分析D4-3-4"/>
-      <sheetName val="重要客户结构分析D4-3-5"/>
-      <sheetName val="重要客户收入情况分析D4-3-6"/>
-      <sheetName val="产品价格分析D4-3-7"/>
-      <sheetName val="收入确认政策检查D4-4"/>
-      <sheetName val="核实被函证单位信息D4-5-2"/>
-      <sheetName val="函证过程控制D4-5-3"/>
-      <sheetName val="主营业务收入差异调节表检查表D4-5-4"/>
-      <sheetName val="回函核对记录D4-5-5"/>
-      <sheetName val="替代程序表D4-5-6"/>
-      <sheetName val="营业收入完整性测试表D4-7"/>
-      <sheetName val="合同形式检查表D4-8-1"/>
-      <sheetName val="合同履行检查表D4-8-2"/>
-      <sheetName val="明细表D4-2-2(品种）(废)"/>
-      <sheetName val="函证结果汇总表D4-5"/>
-      <sheetName val="营业收入真实性测试表D4-6"/>
-      <sheetName val="绿化养护收入截止测试D4-9"/>
-      <sheetName val="识别未披露的关联方D4-10"/>
-      <sheetName val="姓名汇总D4-10-1"/>
-      <sheetName val="公司高管亲属名单D4-10-2"/>
-      <sheetName val="职工花名册D4-10-3"/>
-      <sheetName val="经销商负责人名单D4-10-4"/>
-      <sheetName val="关联方销售情况及价格公允性检查D4-11"/>
-      <sheetName val="D4-12-1销售退回核查"/>
-      <sheetName val="D14-12-2销售折扣与折让核查"/>
-      <sheetName val="D4-13客户核查清单"/>
-      <sheetName val="D4-13-1电话访谈示例"/>
-      <sheetName val="D4-13-2互联网查询示例"/>
-      <sheetName val="D4-13-3客户走访模板1"/>
-      <sheetName val="D4-13-3客户走访模板2"/>
-      <sheetName val="针对环保局合同及收款核对检查表D4-16 (原,废)"/>
-      <sheetName val="建造合同核查D4-14"/>
-      <sheetName val="工程结算检查表(原D4-9-2)D4-15"/>
-      <sheetName val="绿化养护_环保局项目检查表D4-16-1"/>
-      <sheetName val="绿化养护_其他项目检查表D4-16-2"/>
-      <sheetName val="建造合同核查D4-17(未设公式)"/>
-      <sheetName val="预计总成本、验工计价检查测试 (2017)0305版"/>
-      <sheetName val="预计总成本、验工计价检查测试 (2017)D4-17"/>
-      <sheetName val="工程施工抽盘汇总表D4-18"/>
-      <sheetName val="绿化养护收入情况检查表D4-15"/>
-      <sheetName val="建造合同核查表 "/>
-      <sheetName val="预计总成本、结算项目检查测试"/>
-      <sheetName val="填写参数"/>
-      <sheetName val="Movement "/>
-      <sheetName val="存货汇总表10"/>
-      <sheetName val="销售毛利润汇总表（原始）"/>
-      <sheetName val="制造费用多栏明细账"/>
-      <sheetName val="数量金额明细账"/>
-      <sheetName val="Capital Spending"/>
-      <sheetName val="Sales Analysis"/>
-      <sheetName val="1-資本租賃條件試算"/>
-      <sheetName val="e13100"/>
-      <sheetName val="CNY"/>
-      <sheetName val="USD"/>
-      <sheetName val="x504明细"/>
-      <sheetName val="ACT Cashflow"/>
-      <sheetName val="Program Controls"/>
-      <sheetName val="BS Heading"/>
-      <sheetName val="A104000期间费用明细表"/>
-      <sheetName val="累计1"/>
-      <sheetName val="Sheet91"/>
-      <sheetName val="수리결과"/>
-      <sheetName val="减少资产"/>
-      <sheetName val="6602"/>
-      <sheetName val="2701"/>
-      <sheetName val="Sheet98"/>
-      <sheetName val="NBCF"/>
-      <sheetName val="M Schedules"/>
-      <sheetName val="CCTL"/>
-      <sheetName val="WIP"/>
-      <sheetName val="D2-2-1风险分类"/>
-      <sheetName val="Sheet160"/>
-      <sheetName val="原材料抽查表"/>
-      <sheetName val="试制收入"/>
-      <sheetName val="12月销售成本表(原表)"/>
-      <sheetName val="6125应付职工薪酬"/>
-      <sheetName val="6126-1-2固定资产折旧明细 "/>
-      <sheetName val="Sheet523"/>
-      <sheetName val="Sheet524"/>
-      <sheetName val="报表层次重要性水平"/>
-      <sheetName val="所有者权益(股东权益)变动表(未审)"/>
-      <sheetName val="订单418"/>
-      <sheetName val="I151-40"/>
-      <sheetName val="TB-I"/>
-      <sheetName val="TB-基"/>
-      <sheetName val="税金 "/>
-      <sheetName val="产品入库序时簿"/>
-      <sheetName val="Sheet6"/>
-      <sheetName val="Sheet7"/>
-      <sheetName val="Sheet115"/>
-      <sheetName val="Sheet438"/>
-      <sheetName val="Sheet120"/>
-      <sheetName val="报表11"/>
-      <sheetName val="其它业务收入分类"/>
-      <sheetName val="壓摸穿燈"/>
-      <sheetName val="Rate"/>
-      <sheetName val="校验"/>
-      <sheetName val="上年审前调整"/>
-      <sheetName val="上年审前试算表"/>
-      <sheetName val="本年审前调整"/>
-      <sheetName val="本年审前试算表"/>
-      <sheetName val="审前报表"/>
-      <sheetName val="B15 重要性计算表"/>
-      <sheetName val="N__其他应收款"/>
-      <sheetName val="N__应收账款"/>
-      <sheetName val="N__营业收入及营业成本"/>
-      <sheetName val="附表2关联交易"/>
-      <sheetName val="集团关联方清单"/>
-      <sheetName val="数据有效性"/>
-      <sheetName val="Sheet1 (2)"/>
-      <sheetName val="进料加工汇总信息查询"/>
-      <sheetName val="现调整"/>
-      <sheetName val="（附表2）固定资产处理情况表"/>
-      <sheetName val="科余表"/>
-      <sheetName val="FIRE Parameters"/>
-      <sheetName val="瓶差"/>
-      <sheetName val="本期毛利"/>
-      <sheetName val="余额表数量"/>
-      <sheetName val="_Profile"/>
-      <sheetName val="Acc1"/>
-      <sheetName val="accode"/>
-      <sheetName val="基本情况"/>
-      <sheetName val="上市1"/>
-      <sheetName val="上市2"/>
-      <sheetName val="上市3"/>
-      <sheetName val="上市4"/>
-      <sheetName val="上市5"/>
-      <sheetName val="上市6"/>
-      <sheetName val="上市7"/>
-      <sheetName val="上市8"/>
-      <sheetName val="上市9"/>
-      <sheetName val="合同检查表"/>
-      <sheetName val="银行未达账项明细表"/>
-      <sheetName val="银行存款"/>
-      <sheetName val="Sheet106"/>
-      <sheetName val="合并TB"/>
-      <sheetName val="制造费用明细表"/>
-      <sheetName val="生产成本检查表"/>
-      <sheetName val="销售费用明细表"/>
-      <sheetName val="应收票据明细账"/>
-      <sheetName val="20应收余额"/>
-      <sheetName val="UFPrn20210723144007"/>
-      <sheetName val="Audit Results"/>
-      <sheetName val="Audit Results Upper Stratum"/>
-      <sheetName val="Population Characteristics"/>
-      <sheetName val="2002.1-6管理费用"/>
-      <sheetName val="G2-5生产成本审定表"/>
-      <sheetName val="FIN48 TP Doc"/>
-      <sheetName val="No.305"/>
-      <sheetName val="No.404"/>
-      <sheetName val="Contents"/>
-      <sheetName val="市场比较法"/>
-      <sheetName val="短期借款汇总表"/>
-      <sheetName val="20年销售出库"/>
-      <sheetName val="固定资产清理"/>
-      <sheetName val="在建工程"/>
-      <sheetName val="Sheet134"/>
-      <sheetName val="Sheet181"/>
-      <sheetName val="Sheet537"/>
-      <sheetName val="Sheet145"/>
-      <sheetName val="SFS(ACTUAL)"/>
-      <sheetName val="Sheet146"/>
-      <sheetName val="Sheet157"/>
-      <sheetName val="Sheet508"/>
-      <sheetName val="Sheet606"/>
-      <sheetName val="Sheet607"/>
-      <sheetName val="Sheet608"/>
-      <sheetName val="New Dept-IX"/>
-      <sheetName val="L105"/>
-      <sheetName val="R221"/>
-      <sheetName val="销售输入表"/>
-      <sheetName val="evaluate资金回收"/>
-      <sheetName val="To tied 2001 opening RE"/>
-      <sheetName val="资产评估结果分类汇总表 (2)"/>
-      <sheetName val="2001年运使费相抵"/>
-      <sheetName val="RESUMEN"/>
-      <sheetName val="通用设备折旧复核"/>
-      <sheetName val="专用设备折旧复核"/>
-      <sheetName val="运输设备折旧复核"/>
-      <sheetName val="电子设备折旧复核"/>
-      <sheetName val="其他设备折旧"/>
-      <sheetName val="Sheet148"/>
-      <sheetName val="管理费用"/>
-      <sheetName val="综合成本"/>
-      <sheetName val="存货收发存汇总表"/>
-      <sheetName val="利润中心"/>
-      <sheetName val="profit2 (2)"/>
-      <sheetName val="218"/>
-      <sheetName val="固定资产卡片"/>
-      <sheetName val="科目代码表"/>
-      <sheetName val="折旧表"/>
-      <sheetName val="0012"/>
-      <sheetName val="ADJ Sum(console)"/>
-      <sheetName val="L1-1"/>
-      <sheetName val="变动"/>
-      <sheetName val="QoA"/>
-      <sheetName val="QofE"/>
-      <sheetName val="QofA"/>
-      <sheetName val="2-试算"/>
-      <sheetName val="CalcOutPut"/>
-      <sheetName val="披露表-上市公司报告"/>
-      <sheetName val="CODES"/>
-      <sheetName val="在建工程Dy"/>
-      <sheetName val="存货Cx"/>
-      <sheetName val="M"/>
-      <sheetName val="损益表 &lt; P1 &gt; "/>
-      <sheetName val="披露表(国企)"/>
-      <sheetName val="销售收入底稿"/>
-      <sheetName val="FO1"/>
-      <sheetName val="应付利息Dy"/>
-      <sheetName val="以前年度损益调整"/>
-      <sheetName val="Khoan cong truong Tan De"/>
-      <sheetName val="5200D-5其他应收款审定明细表1"/>
-      <sheetName val="营业费用趋势分析"/>
-      <sheetName val="3-11待摊"/>
-      <sheetName val="6-1土地"/>
-      <sheetName val="Base Info"/>
-      <sheetName val="費用"/>
-      <sheetName val="資本支出"/>
-      <sheetName val="人力"/>
-      <sheetName val="編製說明"/>
-      <sheetName val="한계원가"/>
-      <sheetName val="2020云汉芯城"/>
-      <sheetName val="内销收人"/>
-      <sheetName val="待摊费用Dy"/>
-      <sheetName val="工程项目"/>
-      <sheetName val="预付账款Mx"/>
-      <sheetName val="预付账款Mx1"/>
-      <sheetName val="应付账款Mx1"/>
-      <sheetName val="原材料Mx1"/>
-      <sheetName val="营业成本Dy"/>
-      <sheetName val="A_1"/>
-      <sheetName val="累计折旧_2"/>
-      <sheetName val="余额表（终稿）"/>
-      <sheetName val="2008年"/>
-      <sheetName val="生产成本mx"/>
-      <sheetName val="qtr local"/>
-      <sheetName val="营业费用截止"/>
-      <sheetName val="递延收益Dy"/>
-      <sheetName val="372D-1 2012年折旧测算"/>
-      <sheetName val="Sheet798"/>
-      <sheetName val="Sheet545"/>
-      <sheetName val="Sheet151"/>
-      <sheetName val="May"/>
-      <sheetName val="Sheet257"/>
-      <sheetName val="Sheet426"/>
-      <sheetName val="Sheet593"/>
-      <sheetName val="CQFMA"/>
-      <sheetName val="Segment"/>
-      <sheetName val="list of LC"/>
-      <sheetName val="04利息支出"/>
-      <sheetName val="利息收入"/>
-      <sheetName val="预提工行贷"/>
-      <sheetName val="查验底稿"/>
-      <sheetName val="Sheet611"/>
-      <sheetName val="Sheet832"/>
-      <sheetName val="Sheet836"/>
-      <sheetName val="56271-2"/>
-      <sheetName val="2021年收入汇总"/>
-      <sheetName val="U8数据"/>
-      <sheetName val="pe"/>
-      <sheetName val="28"/>
-      <sheetName val="14"/>
-      <sheetName val="36"/>
-      <sheetName val="13"/>
-      <sheetName val="16-1"/>
-      <sheetName val="16-2"/>
-      <sheetName val="16-3"/>
-      <sheetName val="Competition ¥"/>
-      <sheetName val="630科目余额表"/>
-      <sheetName val="ZA-DY"/>
-      <sheetName val="FY02"/>
-      <sheetName val="审计差异汇总"/>
-      <sheetName val="B15 重要性计算表(审计前）"/>
-      <sheetName val="CE_P"/>
-      <sheetName val="表头及目录"/>
-      <sheetName val="N__财务费用"/>
-      <sheetName val="N__持有至到期投资"/>
-      <sheetName val="N__存货"/>
-      <sheetName val="N__递延所得税资产和递延所得税负债"/>
-      <sheetName val="N__短期借款"/>
-      <sheetName val="所合并"/>
-      <sheetName val="资合并"/>
-      <sheetName val="N__工程物资"/>
-      <sheetName val="N__公允价值变动收益"/>
-      <sheetName val="N__股本"/>
-      <sheetName val="N__固定资产"/>
-      <sheetName val="N__固定资产清理"/>
-      <sheetName val="N__管理费用"/>
-      <sheetName val="N__货币资金"/>
-      <sheetName val="N__交易性金融负债"/>
-      <sheetName val="N__交易性金融资产"/>
-      <sheetName val="N__开发支出"/>
-      <sheetName val="N__可供出售金融资产"/>
-      <sheetName val="N__库存股"/>
-      <sheetName val="利合并"/>
-      <sheetName val="N__每股收益"/>
-      <sheetName val="N__其他非流动负债"/>
-      <sheetName val="N__其他非流动资产"/>
-      <sheetName val="N__其他流动负债"/>
-      <sheetName val="N__其他应付款"/>
-      <sheetName val="N__其他综合收益"/>
-      <sheetName val="N__其他流动资产"/>
-      <sheetName val="N__商誉"/>
-      <sheetName val="N__生产性生物资产"/>
-      <sheetName val="N__所得税费用"/>
-      <sheetName val="N__投资收益"/>
-      <sheetName val="N__投资性房地产"/>
-      <sheetName val="N__未分配利润"/>
-      <sheetName val="N__无形资产"/>
-      <sheetName val="N__现金流量表附注"/>
-      <sheetName val="现合并"/>
-      <sheetName val="N__销售费用"/>
-      <sheetName val="N__一年内到期的非流动负债"/>
-      <sheetName val="N__一年内到期的非流动资产"/>
-      <sheetName val="N__应付股利"/>
-      <sheetName val="N__应付利息"/>
-      <sheetName val="N__应付票据"/>
-      <sheetName val="N__应付债券"/>
-      <sheetName val="N__应付账款"/>
-      <sheetName val="N__应付职工薪酬"/>
-      <sheetName val="N__应交税费"/>
-      <sheetName val="N__应收股利"/>
-      <sheetName val="N__应收利息"/>
-      <sheetName val="N__应收票据"/>
-      <sheetName val="N__盈余公积"/>
-      <sheetName val="N__税金及附加"/>
-      <sheetName val="N__营业外收入"/>
-      <sheetName val="N__营业外支出"/>
-      <sheetName val="N__油气资产"/>
-      <sheetName val="N__预付款项"/>
-      <sheetName val="N__预计负债"/>
-      <sheetName val="N__预收账款"/>
-      <sheetName val="N__在建工程"/>
-      <sheetName val="N__长期待摊费用"/>
-      <sheetName val="N__长期借款"/>
-      <sheetName val="N__长期应付款"/>
-      <sheetName val="N__长期应收款"/>
-      <sheetName val="N__专项储备"/>
-      <sheetName val="N__专项应付款"/>
-      <sheetName val="N__资本公积"/>
-      <sheetName val="N__资产减值损失"/>
-      <sheetName val="N__资产减值准备"/>
-      <sheetName val="Variables"/>
-      <sheetName val="维护表"/>
-      <sheetName val="enums"/>
-      <sheetName val="原材料采购价格检查G4-7"/>
-      <sheetName val="Basic_Setting"/>
-      <sheetName val="A1-4 Failure Impact "/>
-      <sheetName val="SMAEU-3"/>
-      <sheetName val="FK Ma"/>
-      <sheetName val="特殊部门按部门分类"/>
-      <sheetName val="技术人员分位值(不含PM&amp;SLS）"/>
-      <sheetName val="DEF"/>
-      <sheetName val="Sheet166"/>
-      <sheetName val="U321"/>
-      <sheetName val="現金流量"/>
-      <sheetName val="固清"/>
-      <sheetName val="PopCache_Sheet1"/>
-      <sheetName val="MetaData"/>
-      <sheetName val="Threshold Table"/>
-      <sheetName val="dd"/>
-      <sheetName val="凭证汇总"/>
-      <sheetName val="维简费"/>
-      <sheetName val="维简费返还"/>
-      <sheetName val="韓国"/>
-      <sheetName val="yszk200412.dbf"/>
-      <sheetName val="5440彙總表"/>
-      <sheetName val="IPO"/>
-      <sheetName val="Summary Page"/>
-      <sheetName val="NR-2006"/>
-      <sheetName val="AR-2006"/>
-      <sheetName val="NR-2005"/>
-      <sheetName val="AR-2005"/>
-      <sheetName val="AR-2004"/>
-      <sheetName val="Q4"/>
-      <sheetName val="Sheet1.1"/>
-      <sheetName val="10 销货成本表"/>
-      <sheetName val="AATI "/>
-      <sheetName val="NECsoic8(bvi)"/>
-      <sheetName val="Anpec(bvi)"/>
-      <sheetName val="Apec(bvi)"/>
-      <sheetName val="ATU"/>
-      <sheetName val="FSC"/>
-      <sheetName val="IR"/>
-      <sheetName val="ITOCHU_Sanyo"/>
-      <sheetName val="Melco"/>
-      <sheetName val="NECtssop8(bvi)"/>
-      <sheetName val="NIKO(bvi)"/>
-      <sheetName val="O2Micro"/>
-      <sheetName val="PAN JIT"/>
-      <sheetName val="Richtek (bvi)"/>
-      <sheetName val="Semiwell"/>
-      <sheetName val="Supertek"/>
-      <sheetName val="3D"/>
-      <sheetName val="CF-8&quot;-y2"/>
-      <sheetName val="PL-monthly"/>
-      <sheetName val="Wacc"/>
-      <sheetName val="IC3A"/>
-      <sheetName val="'IC4'A"/>
-      <sheetName val="'IO7"/>
-      <sheetName val="'IO8"/>
-      <sheetName val="PL"/>
-      <sheetName val="列表选择表"/>
-      <sheetName val="JPN Chl"/>
-      <sheetName val="科目索引"/>
-      <sheetName val="7-1 2008管理费用-办公费"/>
-      <sheetName val="7-5 2008年管理费用-试验检验费"/>
-      <sheetName val="7-1 2009年管理费用-办公费"/>
-      <sheetName val="7-5 2009年管理费用-试验检验费"/>
-      <sheetName val="7-1 2010年管理费用-办公费"/>
-      <sheetName val="7-5 2010年管理费用-试验检验费"/>
-      <sheetName val="财企01表_南宁轨道交通集团有限责任公司（集团合并）期末数"/>
-      <sheetName val="销售毛利润表"/>
-      <sheetName val="PLGROUPCPY"/>
-      <sheetName val="销售发票专用序时簿"/>
-      <sheetName val="DEP"/>
-      <sheetName val="制造费用"/>
-      <sheetName val="11908发生额"/>
-      <sheetName val="帐上"/>
-      <sheetName val="5500A-4固定资产检查"/>
-      <sheetName val="6200B-4应付职工薪酬检查"/>
-      <sheetName val="6200B-5应付职工薪酬勾稽检查"/>
-      <sheetName val="勿删-各公司按部门汇总工资"/>
-      <sheetName val="6200B-6.1应付职工薪酬检查-工资"/>
-      <sheetName val="6200B-3应付职工薪酬披露核对表"/>
-      <sheetName val="YA-1-1"/>
-      <sheetName val="外销收入明细表"/>
-      <sheetName val="内部销售明细表"/>
-      <sheetName val="actbgtbyM"/>
-      <sheetName val="Inputs"/>
-      <sheetName val="DR Summary Margin"/>
-      <sheetName val="DR Summary Margin - Fcst"/>
-      <sheetName val="Prior Week Funnel"/>
-      <sheetName val="DR Summary Revenue"/>
-      <sheetName val="DR Summary Revenue - Fcst"/>
-      <sheetName val="DR Summary Units"/>
-      <sheetName val="DR Summary Units - Fcst"/>
-      <sheetName val="3-9其他应收"/>
-      <sheetName val="9-3应付帐款"/>
-      <sheetName val="按客户"/>
-      <sheetName val="Prg"/>
-      <sheetName val="Profile"/>
-      <sheetName val="项目编号列表"/>
-      <sheetName val="使用说明"/>
-      <sheetName val="Income Stm"/>
-      <sheetName val="（27）实收资本"/>
-      <sheetName val="5200A-5应收账款函证汇总表"/>
-      <sheetName val="2、生产成本月际分析"/>
-      <sheetName val="预付账款Mx12"/>
-      <sheetName val="NGUON"/>
-      <sheetName val="自制半成品1-12计价测试"/>
-      <sheetName val="Breakdown G&amp;A"/>
-      <sheetName val="Bad debt provison&amp;aging analysi"/>
-      <sheetName val="alternative"/>
-      <sheetName val="自制半成品 (2)"/>
-      <sheetName val="产成品明细"/>
-      <sheetName val="主营业务成本 (2)"/>
-      <sheetName val="Drop List References"/>
-      <sheetName val="Bank"/>
-      <sheetName val="工程量计算"/>
-      <sheetName val="Expense Summary-M"/>
-      <sheetName val="Production"/>
-      <sheetName val="上缴管理费明细"/>
-      <sheetName val="出库"/>
-      <sheetName val="入库"/>
-      <sheetName val="3-1-1现金"/>
-      <sheetName val="3-1-2银存"/>
-      <sheetName val="3-1-3其他货币"/>
-      <sheetName val="10-1长借"/>
-      <sheetName val="10-2应付债券"/>
-      <sheetName val="10-3长期应付款"/>
-      <sheetName val="10-4住房周转金"/>
-      <sheetName val="10-5其他长期负债"/>
-      <sheetName val="10-6递延税款贷项"/>
-      <sheetName val="3-10存货汇总"/>
-      <sheetName val="3-12待处理流损"/>
-      <sheetName val="3-13一年长债"/>
-      <sheetName val="3-14其他流资"/>
-      <sheetName val="3-2短投汇总"/>
-      <sheetName val="3-5应收股利"/>
-      <sheetName val="3-6应收利息"/>
-      <sheetName val="3-7预付帐款"/>
-      <sheetName val="3-8应收补贴"/>
-      <sheetName val="长投汇总"/>
-      <sheetName val="6-2其他无形"/>
-      <sheetName val="7-1开办费"/>
-      <sheetName val="7-2长期待摊"/>
-      <sheetName val="8-1其他长期"/>
-      <sheetName val="8-2递税借项"/>
-      <sheetName val="9-1短期借款"/>
-      <sheetName val="9-10应付利润"/>
-      <sheetName val="9-11其他应交"/>
-      <sheetName val="9-12预提"/>
-      <sheetName val="9-13一年内长债"/>
-      <sheetName val="9-14其他流负"/>
-      <sheetName val="9-2应付票据"/>
-      <sheetName val="9-4预收帐款"/>
-      <sheetName val="9-5代销商品款"/>
-      <sheetName val="9-6其他应付款"/>
-      <sheetName val="9-7应付工资"/>
-      <sheetName val="9-8应付福利费"/>
-      <sheetName val="9-9应交税金"/>
-      <sheetName val="Notes"/>
-      <sheetName val="折旧测算表"/>
-      <sheetName val="5-3工程物资"/>
-      <sheetName val="5-4-2在建安装"/>
-      <sheetName val="5-5固定清理"/>
-      <sheetName val="5-6待处理固定损失"/>
-      <sheetName val="十价"/>
-      <sheetName val="KLHT"/>
-      <sheetName val="IC-5保理费用核查"/>
-      <sheetName val="10-3-1工作量确认单核查 --OK"/>
-      <sheetName val="收入成本大表"/>
-      <sheetName val="check是否取回"/>
-      <sheetName val="变更前的成本大表"/>
-      <sheetName val="2017年表"/>
-      <sheetName val="关联方抵消"/>
-      <sheetName val="10-3-2回复"/>
-      <sheetName val="Basic information"/>
-      <sheetName val="Basic_Information"/>
-      <sheetName val="FORM14_2"/>
-      <sheetName val="L1-1资产负债表"/>
-      <sheetName val="工程量"/>
-      <sheetName val="工作底稿扉页"/>
-      <sheetName val="Y3-1一般会计制度附注"/>
-      <sheetName val="Y3-2 06企业会计制度附注"/>
-      <sheetName val="Y0-1报告准备表（无需打印）"/>
-      <sheetName val="5-1-3管沟"/>
-      <sheetName val="梁家5-1-1房建"/>
-      <sheetName val="5-4-1在建土建"/>
-      <sheetName val="$TB 1"/>
-      <sheetName val="$TB"/>
-      <sheetName val="建发股份关联方清单"/>
-      <sheetName val="评估结论"/>
-      <sheetName val="HKBUD"/>
-      <sheetName val="I-COA"/>
-      <sheetName val="合并范围"/>
-      <sheetName val="长期应付款Dy"/>
-      <sheetName val="Acct"/>
-      <sheetName val="template"/>
-      <sheetName val="JP Report"/>
-      <sheetName val="1-000-1"/>
-      <sheetName val="1-000-3"/>
-      <sheetName val="10K4"/>
-      <sheetName val="Sheet121"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
-      <sheetData sheetId="1" refreshError="1"/>
-      <sheetData sheetId="2" refreshError="1"/>
-      <sheetData sheetId="3" refreshError="1"/>
-      <sheetData sheetId="4" refreshError="1"/>
-      <sheetData sheetId="5" refreshError="1"/>
-      <sheetData sheetId="6" refreshError="1"/>
-      <sheetData sheetId="7" refreshError="1"/>
-      <sheetData sheetId="8" refreshError="1"/>
-      <sheetData sheetId="9" refreshError="1"/>
-      <sheetData sheetId="10" refreshError="1"/>
-      <sheetData sheetId="11" refreshError="1"/>
-      <sheetData sheetId="12" refreshError="1"/>
-      <sheetData sheetId="13" refreshError="1"/>
-      <sheetData sheetId="14" refreshError="1"/>
-      <sheetData sheetId="15" refreshError="1"/>
-      <sheetData sheetId="16" refreshError="1"/>
-      <sheetData sheetId="17" refreshError="1"/>
-      <sheetData sheetId="18" refreshError="1"/>
-      <sheetData sheetId="19" refreshError="1"/>
-      <sheetData sheetId="20" refreshError="1"/>
-      <sheetData sheetId="21" refreshError="1"/>
-      <sheetData sheetId="22" refreshError="1"/>
-      <sheetData sheetId="23" refreshError="1"/>
-      <sheetData sheetId="24" refreshError="1"/>
-      <sheetData sheetId="25" refreshError="1"/>
-      <sheetData sheetId="26" refreshError="1"/>
-      <sheetData sheetId="27" refreshError="1"/>
-      <sheetData sheetId="28" refreshError="1"/>
-      <sheetData sheetId="29" refreshError="1"/>
-      <sheetData sheetId="30" refreshError="1"/>
-      <sheetData sheetId="31" refreshError="1"/>
-      <sheetData sheetId="32" refreshError="1"/>
-      <sheetData sheetId="33" refreshError="1"/>
-      <sheetData sheetId="34" refreshError="1"/>
-      <sheetData sheetId="35" refreshError="1"/>
-      <sheetData sheetId="36" refreshError="1"/>
-      <sheetData sheetId="37" refreshError="1"/>
-      <sheetData sheetId="38" refreshError="1"/>
-      <sheetData sheetId="39" refreshError="1"/>
-      <sheetData sheetId="40" refreshError="1"/>
-      <sheetData sheetId="41" refreshError="1"/>
-      <sheetData sheetId="42" refreshError="1"/>
-      <sheetData sheetId="43" refreshError="1"/>
-      <sheetData sheetId="44" refreshError="1"/>
-      <sheetData sheetId="45" refreshError="1"/>
-      <sheetData sheetId="46" refreshError="1"/>
-      <sheetData sheetId="47" refreshError="1"/>
-      <sheetData sheetId="48" refreshError="1"/>
-      <sheetData sheetId="49" refreshError="1"/>
-      <sheetData sheetId="50" refreshError="1"/>
-      <sheetData sheetId="51" refreshError="1"/>
-      <sheetData sheetId="52" refreshError="1"/>
-      <sheetData sheetId="53" refreshError="1"/>
-      <sheetData sheetId="54" refreshError="1"/>
-      <sheetData sheetId="55" refreshError="1"/>
-      <sheetData sheetId="56" refreshError="1"/>
-      <sheetData sheetId="57" refreshError="1"/>
-      <sheetData sheetId="58" refreshError="1"/>
-      <sheetData sheetId="59" refreshError="1"/>
-      <sheetData sheetId="60" refreshError="1"/>
-      <sheetData sheetId="61" refreshError="1"/>
-      <sheetData sheetId="62" refreshError="1"/>
-      <sheetData sheetId="63" refreshError="1"/>
-      <sheetData sheetId="64" refreshError="1"/>
-      <sheetData sheetId="65" refreshError="1"/>
-      <sheetData sheetId="66" refreshError="1"/>
-      <sheetData sheetId="67" refreshError="1"/>
-      <sheetData sheetId="68" refreshError="1"/>
-      <sheetData sheetId="69" refreshError="1"/>
-      <sheetData sheetId="70" refreshError="1"/>
-      <sheetData sheetId="71" refreshError="1"/>
-      <sheetData sheetId="72" refreshError="1"/>
-      <sheetData sheetId="73" refreshError="1"/>
-      <sheetData sheetId="74" refreshError="1"/>
-      <sheetData sheetId="75" refreshError="1"/>
-      <sheetData sheetId="76" refreshError="1"/>
-      <sheetData sheetId="77" refreshError="1"/>
-      <sheetData sheetId="78" refreshError="1"/>
-      <sheetData sheetId="79" refreshError="1"/>
-      <sheetData sheetId="80" refreshError="1"/>
-      <sheetData sheetId="81" refreshError="1"/>
-      <sheetData sheetId="82" refreshError="1"/>
-      <sheetData sheetId="83" refreshError="1"/>
-      <sheetData sheetId="84" refreshError="1"/>
-      <sheetData sheetId="85" refreshError="1"/>
-      <sheetData sheetId="86" refreshError="1"/>
-      <sheetData sheetId="87" refreshError="1"/>
-      <sheetData sheetId="88" refreshError="1"/>
-      <sheetData sheetId="89" refreshError="1"/>
-      <sheetData sheetId="90" refreshError="1"/>
-      <sheetData sheetId="91" refreshError="1"/>
-      <sheetData sheetId="92" refreshError="1"/>
-      <sheetData sheetId="93" refreshError="1"/>
-      <sheetData sheetId="94" refreshError="1"/>
-      <sheetData sheetId="95" refreshError="1"/>
-      <sheetData sheetId="96" refreshError="1"/>
-      <sheetData sheetId="97" refreshError="1"/>
-      <sheetData sheetId="98" refreshError="1"/>
-      <sheetData sheetId="99" refreshError="1"/>
-      <sheetData sheetId="100" refreshError="1"/>
-      <sheetData sheetId="101" refreshError="1"/>
-      <sheetData sheetId="102" refreshError="1"/>
-      <sheetData sheetId="103" refreshError="1"/>
-      <sheetData sheetId="104" refreshError="1"/>
-      <sheetData sheetId="105" refreshError="1"/>
-      <sheetData sheetId="106" refreshError="1"/>
-      <sheetData sheetId="107" refreshError="1"/>
-      <sheetData sheetId="108" refreshError="1"/>
-      <sheetData sheetId="109" refreshError="1"/>
-      <sheetData sheetId="110" refreshError="1"/>
-      <sheetData sheetId="111" refreshError="1"/>
-      <sheetData sheetId="112" refreshError="1"/>
-      <sheetData sheetId="113" refreshError="1"/>
-      <sheetData sheetId="114" refreshError="1"/>
-      <sheetData sheetId="115" refreshError="1"/>
-      <sheetData sheetId="116" refreshError="1"/>
-      <sheetData sheetId="117" refreshError="1"/>
-      <sheetData sheetId="118" refreshError="1"/>
-      <sheetData sheetId="119" refreshError="1"/>
-      <sheetData sheetId="120" refreshError="1"/>
-      <sheetData sheetId="121" refreshError="1"/>
-      <sheetData sheetId="122" refreshError="1"/>
-      <sheetData sheetId="123" refreshError="1"/>
-      <sheetData sheetId="124" refreshError="1"/>
-      <sheetData sheetId="125" refreshError="1"/>
-      <sheetData sheetId="126" refreshError="1"/>
-      <sheetData sheetId="127" refreshError="1"/>
-      <sheetData sheetId="128" refreshError="1"/>
-      <sheetData sheetId="129" refreshError="1"/>
-      <sheetData sheetId="130" refreshError="1"/>
-      <sheetData sheetId="131" refreshError="1"/>
-      <sheetData sheetId="132" refreshError="1"/>
-      <sheetData sheetId="133" refreshError="1"/>
-      <sheetData sheetId="134" refreshError="1"/>
-      <sheetData sheetId="135" refreshError="1"/>
-      <sheetData sheetId="136" refreshError="1"/>
-      <sheetData sheetId="137" refreshError="1"/>
-      <sheetData sheetId="138" refreshError="1"/>
-      <sheetData sheetId="139" refreshError="1"/>
-      <sheetData sheetId="140" refreshError="1"/>
-      <sheetData sheetId="141" refreshError="1"/>
-      <sheetData sheetId="142" refreshError="1"/>
-      <sheetData sheetId="143" refreshError="1"/>
-      <sheetData sheetId="144" refreshError="1"/>
-      <sheetData sheetId="145" refreshError="1"/>
-      <sheetData sheetId="146" refreshError="1"/>
-      <sheetData sheetId="147" refreshError="1"/>
-      <sheetData sheetId="148" refreshError="1"/>
-      <sheetData sheetId="149" refreshError="1"/>
-      <sheetData sheetId="150" refreshError="1"/>
-      <sheetData sheetId="151" refreshError="1"/>
-      <sheetData sheetId="152" refreshError="1"/>
-      <sheetData sheetId="153" refreshError="1"/>
-      <sheetData sheetId="154" refreshError="1"/>
-      <sheetData sheetId="155" refreshError="1"/>
-      <sheetData sheetId="156" refreshError="1"/>
-      <sheetData sheetId="157" refreshError="1"/>
-      <sheetData sheetId="158" refreshError="1"/>
-      <sheetData sheetId="159" refreshError="1"/>
-      <sheetData sheetId="160" refreshError="1"/>
-      <sheetData sheetId="161" refreshError="1"/>
-      <sheetData sheetId="162" refreshError="1"/>
-      <sheetData sheetId="163" refreshError="1"/>
-      <sheetData sheetId="164" refreshError="1"/>
-      <sheetData sheetId="165" refreshError="1"/>
-      <sheetData sheetId="166" refreshError="1"/>
-      <sheetData sheetId="167" refreshError="1"/>
-      <sheetData sheetId="168" refreshError="1"/>
-      <sheetData sheetId="169" refreshError="1"/>
-      <sheetData sheetId="170" refreshError="1"/>
-      <sheetData sheetId="171" refreshError="1"/>
-      <sheetData sheetId="172" refreshError="1"/>
-      <sheetData sheetId="173" refreshError="1"/>
-      <sheetData sheetId="174" refreshError="1"/>
-      <sheetData sheetId="175" refreshError="1"/>
-      <sheetData sheetId="176" refreshError="1"/>
-      <sheetData sheetId="177" refreshError="1"/>
-      <sheetData sheetId="178" refreshError="1"/>
-      <sheetData sheetId="179" refreshError="1"/>
-      <sheetData sheetId="180" refreshError="1"/>
-      <sheetData sheetId="181" refreshError="1"/>
-      <sheetData sheetId="182" refreshError="1"/>
-      <sheetData sheetId="183" refreshError="1"/>
-      <sheetData sheetId="184" refreshError="1"/>
-      <sheetData sheetId="185" refreshError="1"/>
-      <sheetData sheetId="186" refreshError="1"/>
-      <sheetData sheetId="187" refreshError="1"/>
-      <sheetData sheetId="188" refreshError="1"/>
-      <sheetData sheetId="189" refreshError="1"/>
-      <sheetData sheetId="190" refreshError="1"/>
-      <sheetData sheetId="191" refreshError="1"/>
-      <sheetData sheetId="192" refreshError="1"/>
-      <sheetData sheetId="193" refreshError="1"/>
-      <sheetData sheetId="194" refreshError="1"/>
-      <sheetData sheetId="195" refreshError="1"/>
-      <sheetData sheetId="196" refreshError="1"/>
-      <sheetData sheetId="197" refreshError="1"/>
-      <sheetData sheetId="198" refreshError="1"/>
-      <sheetData sheetId="199" refreshError="1"/>
-      <sheetData sheetId="200" refreshError="1"/>
-      <sheetData sheetId="201" refreshError="1"/>
-      <sheetData sheetId="202" refreshError="1"/>
-      <sheetData sheetId="203" refreshError="1"/>
-      <sheetData sheetId="204" refreshError="1"/>
-      <sheetData sheetId="205" refreshError="1"/>
-      <sheetData sheetId="206" refreshError="1"/>
-      <sheetData sheetId="207" refreshError="1"/>
-      <sheetData sheetId="208" refreshError="1"/>
-      <sheetData sheetId="209" refreshError="1"/>
-      <sheetData sheetId="210" refreshError="1"/>
-      <sheetData sheetId="211" refreshError="1"/>
-      <sheetData sheetId="212" refreshError="1"/>
-      <sheetData sheetId="213" refreshError="1"/>
-      <sheetData sheetId="214" refreshError="1"/>
-      <sheetData sheetId="215" refreshError="1"/>
-      <sheetData sheetId="216" refreshError="1"/>
-      <sheetData sheetId="217" refreshError="1"/>
-      <sheetData sheetId="218" refreshError="1"/>
-      <sheetData sheetId="219" refreshError="1"/>
-      <sheetData sheetId="220" refreshError="1"/>
-      <sheetData sheetId="221" refreshError="1"/>
-      <sheetData sheetId="222" refreshError="1"/>
-      <sheetData sheetId="223" refreshError="1"/>
-      <sheetData sheetId="224" refreshError="1"/>
-      <sheetData sheetId="225" refreshError="1"/>
-      <sheetData sheetId="226" refreshError="1"/>
-      <sheetData sheetId="227" refreshError="1"/>
-      <sheetData sheetId="228" refreshError="1"/>
-      <sheetData sheetId="229" refreshError="1"/>
-      <sheetData sheetId="230" refreshError="1"/>
-      <sheetData sheetId="231" refreshError="1"/>
-      <sheetData sheetId="232" refreshError="1"/>
-      <sheetData sheetId="233" refreshError="1"/>
-      <sheetData sheetId="234" refreshError="1"/>
-      <sheetData sheetId="235" refreshError="1"/>
-      <sheetData sheetId="236" refreshError="1"/>
-      <sheetData sheetId="237" refreshError="1"/>
-      <sheetData sheetId="238" refreshError="1"/>
-      <sheetData sheetId="239" refreshError="1"/>
-      <sheetData sheetId="240" refreshError="1"/>
-      <sheetData sheetId="241" refreshError="1"/>
-      <sheetData sheetId="242" refreshError="1"/>
-      <sheetData sheetId="243" refreshError="1"/>
-      <sheetData sheetId="244" refreshError="1"/>
-      <sheetData sheetId="245" refreshError="1"/>
-      <sheetData sheetId="246" refreshError="1"/>
-      <sheetData sheetId="247" refreshError="1"/>
-      <sheetData sheetId="248" refreshError="1"/>
-      <sheetData sheetId="249" refreshError="1"/>
-      <sheetData sheetId="250" refreshError="1"/>
-      <sheetData sheetId="251" refreshError="1"/>
-      <sheetData sheetId="252" refreshError="1"/>
-      <sheetData sheetId="253" refreshError="1"/>
-      <sheetData sheetId="254" refreshError="1"/>
-      <sheetData sheetId="255" refreshError="1"/>
-      <sheetData sheetId="256" refreshError="1"/>
-      <sheetData sheetId="257" refreshError="1"/>
-      <sheetData sheetId="258" refreshError="1"/>
-      <sheetData sheetId="259" refreshError="1"/>
-      <sheetData sheetId="260" refreshError="1"/>
-      <sheetData sheetId="261" refreshError="1"/>
-      <sheetData sheetId="262" refreshError="1"/>
-      <sheetData sheetId="263" refreshError="1"/>
-      <sheetData sheetId="264" refreshError="1"/>
-      <sheetData sheetId="265" refreshError="1"/>
-      <sheetData sheetId="266" refreshError="1"/>
-      <sheetData sheetId="267" refreshError="1"/>
-      <sheetData sheetId="268" refreshError="1"/>
-      <sheetData sheetId="269" refreshError="1"/>
-      <sheetData sheetId="270" refreshError="1"/>
-      <sheetData sheetId="271" refreshError="1"/>
-      <sheetData sheetId="272" refreshError="1"/>
-      <sheetData sheetId="273" refreshError="1"/>
-      <sheetData sheetId="274" refreshError="1"/>
-      <sheetData sheetId="275" refreshError="1"/>
-      <sheetData sheetId="276" refreshError="1"/>
-      <sheetData sheetId="277" refreshError="1"/>
-      <sheetData sheetId="278" refreshError="1"/>
-      <sheetData sheetId="279" refreshError="1"/>
-      <sheetData sheetId="280" refreshError="1"/>
-      <sheetData sheetId="281" refreshError="1"/>
-      <sheetData sheetId="282" refreshError="1"/>
-      <sheetData sheetId="283" refreshError="1"/>
-      <sheetData sheetId="284" refreshError="1"/>
-      <sheetData sheetId="285" refreshError="1"/>
-      <sheetData sheetId="286" refreshError="1"/>
-      <sheetData sheetId="287" refreshError="1"/>
-      <sheetData sheetId="288" refreshError="1"/>
-      <sheetData sheetId="289" refreshError="1"/>
-      <sheetData sheetId="290" refreshError="1"/>
-      <sheetData sheetId="291" refreshError="1"/>
-      <sheetData sheetId="292" refreshError="1"/>
-      <sheetData sheetId="293" refreshError="1"/>
-      <sheetData sheetId="294" refreshError="1"/>
-      <sheetData sheetId="295" refreshError="1"/>
-      <sheetData sheetId="296" refreshError="1"/>
-      <sheetData sheetId="297" refreshError="1"/>
-      <sheetData sheetId="298" refreshError="1"/>
-      <sheetData sheetId="299" refreshError="1"/>
-      <sheetData sheetId="300" refreshError="1"/>
-      <sheetData sheetId="301" refreshError="1"/>
-      <sheetData sheetId="302" refreshError="1"/>
-      <sheetData sheetId="303" refreshError="1"/>
-      <sheetData sheetId="304" refreshError="1"/>
-      <sheetData sheetId="305" refreshError="1"/>
-      <sheetData sheetId="306" refreshError="1"/>
-      <sheetData sheetId="307" refreshError="1"/>
-      <sheetData sheetId="308" refreshError="1"/>
-      <sheetData sheetId="309" refreshError="1"/>
-      <sheetData sheetId="310" refreshError="1"/>
-      <sheetData sheetId="311" refreshError="1"/>
-      <sheetData sheetId="312" refreshError="1"/>
-      <sheetData sheetId="313" refreshError="1"/>
-      <sheetData sheetId="314" refreshError="1"/>
-      <sheetData sheetId="315" refreshError="1"/>
-      <sheetData sheetId="316" refreshError="1"/>
-      <sheetData sheetId="317" refreshError="1"/>
-      <sheetData sheetId="318" refreshError="1"/>
-      <sheetData sheetId="319" refreshError="1"/>
-      <sheetData sheetId="320" refreshError="1"/>
-      <sheetData sheetId="321" refreshError="1"/>
-      <sheetData sheetId="322" refreshError="1"/>
-      <sheetData sheetId="323" refreshError="1"/>
-      <sheetData sheetId="324" refreshError="1"/>
-      <sheetData sheetId="325" refreshError="1"/>
-      <sheetData sheetId="326" refreshError="1"/>
-      <sheetData sheetId="327" refreshError="1"/>
-      <sheetData sheetId="328" refreshError="1"/>
-      <sheetData sheetId="329" refreshError="1"/>
-      <sheetData sheetId="330" refreshError="1"/>
-      <sheetData sheetId="331" refreshError="1"/>
-      <sheetData sheetId="332" refreshError="1"/>
-      <sheetData sheetId="333" refreshError="1"/>
-      <sheetData sheetId="334" refreshError="1"/>
-      <sheetData sheetId="335" refreshError="1"/>
-      <sheetData sheetId="336" refreshError="1"/>
-      <sheetData sheetId="337" refreshError="1"/>
-      <sheetData sheetId="338" refreshError="1"/>
-      <sheetData sheetId="339" refreshError="1"/>
-      <sheetData sheetId="340" refreshError="1"/>
-      <sheetData sheetId="341" refreshError="1"/>
-      <sheetData sheetId="342" refreshError="1"/>
-      <sheetData sheetId="343" refreshError="1"/>
-      <sheetData sheetId="344" refreshError="1"/>
-      <sheetData sheetId="345" refreshError="1"/>
-      <sheetData sheetId="346" refreshError="1"/>
-      <sheetData sheetId="347" refreshError="1"/>
-      <sheetData sheetId="348" refreshError="1"/>
-      <sheetData sheetId="349" refreshError="1"/>
-      <sheetData sheetId="350" refreshError="1"/>
-      <sheetData sheetId="351" refreshError="1"/>
-      <sheetData sheetId="352" refreshError="1"/>
-      <sheetData sheetId="353" refreshError="1"/>
-      <sheetData sheetId="354" refreshError="1"/>
-      <sheetData sheetId="355" refreshError="1"/>
-      <sheetData sheetId="356" refreshError="1"/>
-      <sheetData sheetId="357" refreshError="1"/>
-      <sheetData sheetId="358" refreshError="1"/>
-      <sheetData sheetId="359" refreshError="1"/>
-      <sheetData sheetId="360" refreshError="1"/>
-      <sheetData sheetId="361" refreshError="1"/>
-      <sheetData sheetId="362" refreshError="1"/>
-      <sheetData sheetId="363" refreshError="1"/>
-      <sheetData sheetId="364" refreshError="1"/>
-      <sheetData sheetId="365" refreshError="1"/>
-      <sheetData sheetId="366" refreshError="1"/>
-      <sheetData sheetId="367" refreshError="1"/>
-      <sheetData sheetId="368" refreshError="1"/>
-      <sheetData sheetId="369" refreshError="1"/>
-      <sheetData sheetId="370" refreshError="1"/>
-      <sheetData sheetId="371" refreshError="1"/>
-      <sheetData sheetId="372" refreshError="1"/>
-      <sheetData sheetId="373" refreshError="1"/>
-      <sheetData sheetId="374" refreshError="1"/>
-      <sheetData sheetId="375" refreshError="1"/>
-      <sheetData sheetId="376" refreshError="1"/>
-      <sheetData sheetId="377" refreshError="1"/>
-      <sheetData sheetId="378" refreshError="1"/>
-      <sheetData sheetId="379" refreshError="1"/>
-      <sheetData sheetId="380" refreshError="1"/>
-      <sheetData sheetId="381" refreshError="1"/>
-      <sheetData sheetId="382" refreshError="1"/>
-      <sheetData sheetId="383" refreshError="1"/>
-      <sheetData sheetId="384" refreshError="1"/>
-      <sheetData sheetId="385" refreshError="1"/>
-      <sheetData sheetId="386" refreshError="1"/>
-      <sheetData sheetId="387" refreshError="1"/>
-      <sheetData sheetId="388" refreshError="1"/>
-      <sheetData sheetId="389" refreshError="1"/>
-      <sheetData sheetId="390" refreshError="1"/>
-      <sheetData sheetId="391" refreshError="1"/>
-      <sheetData sheetId="392" refreshError="1"/>
-      <sheetData sheetId="393" refreshError="1"/>
-      <sheetData sheetId="394" refreshError="1"/>
-      <sheetData sheetId="395" refreshError="1"/>
-      <sheetData sheetId="396" refreshError="1"/>
-      <sheetData sheetId="397" refreshError="1"/>
-      <sheetData sheetId="398" refreshError="1"/>
-      <sheetData sheetId="399" refreshError="1"/>
-      <sheetData sheetId="400" refreshError="1"/>
-      <sheetData sheetId="401" refreshError="1"/>
-      <sheetData sheetId="402" refreshError="1"/>
-      <sheetData sheetId="403" refreshError="1"/>
-      <sheetData sheetId="404" refreshError="1"/>
-      <sheetData sheetId="405" refreshError="1"/>
-      <sheetData sheetId="406" refreshError="1"/>
-      <sheetData sheetId="407" refreshError="1"/>
-      <sheetData sheetId="408" refreshError="1"/>
-      <sheetData sheetId="409" refreshError="1"/>
-      <sheetData sheetId="410" refreshError="1"/>
-      <sheetData sheetId="411" refreshError="1"/>
-      <sheetData sheetId="412" refreshError="1"/>
-      <sheetData sheetId="413" refreshError="1"/>
-      <sheetData sheetId="414" refreshError="1"/>
-      <sheetData sheetId="415" refreshError="1"/>
-      <sheetData sheetId="416" refreshError="1"/>
-      <sheetData sheetId="417" refreshError="1"/>
-      <sheetData sheetId="418" refreshError="1"/>
-      <sheetData sheetId="419" refreshError="1"/>
-      <sheetData sheetId="420" refreshError="1"/>
-      <sheetData sheetId="421" refreshError="1"/>
-      <sheetData sheetId="422" refreshError="1"/>
-      <sheetData sheetId="423" refreshError="1"/>
-      <sheetData sheetId="424" refreshError="1"/>
-      <sheetData sheetId="425" refreshError="1"/>
-      <sheetData sheetId="426" refreshError="1"/>
-      <sheetData sheetId="427" refreshError="1"/>
-      <sheetData sheetId="428" refreshError="1"/>
-      <sheetData sheetId="429" refreshError="1"/>
-      <sheetData sheetId="430" refreshError="1"/>
-      <sheetData sheetId="431" refreshError="1"/>
-      <sheetData sheetId="432" refreshError="1"/>
-      <sheetData sheetId="433" refreshError="1"/>
-      <sheetData sheetId="434" refreshError="1"/>
-      <sheetData sheetId="435" refreshError="1"/>
-      <sheetData sheetId="436" refreshError="1"/>
-      <sheetData sheetId="437" refreshError="1"/>
-      <sheetData sheetId="438" refreshError="1"/>
-      <sheetData sheetId="439" refreshError="1"/>
-      <sheetData sheetId="440" refreshError="1"/>
-      <sheetData sheetId="441" refreshError="1"/>
-      <sheetData sheetId="442" refreshError="1"/>
-      <sheetData sheetId="443" refreshError="1"/>
-      <sheetData sheetId="444" refreshError="1"/>
-      <sheetData sheetId="445" refreshError="1"/>
-      <sheetData sheetId="446" refreshError="1"/>
-      <sheetData sheetId="447" refreshError="1"/>
-      <sheetData sheetId="448" refreshError="1"/>
-      <sheetData sheetId="449" refreshError="1"/>
-      <sheetData sheetId="450" refreshError="1"/>
-      <sheetData sheetId="451" refreshError="1"/>
-      <sheetData sheetId="452" refreshError="1"/>
-      <sheetData sheetId="453" refreshError="1"/>
-      <sheetData sheetId="454" refreshError="1"/>
-      <sheetData sheetId="455" refreshError="1"/>
-      <sheetData sheetId="456" refreshError="1"/>
-      <sheetData sheetId="457" refreshError="1"/>
-      <sheetData sheetId="458" refreshError="1"/>
-      <sheetData sheetId="459" refreshError="1"/>
-      <sheetData sheetId="460" refreshError="1"/>
-      <sheetData sheetId="461" refreshError="1"/>
-      <sheetData sheetId="462" refreshError="1"/>
-      <sheetData sheetId="463" refreshError="1"/>
-      <sheetData sheetId="464" refreshError="1"/>
-      <sheetData sheetId="465" refreshError="1"/>
-      <sheetData sheetId="466" refreshError="1"/>
-      <sheetData sheetId="467" refreshError="1"/>
-      <sheetData sheetId="468" refreshError="1"/>
-      <sheetData sheetId="469" refreshError="1"/>
-      <sheetData sheetId="470" refreshError="1"/>
-      <sheetData sheetId="471" refreshError="1"/>
-      <sheetData sheetId="472" refreshError="1"/>
-      <sheetData sheetId="473" refreshError="1"/>
-      <sheetData sheetId="474" refreshError="1"/>
-      <sheetData sheetId="475" refreshError="1"/>
-      <sheetData sheetId="476" refreshError="1"/>
-      <sheetData sheetId="477" refreshError="1"/>
-      <sheetData sheetId="478" refreshError="1"/>
-      <sheetData sheetId="479" refreshError="1"/>
-      <sheetData sheetId="480" refreshError="1"/>
-      <sheetData sheetId="481" refreshError="1"/>
-      <sheetData sheetId="482" refreshError="1"/>
-      <sheetData sheetId="483" refreshError="1"/>
-      <sheetData sheetId="484" refreshError="1"/>
-      <sheetData sheetId="485" refreshError="1"/>
-      <sheetData sheetId="486" refreshError="1"/>
-      <sheetData sheetId="487" refreshError="1"/>
-      <sheetData sheetId="488" refreshError="1"/>
-      <sheetData sheetId="489" refreshError="1"/>
-      <sheetData sheetId="490" refreshError="1"/>
-      <sheetData sheetId="491" refreshError="1"/>
-      <sheetData sheetId="492" refreshError="1"/>
-      <sheetData sheetId="493" refreshError="1"/>
-      <sheetData sheetId="494" refreshError="1"/>
-      <sheetData sheetId="495" refreshError="1"/>
-      <sheetData sheetId="496" refreshError="1"/>
-      <sheetData sheetId="497" refreshError="1"/>
-      <sheetData sheetId="498" refreshError="1"/>
-      <sheetData sheetId="499" refreshError="1"/>
-      <sheetData sheetId="500" refreshError="1"/>
-      <sheetData sheetId="501" refreshError="1"/>
-      <sheetData sheetId="502" refreshError="1"/>
-      <sheetData sheetId="503" refreshError="1"/>
-      <sheetData sheetId="504" refreshError="1"/>
-      <sheetData sheetId="505" refreshError="1"/>
-      <sheetData sheetId="506" refreshError="1"/>
-      <sheetData sheetId="507" refreshError="1"/>
-      <sheetData sheetId="508" refreshError="1"/>
-      <sheetData sheetId="509" refreshError="1"/>
-      <sheetData sheetId="510" refreshError="1"/>
-      <sheetData sheetId="511" refreshError="1"/>
-      <sheetData sheetId="512" refreshError="1"/>
-      <sheetData sheetId="513" refreshError="1"/>
-      <sheetData sheetId="514" refreshError="1"/>
-      <sheetData sheetId="515" refreshError="1"/>
-      <sheetData sheetId="516" refreshError="1"/>
-      <sheetData sheetId="517" refreshError="1"/>
-      <sheetData sheetId="518" refreshError="1"/>
-      <sheetData sheetId="519" refreshError="1"/>
-      <sheetData sheetId="520" refreshError="1"/>
-      <sheetData sheetId="521" refreshError="1"/>
-      <sheetData sheetId="522" refreshError="1"/>
-      <sheetData sheetId="523" refreshError="1"/>
-      <sheetData sheetId="524" refreshError="1"/>
-      <sheetData sheetId="525" refreshError="1"/>
-      <sheetData sheetId="526" refreshError="1"/>
-      <sheetData sheetId="527" refreshError="1"/>
-      <sheetData sheetId="528" refreshError="1"/>
-      <sheetData sheetId="529" refreshError="1"/>
-      <sheetData sheetId="530" refreshError="1"/>
-      <sheetData sheetId="531" refreshError="1"/>
-      <sheetData sheetId="532" refreshError="1"/>
-      <sheetData sheetId="533" refreshError="1"/>
-      <sheetData sheetId="534" refreshError="1"/>
-      <sheetData sheetId="535" refreshError="1"/>
-      <sheetData sheetId="536" refreshError="1"/>
-      <sheetData sheetId="537" refreshError="1"/>
-      <sheetData sheetId="538" refreshError="1"/>
-      <sheetData sheetId="539" refreshError="1"/>
-      <sheetData sheetId="540" refreshError="1"/>
-      <sheetData sheetId="541" refreshError="1"/>
-      <sheetData sheetId="542" refreshError="1"/>
-      <sheetData sheetId="543" refreshError="1"/>
-      <sheetData sheetId="544" refreshError="1"/>
-      <sheetData sheetId="545" refreshError="1"/>
-      <sheetData sheetId="546" refreshError="1"/>
-      <sheetData sheetId="547" refreshError="1"/>
-      <sheetData sheetId="548" refreshError="1"/>
-      <sheetData sheetId="549" refreshError="1"/>
-      <sheetData sheetId="550" refreshError="1"/>
-      <sheetData sheetId="551" refreshError="1"/>
-      <sheetData sheetId="552" refreshError="1"/>
-      <sheetData sheetId="553" refreshError="1"/>
-      <sheetData sheetId="554" refreshError="1"/>
-      <sheetData sheetId="555" refreshError="1"/>
-      <sheetData sheetId="556" refreshError="1"/>
-      <sheetData sheetId="557" refreshError="1"/>
-      <sheetData sheetId="558" refreshError="1"/>
-      <sheetData sheetId="559" refreshError="1"/>
-      <sheetData sheetId="560" refreshError="1"/>
-      <sheetData sheetId="561" refreshError="1"/>
-      <sheetData sheetId="562" refreshError="1"/>
-      <sheetData sheetId="563" refreshError="1"/>
-      <sheetData sheetId="564" refreshError="1"/>
-      <sheetData sheetId="565" refreshError="1"/>
-      <sheetData sheetId="566" refreshError="1"/>
-      <sheetData sheetId="567" refreshError="1"/>
-      <sheetData sheetId="568" refreshError="1"/>
-      <sheetData sheetId="569" refreshError="1"/>
-      <sheetData sheetId="570" refreshError="1"/>
-      <sheetData sheetId="571" refreshError="1"/>
-      <sheetData sheetId="572" refreshError="1"/>
-      <sheetData sheetId="573" refreshError="1"/>
-      <sheetData sheetId="574" refreshError="1"/>
-      <sheetData sheetId="575" refreshError="1"/>
-      <sheetData sheetId="576" refreshError="1"/>
-      <sheetData sheetId="577" refreshError="1"/>
-      <sheetData sheetId="578" refreshError="1"/>
-      <sheetData sheetId="579" refreshError="1"/>
-      <sheetData sheetId="580" refreshError="1"/>
-      <sheetData sheetId="581" refreshError="1"/>
-      <sheetData sheetId="582" refreshError="1"/>
-      <sheetData sheetId="583" refreshError="1"/>
-      <sheetData sheetId="584" refreshError="1"/>
-      <sheetData sheetId="585" refreshError="1"/>
-      <sheetData sheetId="586" refreshError="1"/>
-      <sheetData sheetId="587" refreshError="1"/>
-      <sheetData sheetId="588" refreshError="1"/>
-      <sheetData sheetId="589" refreshError="1"/>
-      <sheetData sheetId="590" refreshError="1"/>
-      <sheetData sheetId="591" refreshError="1"/>
-      <sheetData sheetId="592" refreshError="1"/>
-      <sheetData sheetId="593" refreshError="1"/>
-      <sheetData sheetId="594" refreshError="1"/>
-      <sheetData sheetId="595" refreshError="1"/>
-      <sheetData sheetId="596" refreshError="1"/>
-      <sheetData sheetId="597" refreshError="1"/>
-      <sheetData sheetId="598" refreshError="1"/>
-      <sheetData sheetId="599" refreshError="1"/>
-      <sheetData sheetId="600" refreshError="1"/>
-      <sheetData sheetId="601" refreshError="1"/>
-      <sheetData sheetId="602" refreshError="1"/>
-      <sheetData sheetId="603" refreshError="1"/>
-      <sheetData sheetId="604" refreshError="1"/>
-      <sheetData sheetId="605" refreshError="1"/>
-      <sheetData sheetId="606" refreshError="1"/>
-      <sheetData sheetId="607" refreshError="1"/>
-      <sheetData sheetId="608" refreshError="1"/>
-      <sheetData sheetId="609" refreshError="1"/>
-      <sheetData sheetId="610" refreshError="1"/>
-      <sheetData sheetId="611" refreshError="1"/>
-      <sheetData sheetId="612" refreshError="1"/>
-      <sheetData sheetId="613" refreshError="1"/>
-      <sheetData sheetId="614" refreshError="1"/>
-      <sheetData sheetId="615" refreshError="1"/>
-      <sheetData sheetId="616" refreshError="1"/>
-      <sheetData sheetId="617" refreshError="1"/>
-      <sheetData sheetId="618" refreshError="1"/>
-      <sheetData sheetId="619" refreshError="1"/>
-      <sheetData sheetId="620" refreshError="1"/>
-      <sheetData sheetId="621" refreshError="1"/>
-      <sheetData sheetId="622" refreshError="1"/>
-      <sheetData sheetId="623" refreshError="1"/>
-      <sheetData sheetId="624" refreshError="1"/>
-      <sheetData sheetId="625" refreshError="1"/>
-      <sheetData sheetId="626" refreshError="1"/>
-      <sheetData sheetId="627" refreshError="1"/>
-      <sheetData sheetId="628" refreshError="1"/>
-      <sheetData sheetId="629" refreshError="1"/>
-      <sheetData sheetId="630" refreshError="1"/>
-      <sheetData sheetId="631" refreshError="1"/>
-      <sheetData sheetId="632" refreshError="1"/>
-      <sheetData sheetId="633" refreshError="1"/>
-      <sheetData sheetId="634" refreshError="1"/>
-      <sheetData sheetId="635" refreshError="1"/>
-      <sheetData sheetId="636" refreshError="1"/>
-      <sheetData sheetId="637" refreshError="1"/>
-      <sheetData sheetId="638" refreshError="1"/>
-      <sheetData sheetId="639" refreshError="1"/>
-      <sheetData sheetId="640" refreshError="1"/>
-      <sheetData sheetId="641" refreshError="1"/>
-      <sheetData sheetId="642" refreshError="1"/>
-      <sheetData sheetId="643" refreshError="1"/>
-      <sheetData sheetId="644" refreshError="1"/>
-      <sheetData sheetId="645" refreshError="1"/>
-      <sheetData sheetId="646" refreshError="1"/>
-      <sheetData sheetId="647" refreshError="1"/>
-      <sheetData sheetId="648" refreshError="1"/>
-      <sheetData sheetId="649" refreshError="1"/>
-      <sheetData sheetId="650" refreshError="1"/>
-      <sheetData sheetId="651" refreshError="1"/>
-      <sheetData sheetId="652" refreshError="1"/>
-      <sheetData sheetId="653" refreshError="1"/>
-      <sheetData sheetId="654" refreshError="1"/>
-      <sheetData sheetId="655" refreshError="1"/>
-      <sheetData sheetId="656" refreshError="1"/>
-      <sheetData sheetId="657" refreshError="1"/>
-      <sheetData sheetId="658" refreshError="1"/>
-      <sheetData sheetId="659" refreshError="1"/>
-      <sheetData sheetId="660" refreshError="1"/>
-      <sheetData sheetId="661" refreshError="1"/>
-      <sheetData sheetId="662" refreshError="1"/>
-      <sheetData sheetId="663" refreshError="1"/>
-      <sheetData sheetId="664" refreshError="1"/>
-      <sheetData sheetId="665" refreshError="1"/>
-      <sheetData sheetId="666" refreshError="1"/>
-      <sheetData sheetId="667" refreshError="1"/>
-      <sheetData sheetId="668" refreshError="1"/>
-      <sheetData sheetId="669" refreshError="1"/>
-      <sheetData sheetId="670" refreshError="1"/>
-      <sheetData sheetId="671" refreshError="1"/>
-      <sheetData sheetId="672" refreshError="1"/>
-      <sheetData sheetId="673" refreshError="1"/>
-      <sheetData sheetId="674" refreshError="1"/>
-      <sheetData sheetId="675" refreshError="1"/>
-      <sheetData sheetId="676" refreshError="1"/>
-      <sheetData sheetId="677" refreshError="1"/>
-      <sheetData sheetId="678" refreshError="1"/>
-      <sheetData sheetId="679" refreshError="1"/>
-      <sheetData sheetId="680" refreshError="1"/>
-      <sheetData sheetId="681" refreshError="1"/>
-      <sheetData sheetId="682" refreshError="1"/>
-      <sheetData sheetId="683" refreshError="1"/>
-      <sheetData sheetId="684" refreshError="1"/>
-      <sheetData sheetId="685" refreshError="1"/>
-      <sheetData sheetId="686" refreshError="1"/>
-      <sheetData sheetId="687" refreshError="1"/>
-      <sheetData sheetId="688" refreshError="1"/>
-      <sheetData sheetId="689" refreshError="1"/>
-      <sheetData sheetId="690" refreshError="1"/>
-      <sheetData sheetId="691" refreshError="1"/>
-      <sheetData sheetId="692" refreshError="1"/>
-      <sheetData sheetId="693" refreshError="1"/>
-      <sheetData sheetId="694" refreshError="1"/>
-      <sheetData sheetId="695" refreshError="1"/>
-      <sheetData sheetId="696" refreshError="1"/>
-      <sheetData sheetId="697" refreshError="1"/>
-      <sheetData sheetId="698" refreshError="1"/>
-      <sheetData sheetId="699" refreshError="1"/>
-      <sheetData sheetId="700" refreshError="1"/>
-      <sheetData sheetId="701" refreshError="1"/>
-      <sheetData sheetId="702" refreshError="1"/>
-      <sheetData sheetId="703" refreshError="1"/>
-      <sheetData sheetId="704" refreshError="1"/>
-      <sheetData sheetId="705" refreshError="1"/>
-      <sheetData sheetId="706" refreshError="1"/>
-      <sheetData sheetId="707" refreshError="1"/>
-      <sheetData sheetId="708" refreshError="1"/>
-      <sheetData sheetId="709" refreshError="1"/>
-      <sheetData sheetId="710" refreshError="1"/>
-      <sheetData sheetId="711" refreshError="1"/>
-      <sheetData sheetId="712" refreshError="1"/>
-      <sheetData sheetId="713" refreshError="1"/>
-      <sheetData sheetId="714" refreshError="1"/>
-      <sheetData sheetId="715" refreshError="1"/>
-      <sheetData sheetId="716" refreshError="1"/>
-      <sheetData sheetId="717" refreshError="1"/>
-      <sheetData sheetId="718" refreshError="1"/>
-      <sheetData sheetId="719" refreshError="1"/>
-      <sheetData sheetId="720" refreshError="1"/>
-      <sheetData sheetId="721" refreshError="1"/>
-      <sheetData sheetId="722" refreshError="1"/>
-      <sheetData sheetId="723" refreshError="1"/>
-      <sheetData sheetId="724" refreshError="1"/>
-      <sheetData sheetId="725" refreshError="1"/>
-      <sheetData sheetId="726" refreshError="1"/>
-      <sheetData sheetId="727" refreshError="1"/>
-      <sheetData sheetId="728" refreshError="1"/>
-      <sheetData sheetId="729" refreshError="1"/>
-      <sheetData sheetId="730" refreshError="1"/>
-      <sheetData sheetId="731" refreshError="1"/>
-      <sheetData sheetId="732" refreshError="1"/>
-      <sheetData sheetId="733" refreshError="1"/>
-      <sheetData sheetId="734" refreshError="1"/>
-      <sheetData sheetId="735" refreshError="1"/>
-      <sheetData sheetId="736" refreshError="1"/>
-      <sheetData sheetId="737" refreshError="1"/>
-      <sheetData sheetId="738" refreshError="1"/>
-      <sheetData sheetId="739" refreshError="1"/>
-      <sheetData sheetId="740" refreshError="1"/>
-      <sheetData sheetId="741" refreshError="1"/>
-      <sheetData sheetId="742" refreshError="1"/>
-      <sheetData sheetId="743" refreshError="1"/>
-      <sheetData sheetId="744" refreshError="1"/>
-      <sheetData sheetId="745" refreshError="1"/>
-      <sheetData sheetId="746" refreshError="1"/>
-      <sheetData sheetId="747" refreshError="1"/>
-      <sheetData sheetId="748" refreshError="1"/>
-      <sheetData sheetId="749" refreshError="1"/>
-      <sheetData sheetId="750" refreshError="1"/>
-      <sheetData sheetId="751" refreshError="1"/>
-      <sheetData sheetId="752" refreshError="1"/>
-      <sheetData sheetId="753" refreshError="1"/>
-      <sheetData sheetId="754" refreshError="1"/>
-      <sheetData sheetId="755" refreshError="1"/>
-      <sheetData sheetId="756" refreshError="1"/>
-      <sheetData sheetId="757" refreshError="1"/>
-      <sheetData sheetId="758" refreshError="1"/>
-      <sheetData sheetId="759" refreshError="1"/>
-      <sheetData sheetId="760" refreshError="1"/>
-      <sheetData sheetId="761" refreshError="1"/>
-      <sheetData sheetId="762" refreshError="1"/>
-      <sheetData sheetId="763" refreshError="1"/>
-      <sheetData sheetId="764" refreshError="1"/>
-      <sheetData sheetId="765" refreshError="1"/>
-      <sheetData sheetId="766" refreshError="1"/>
-      <sheetData sheetId="767" refreshError="1"/>
-      <sheetData sheetId="768" refreshError="1"/>
-      <sheetData sheetId="769" refreshError="1"/>
-      <sheetData sheetId="770" refreshError="1"/>
-      <sheetData sheetId="771" refreshError="1"/>
-      <sheetData sheetId="772" refreshError="1"/>
-      <sheetData sheetId="773" refreshError="1"/>
-      <sheetData sheetId="774" refreshError="1"/>
-      <sheetData sheetId="775" refreshError="1"/>
-      <sheetData sheetId="776" refreshError="1"/>
-      <sheetData sheetId="777" refreshError="1"/>
-      <sheetData sheetId="778" refreshError="1"/>
-      <sheetData sheetId="779" refreshError="1"/>
-      <sheetData sheetId="780" refreshError="1"/>
-      <sheetData sheetId="781" refreshError="1"/>
-      <sheetData sheetId="782" refreshError="1"/>
-      <sheetData sheetId="783" refreshError="1"/>
-      <sheetData sheetId="784" refreshError="1"/>
-      <sheetData sheetId="785" refreshError="1"/>
-      <sheetData sheetId="786" refreshError="1"/>
-      <sheetData sheetId="787" refreshError="1"/>
-      <sheetData sheetId="788" refreshError="1"/>
-      <sheetData sheetId="789" refreshError="1"/>
-      <sheetData sheetId="790" refreshError="1"/>
-      <sheetData sheetId="791" refreshError="1"/>
-      <sheetData sheetId="792" refreshError="1"/>
-      <sheetData sheetId="793" refreshError="1"/>
-      <sheetData sheetId="794" refreshError="1"/>
-      <sheetData sheetId="795" refreshError="1"/>
-      <sheetData sheetId="796" refreshError="1"/>
-      <sheetData sheetId="797" refreshError="1"/>
-      <sheetData sheetId="798" refreshError="1"/>
-      <sheetData sheetId="799" refreshError="1"/>
-      <sheetData sheetId="800" refreshError="1"/>
-      <sheetData sheetId="801" refreshError="1"/>
-      <sheetData sheetId="802" refreshError="1"/>
-      <sheetData sheetId="803" refreshError="1"/>
-      <sheetData sheetId="804" refreshError="1"/>
-      <sheetData sheetId="805" refreshError="1"/>
-      <sheetData sheetId="806" refreshError="1"/>
-      <sheetData sheetId="807" refreshError="1"/>
-      <sheetData sheetId="808" refreshError="1"/>
-      <sheetData sheetId="809" refreshError="1"/>
-      <sheetData sheetId="810" refreshError="1"/>
-      <sheetData sheetId="811" refreshError="1"/>
-      <sheetData sheetId="812" refreshError="1"/>
-      <sheetData sheetId="813" refreshError="1"/>
-      <sheetData sheetId="814" refreshError="1"/>
-      <sheetData sheetId="815" refreshError="1"/>
-      <sheetData sheetId="816" refreshError="1"/>
-      <sheetData sheetId="817" refreshError="1"/>
-      <sheetData sheetId="818" refreshError="1"/>
-      <sheetData sheetId="819" refreshError="1"/>
-      <sheetData sheetId="820" refreshError="1"/>
-      <sheetData sheetId="821" refreshError="1"/>
-      <sheetData sheetId="822" refreshError="1"/>
-      <sheetData sheetId="823" refreshError="1"/>
-      <sheetData sheetId="824" refreshError="1"/>
-      <sheetData sheetId="825" refreshError="1"/>
-      <sheetData sheetId="826" refreshError="1"/>
-      <sheetData sheetId="827" refreshError="1"/>
-      <sheetData sheetId="828" refreshError="1"/>
-      <sheetData sheetId="829" refreshError="1"/>
-      <sheetData sheetId="830" refreshError="1"/>
-      <sheetData sheetId="831" refreshError="1"/>
-      <sheetData sheetId="832" refreshError="1"/>
-      <sheetData sheetId="833" refreshError="1"/>
-      <sheetData sheetId="834" refreshError="1"/>
-      <sheetData sheetId="835" refreshError="1"/>
-      <sheetData sheetId="836" refreshError="1"/>
-      <sheetData sheetId="837" refreshError="1"/>
-      <sheetData sheetId="838" refreshError="1"/>
-      <sheetData sheetId="839" refreshError="1"/>
-      <sheetData sheetId="840" refreshError="1"/>
-      <sheetData sheetId="841" refreshError="1"/>
-      <sheetData sheetId="842" refreshError="1"/>
-      <sheetData sheetId="843" refreshError="1"/>
-      <sheetData sheetId="844" refreshError="1"/>
-      <sheetData sheetId="845" refreshError="1"/>
-      <sheetData sheetId="846" refreshError="1"/>
-      <sheetData sheetId="847" refreshError="1"/>
-      <sheetData sheetId="848" refreshError="1"/>
-      <sheetData sheetId="849" refreshError="1"/>
-      <sheetData sheetId="850" refreshError="1"/>
-      <sheetData sheetId="851" refreshError="1"/>
-      <sheetData sheetId="852" refreshError="1"/>
-      <sheetData sheetId="853" refreshError="1"/>
-      <sheetData sheetId="854" refreshError="1"/>
-      <sheetData sheetId="855" refreshError="1"/>
-      <sheetData sheetId="856" refreshError="1"/>
-      <sheetData sheetId="857" refreshError="1"/>
-      <sheetData sheetId="858" refreshError="1"/>
-      <sheetData sheetId="859" refreshError="1"/>
-      <sheetData sheetId="860" refreshError="1"/>
-      <sheetData sheetId="861" refreshError="1"/>
-      <sheetData sheetId="862" refreshError="1"/>
-      <sheetData sheetId="863" refreshError="1"/>
-      <sheetData sheetId="864" refreshError="1"/>
-      <sheetData sheetId="865" refreshError="1"/>
-      <sheetData sheetId="866" refreshError="1"/>
-      <sheetData sheetId="867" refreshError="1"/>
-      <sheetData sheetId="868" refreshError="1"/>
-      <sheetData sheetId="869" refreshError="1"/>
-      <sheetData sheetId="870" refreshError="1"/>
-      <sheetData sheetId="871" refreshError="1"/>
-      <sheetData sheetId="872" refreshError="1"/>
-      <sheetData sheetId="873" refreshError="1"/>
-      <sheetData sheetId="874" refreshError="1"/>
-      <sheetData sheetId="875" refreshError="1"/>
-      <sheetData sheetId="876" refreshError="1"/>
-      <sheetData sheetId="877" refreshError="1"/>
-      <sheetData sheetId="878" refreshError="1"/>
-      <sheetData sheetId="879" refreshError="1"/>
-      <sheetData sheetId="880" refreshError="1"/>
-      <sheetData sheetId="881" refreshError="1"/>
-      <sheetData sheetId="882" refreshError="1"/>
-      <sheetData sheetId="883" refreshError="1"/>
-      <sheetData sheetId="884" refreshError="1"/>
-      <sheetData sheetId="885" refreshError="1"/>
-      <sheetData sheetId="886" refreshError="1"/>
-      <sheetData sheetId="887" refreshError="1"/>
-      <sheetData sheetId="888" refreshError="1"/>
-      <sheetData sheetId="889" refreshError="1"/>
-      <sheetData sheetId="890" refreshError="1"/>
-      <sheetData sheetId="891" refreshError="1"/>
-      <sheetData sheetId="892" refreshError="1"/>
-      <sheetData sheetId="893" refreshError="1"/>
-      <sheetData sheetId="894" refreshError="1"/>
-      <sheetData sheetId="895" refreshError="1"/>
-      <sheetData sheetId="896" refreshError="1"/>
-      <sheetData sheetId="897" refreshError="1"/>
-      <sheetData sheetId="898" refreshError="1"/>
-      <sheetData sheetId="899" refreshError="1"/>
-      <sheetData sheetId="900" refreshError="1"/>
-      <sheetData sheetId="901" refreshError="1"/>
-      <sheetData sheetId="902" refreshError="1"/>
-      <sheetData sheetId="903" refreshError="1"/>
-      <sheetData sheetId="904" refreshError="1"/>
-      <sheetData sheetId="905" refreshError="1"/>
-      <sheetData sheetId="906" refreshError="1"/>
-      <sheetData sheetId="907" refreshError="1"/>
-      <sheetData sheetId="908" refreshError="1"/>
-      <sheetData sheetId="909" refreshError="1"/>
-      <sheetData sheetId="910" refreshError="1"/>
-      <sheetData sheetId="911" refreshError="1"/>
-      <sheetData sheetId="912" refreshError="1"/>
-      <sheetData sheetId="913" refreshError="1"/>
-      <sheetData sheetId="914" refreshError="1"/>
-      <sheetData sheetId="915" refreshError="1"/>
-      <sheetData sheetId="916" refreshError="1"/>
-      <sheetData sheetId="917" refreshError="1"/>
-      <sheetData sheetId="918" refreshError="1"/>
-      <sheetData sheetId="919" refreshError="1"/>
-      <sheetData sheetId="920" refreshError="1"/>
-      <sheetData sheetId="921" refreshError="1"/>
-      <sheetData sheetId="922" refreshError="1"/>
-      <sheetData sheetId="923" refreshError="1"/>
-      <sheetData sheetId="924" refreshError="1"/>
-      <sheetData sheetId="925" refreshError="1"/>
-      <sheetData sheetId="926" refreshError="1"/>
-      <sheetData sheetId="927" refreshError="1"/>
-      <sheetData sheetId="928" refreshError="1"/>
-      <sheetData sheetId="929" refreshError="1"/>
-      <sheetData sheetId="930" refreshError="1"/>
-      <sheetData sheetId="931" refreshError="1"/>
-      <sheetData sheetId="932" refreshError="1"/>
-      <sheetData sheetId="933" refreshError="1"/>
-      <sheetData sheetId="934" refreshError="1"/>
-      <sheetData sheetId="935" refreshError="1"/>
-      <sheetData sheetId="936" refreshError="1"/>
-      <sheetData sheetId="937" refreshError="1"/>
-      <sheetData sheetId="938" refreshError="1"/>
-      <sheetData sheetId="939" refreshError="1"/>
-      <sheetData sheetId="940" refreshError="1"/>
-      <sheetData sheetId="941" refreshError="1"/>
-      <sheetData sheetId="942" refreshError="1"/>
-      <sheetData sheetId="943" refreshError="1"/>
-      <sheetData sheetId="944" refreshError="1"/>
-      <sheetData sheetId="945" refreshError="1"/>
-      <sheetData sheetId="946" refreshError="1"/>
-      <sheetData sheetId="947" refreshError="1"/>
-      <sheetData sheetId="948" refreshError="1"/>
-      <sheetData sheetId="949" refreshError="1"/>
-      <sheetData sheetId="950" refreshError="1"/>
-      <sheetData sheetId="951" refreshError="1"/>
-      <sheetData sheetId="952" refreshError="1"/>
-      <sheetData sheetId="953" refreshError="1"/>
-      <sheetData sheetId="954" refreshError="1"/>
-      <sheetData sheetId="955" refreshError="1"/>
-      <sheetData sheetId="956" refreshError="1"/>
-      <sheetData sheetId="957" refreshError="1"/>
-      <sheetData sheetId="958" refreshError="1"/>
-      <sheetData sheetId="959" refreshError="1"/>
-      <sheetData sheetId="960" refreshError="1"/>
-      <sheetData sheetId="961" refreshError="1"/>
-      <sheetData sheetId="962" refreshError="1"/>
-      <sheetData sheetId="963" refreshError="1"/>
-      <sheetData sheetId="964" refreshError="1"/>
-      <sheetData sheetId="965" refreshError="1"/>
-      <sheetData sheetId="966" refreshError="1"/>
-      <sheetData sheetId="967" refreshError="1"/>
-      <sheetData sheetId="968" refreshError="1"/>
-      <sheetData sheetId="969" refreshError="1"/>
-      <sheetData sheetId="970" refreshError="1"/>
-      <sheetData sheetId="971" refreshError="1"/>
-      <sheetData sheetId="972" refreshError="1"/>
-      <sheetData sheetId="973" refreshError="1"/>
-      <sheetData sheetId="974" refreshError="1"/>
-      <sheetData sheetId="975" refreshError="1"/>
-      <sheetData sheetId="976" refreshError="1"/>
-      <sheetData sheetId="977" refreshError="1"/>
-      <sheetData sheetId="978" refreshError="1"/>
-      <sheetData sheetId="979" refreshError="1"/>
-      <sheetData sheetId="980" refreshError="1"/>
-      <sheetData sheetId="981" refreshError="1"/>
-      <sheetData sheetId="982" refreshError="1"/>
-      <sheetData sheetId="983" refreshError="1"/>
-      <sheetData sheetId="984" refreshError="1"/>
-      <sheetData sheetId="985" refreshError="1"/>
-      <sheetData sheetId="986" refreshError="1"/>
-      <sheetData sheetId="987" refreshError="1"/>
-      <sheetData sheetId="988" refreshError="1"/>
-      <sheetData sheetId="989" refreshError="1"/>
-      <sheetData sheetId="990" refreshError="1"/>
-      <sheetData sheetId="991" refreshError="1"/>
-      <sheetData sheetId="992" refreshError="1"/>
-      <sheetData sheetId="993" refreshError="1"/>
-      <sheetData sheetId="994" refreshError="1"/>
-      <sheetData sheetId="995" refreshError="1"/>
-      <sheetData sheetId="996" refreshError="1"/>
-      <sheetData sheetId="997" refreshError="1"/>
-      <sheetData sheetId="998" refreshError="1"/>
-      <sheetData sheetId="999" refreshError="1"/>
-      <sheetData sheetId="1000" refreshError="1"/>
-      <sheetData sheetId="1001" refreshError="1"/>
-      <sheetData sheetId="1002" refreshError="1"/>
-      <sheetData sheetId="1003" refreshError="1"/>
-      <sheetData sheetId="1004" refreshError="1"/>
-      <sheetData sheetId="1005" refreshError="1"/>
-      <sheetData sheetId="1006" refreshError="1"/>
-      <sheetData sheetId="1007" refreshError="1"/>
-      <sheetData sheetId="1008" refreshError="1"/>
-      <sheetData sheetId="1009" refreshError="1"/>
-      <sheetData sheetId="1010" refreshError="1"/>
-      <sheetData sheetId="1011" refreshError="1"/>
-      <sheetData sheetId="1012" refreshError="1"/>
-      <sheetData sheetId="1013" refreshError="1"/>
-      <sheetData sheetId="1014" refreshError="1"/>
-      <sheetData sheetId="1015" refreshError="1"/>
-      <sheetData sheetId="1016" refreshError="1"/>
-      <sheetData sheetId="1017" refreshError="1"/>
-      <sheetData sheetId="1018" refreshError="1"/>
-      <sheetData sheetId="1019" refreshError="1"/>
-      <sheetData sheetId="1020" refreshError="1"/>
-      <sheetData sheetId="1021" refreshError="1"/>
-      <sheetData sheetId="1022" refreshError="1"/>
-      <sheetData sheetId="1023" refreshError="1"/>
-      <sheetData sheetId="1024" refreshError="1"/>
-      <sheetData sheetId="1025" refreshError="1"/>
-      <sheetData sheetId="1026" refreshError="1"/>
-      <sheetData sheetId="1027" refreshError="1"/>
-      <sheetData sheetId="1028"/>
-      <sheetData sheetId="1029" refreshError="1"/>
-      <sheetData sheetId="1030" refreshError="1"/>
-      <sheetData sheetId="1031" refreshError="1"/>
-      <sheetData sheetId="1032" refreshError="1"/>
-      <sheetData sheetId="1033" refreshError="1"/>
-      <sheetData sheetId="1034" refreshError="1"/>
-      <sheetData sheetId="1035" refreshError="1"/>
-      <sheetData sheetId="1036" refreshError="1"/>
-      <sheetData sheetId="1037" refreshError="1"/>
-      <sheetData sheetId="1038" refreshError="1"/>
-      <sheetData sheetId="1039" refreshError="1"/>
-      <sheetData sheetId="1040" refreshError="1"/>
-      <sheetData sheetId="1041" refreshError="1"/>
-      <sheetData sheetId="1042" refreshError="1"/>
-      <sheetData sheetId="1043" refreshError="1"/>
-      <sheetData sheetId="1044" refreshError="1"/>
-      <sheetData sheetId="1045" refreshError="1"/>
-      <sheetData sheetId="1046" refreshError="1"/>
-      <sheetData sheetId="1047" refreshError="1"/>
-      <sheetData sheetId="1048" refreshError="1"/>
-      <sheetData sheetId="1049" refreshError="1"/>
-      <sheetData sheetId="1050" refreshError="1"/>
-      <sheetData sheetId="1051" refreshError="1"/>
-      <sheetData sheetId="1052" refreshError="1"/>
-      <sheetData sheetId="1053" refreshError="1"/>
-      <sheetData sheetId="1054" refreshError="1"/>
-      <sheetData sheetId="1055" refreshError="1"/>
-      <sheetData sheetId="1056" refreshError="1"/>
-      <sheetData sheetId="1057" refreshError="1"/>
-      <sheetData sheetId="1058" refreshError="1"/>
-      <sheetData sheetId="1059" refreshError="1"/>
-      <sheetData sheetId="1060" refreshError="1"/>
-      <sheetData sheetId="1061" refreshError="1"/>
-      <sheetData sheetId="1062" refreshError="1"/>
-      <sheetData sheetId="1063" refreshError="1"/>
-      <sheetData sheetId="1064" refreshError="1"/>
-      <sheetData sheetId="1065" refreshError="1"/>
-      <sheetData sheetId="1066" refreshError="1"/>
-      <sheetData sheetId="1067" refreshError="1"/>
-      <sheetData sheetId="1068" refreshError="1"/>
-      <sheetData sheetId="1069" refreshError="1"/>
-      <sheetData sheetId="1070" refreshError="1"/>
-      <sheetData sheetId="1071" refreshError="1"/>
-      <sheetData sheetId="1072" refreshError="1"/>
-      <sheetData sheetId="1073" refreshError="1"/>
-      <sheetData sheetId="1074" refreshError="1"/>
-      <sheetData sheetId="1075" refreshError="1"/>
-      <sheetData sheetId="1076" refreshError="1"/>
-      <sheetData sheetId="1077" refreshError="1"/>
-      <sheetData sheetId="1078" refreshError="1"/>
-      <sheetData sheetId="1079" refreshError="1"/>
-      <sheetData sheetId="1080" refreshError="1"/>
-      <sheetData sheetId="1081" refreshError="1"/>
-      <sheetData sheetId="1082" refreshError="1"/>
-      <sheetData sheetId="1083" refreshError="1"/>
-      <sheetData sheetId="1084" refreshError="1"/>
-      <sheetData sheetId="1085" refreshError="1"/>
-      <sheetData sheetId="1086" refreshError="1"/>
-      <sheetData sheetId="1087" refreshError="1"/>
-      <sheetData sheetId="1088" refreshError="1"/>
-      <sheetData sheetId="1089" refreshError="1"/>
-      <sheetData sheetId="1090"/>
-      <sheetData sheetId="1091"/>
-      <sheetData sheetId="1092" refreshError="1"/>
-      <sheetData sheetId="1093" refreshError="1"/>
-      <sheetData sheetId="1094" refreshError="1"/>
-      <sheetData sheetId="1095" refreshError="1"/>
-      <sheetData sheetId="1096" refreshError="1"/>
-      <sheetData sheetId="1097" refreshError="1"/>
-      <sheetData sheetId="1098" refreshError="1"/>
-      <sheetData sheetId="1099" refreshError="1"/>
-      <sheetData sheetId="1100" refreshError="1"/>
-      <sheetData sheetId="1101" refreshError="1"/>
-      <sheetData sheetId="1102" refreshError="1"/>
-      <sheetData sheetId="1103" refreshError="1"/>
-      <sheetData sheetId="1104" refreshError="1"/>
-      <sheetData sheetId="1105" refreshError="1"/>
-      <sheetData sheetId="1106" refreshError="1"/>
-      <sheetData sheetId="1107" refreshError="1"/>
-      <sheetData sheetId="1108" refreshError="1"/>
-      <sheetData sheetId="1109" refreshError="1"/>
-      <sheetData sheetId="1110" refreshError="1"/>
-      <sheetData sheetId="1111" refreshError="1"/>
-      <sheetData sheetId="1112"/>
-      <sheetData sheetId="1113"/>
-      <sheetData sheetId="1114" refreshError="1"/>
-      <sheetData sheetId="1115" refreshError="1"/>
-      <sheetData sheetId="1116" refreshError="1"/>
-      <sheetData sheetId="1117" refreshError="1"/>
-      <sheetData sheetId="1118" refreshError="1"/>
-      <sheetData sheetId="1119" refreshError="1"/>
-      <sheetData sheetId="1120" refreshError="1"/>
-      <sheetData sheetId="1121" refreshError="1"/>
-      <sheetData sheetId="1122" refreshError="1"/>
-      <sheetData sheetId="1123" refreshError="1"/>
-      <sheetData sheetId="1124" refreshError="1"/>
-      <sheetData sheetId="1125" refreshError="1"/>
-      <sheetData sheetId="1126" refreshError="1"/>
-      <sheetData sheetId="1127" refreshError="1"/>
-      <sheetData sheetId="1128" refreshError="1"/>
-      <sheetData sheetId="1129"/>
-      <sheetData sheetId="1130" refreshError="1"/>
-      <sheetData sheetId="1131" refreshError="1"/>
-      <sheetData sheetId="1132" refreshError="1"/>
-      <sheetData sheetId="1133" refreshError="1"/>
-      <sheetData sheetId="1134" refreshError="1"/>
-      <sheetData sheetId="1135" refreshError="1"/>
-      <sheetData sheetId="1136" refreshError="1"/>
-      <sheetData sheetId="1137" refreshError="1"/>
-      <sheetData sheetId="1138" refreshError="1"/>
-      <sheetData sheetId="1139" refreshError="1"/>
-      <sheetData sheetId="1140"/>
-      <sheetData sheetId="1141"/>
-      <sheetData sheetId="1142"/>
-      <sheetData sheetId="1143" refreshError="1"/>
-      <sheetData sheetId="1144" refreshError="1"/>
-      <sheetData sheetId="1145" refreshError="1"/>
-      <sheetData sheetId="1146" refreshError="1"/>
-      <sheetData sheetId="1147" refreshError="1"/>
-      <sheetData sheetId="1148" refreshError="1"/>
-      <sheetData sheetId="1149" refreshError="1"/>
-      <sheetData sheetId="1150" refreshError="1"/>
-      <sheetData sheetId="1151" refreshError="1"/>
-      <sheetData sheetId="1152" refreshError="1"/>
-      <sheetData sheetId="1153" refreshError="1"/>
-      <sheetData sheetId="1154" refreshError="1"/>
-      <sheetData sheetId="1155" refreshError="1"/>
-      <sheetData sheetId="1156" refreshError="1"/>
-      <sheetData sheetId="1157" refreshError="1"/>
-      <sheetData sheetId="1158" refreshError="1"/>
-      <sheetData sheetId="1159" refreshError="1"/>
-      <sheetData sheetId="1160" refreshError="1"/>
-      <sheetData sheetId="1161" refreshError="1"/>
-      <sheetData sheetId="1162" refreshError="1"/>
-      <sheetData sheetId="1163" refreshError="1"/>
-      <sheetData sheetId="1164" refreshError="1"/>
-      <sheetData sheetId="1165" refreshError="1"/>
-      <sheetData sheetId="1166" refreshError="1"/>
-      <sheetData sheetId="1167" refreshError="1"/>
-      <sheetData sheetId="1168" refreshError="1"/>
-      <sheetData sheetId="1169" refreshError="1"/>
-      <sheetData sheetId="1170" refreshError="1"/>
-      <sheetData sheetId="1171" refreshError="1"/>
-      <sheetData sheetId="1172" refreshError="1"/>
-      <sheetData sheetId="1173" refreshError="1"/>
-      <sheetData sheetId="1174" refreshError="1"/>
-      <sheetData sheetId="1175" refreshError="1"/>
-      <sheetData sheetId="1176" refreshError="1"/>
-      <sheetData sheetId="1177" refreshError="1"/>
-      <sheetData sheetId="1178" refreshError="1"/>
-      <sheetData sheetId="1179" refreshError="1"/>
-      <sheetData sheetId="1180" refreshError="1"/>
-      <sheetData sheetId="1181" refreshError="1"/>
-      <sheetData sheetId="1182" refreshError="1"/>
-      <sheetData sheetId="1183" refreshError="1"/>
-      <sheetData sheetId="1184" refreshError="1"/>
-      <sheetData sheetId="1185" refreshError="1"/>
-      <sheetData sheetId="1186" refreshError="1"/>
-      <sheetData sheetId="1187" refreshError="1"/>
-      <sheetData sheetId="1188" refreshError="1"/>
-      <sheetData sheetId="1189" refreshError="1"/>
-      <sheetData sheetId="1190" refreshError="1"/>
-      <sheetData sheetId="1191" refreshError="1"/>
-      <sheetData sheetId="1192" refreshError="1"/>
-      <sheetData sheetId="1193" refreshError="1"/>
-      <sheetData sheetId="1194" refreshError="1"/>
-      <sheetData sheetId="1195" refreshError="1"/>
-      <sheetData sheetId="1196" refreshError="1"/>
-      <sheetData sheetId="1197" refreshError="1"/>
-      <sheetData sheetId="1198" refreshError="1"/>
-      <sheetData sheetId="1199" refreshError="1"/>
-      <sheetData sheetId="1200" refreshError="1"/>
-      <sheetData sheetId="1201" refreshError="1"/>
-      <sheetData sheetId="1202" refreshError="1"/>
-      <sheetData sheetId="1203" refreshError="1"/>
-      <sheetData sheetId="1204" refreshError="1"/>
-      <sheetData sheetId="1205" refreshError="1"/>
-      <sheetData sheetId="1206" refreshError="1"/>
-      <sheetData sheetId="1207" refreshError="1"/>
-      <sheetData sheetId="1208" refreshError="1"/>
-      <sheetData sheetId="1209" refreshError="1"/>
-      <sheetData sheetId="1210" refreshError="1"/>
-      <sheetData sheetId="1211" refreshError="1"/>
-      <sheetData sheetId="1212" refreshError="1"/>
-      <sheetData sheetId="1213" refreshError="1"/>
-      <sheetData sheetId="1214" refreshError="1"/>
-      <sheetData sheetId="1215" refreshError="1"/>
-      <sheetData sheetId="1216" refreshError="1"/>
-      <sheetData sheetId="1217" refreshError="1"/>
-      <sheetData sheetId="1218"/>
-      <sheetData sheetId="1219" refreshError="1"/>
-      <sheetData sheetId="1220" refreshError="1"/>
-      <sheetData sheetId="1221" refreshError="1"/>
-      <sheetData sheetId="1222" refreshError="1"/>
-      <sheetData sheetId="1223"/>
-      <sheetData sheetId="1224" refreshError="1"/>
-      <sheetData sheetId="1225" refreshError="1"/>
-      <sheetData sheetId="1226" refreshError="1"/>
-      <sheetData sheetId="1227" refreshError="1"/>
-      <sheetData sheetId="1228" refreshError="1"/>
-      <sheetData sheetId="1229"/>
-      <sheetData sheetId="1230" refreshError="1"/>
-      <sheetData sheetId="1231" refreshError="1"/>
-      <sheetData sheetId="1232" refreshError="1"/>
-      <sheetData sheetId="1233" refreshError="1"/>
-      <sheetData sheetId="1234" refreshError="1"/>
-      <sheetData sheetId="1235"/>
-      <sheetData sheetId="1236"/>
-      <sheetData sheetId="1237" refreshError="1"/>
-      <sheetData sheetId="1238" refreshError="1"/>
-      <sheetData sheetId="1239" refreshError="1"/>
-      <sheetData sheetId="1240" refreshError="1"/>
-      <sheetData sheetId="1241" refreshError="1"/>
-      <sheetData sheetId="1242" refreshError="1"/>
-      <sheetData sheetId="1243" refreshError="1"/>
-      <sheetData sheetId="1244" refreshError="1"/>
-      <sheetData sheetId="1245" refreshError="1"/>
-      <sheetData sheetId="1246" refreshError="1"/>
-      <sheetData sheetId="1247" refreshError="1"/>
-      <sheetData sheetId="1248" refreshError="1"/>
-      <sheetData sheetId="1249" refreshError="1"/>
-      <sheetData sheetId="1250" refreshError="1"/>
-      <sheetData sheetId="1251" refreshError="1"/>
-      <sheetData sheetId="1252" refreshError="1"/>
-      <sheetData sheetId="1253" refreshError="1"/>
-      <sheetData sheetId="1254" refreshError="1"/>
-      <sheetData sheetId="1255" refreshError="1"/>
-      <sheetData sheetId="1256" refreshError="1"/>
-      <sheetData sheetId="1257" refreshError="1"/>
-      <sheetData sheetId="1258" refreshError="1"/>
-      <sheetData sheetId="1259" refreshError="1"/>
-      <sheetData sheetId="1260" refreshError="1"/>
-      <sheetData sheetId="1261" refreshError="1"/>
-      <sheetData sheetId="1262" refreshError="1"/>
-      <sheetData sheetId="1263" refreshError="1"/>
-      <sheetData sheetId="1264" refreshError="1"/>
-      <sheetData sheetId="1265" refreshError="1"/>
-      <sheetData sheetId="1266" refreshError="1"/>
-      <sheetData sheetId="1267" refreshError="1"/>
-      <sheetData sheetId="1268" refreshError="1"/>
-      <sheetData sheetId="1269" refreshError="1"/>
-      <sheetData sheetId="1270" refreshError="1"/>
-      <sheetData sheetId="1271" refreshError="1"/>
-      <sheetData sheetId="1272" refreshError="1"/>
-      <sheetData sheetId="1273" refreshError="1"/>
-      <sheetData sheetId="1274" refreshError="1"/>
-      <sheetData sheetId="1275" refreshError="1"/>
-      <sheetData sheetId="1276" refreshError="1"/>
-      <sheetData sheetId="1277" refreshError="1"/>
-      <sheetData sheetId="1278" refreshError="1"/>
-      <sheetData sheetId="1279" refreshError="1"/>
-      <sheetData sheetId="1280" refreshError="1"/>
-      <sheetData sheetId="1281" refreshError="1"/>
-      <sheetData sheetId="1282" refreshError="1"/>
-      <sheetData sheetId="1283" refreshError="1"/>
-      <sheetData sheetId="1284" refreshError="1"/>
-      <sheetData sheetId="1285" refreshError="1"/>
-      <sheetData sheetId="1286" refreshError="1"/>
-      <sheetData sheetId="1287" refreshError="1"/>
-      <sheetData sheetId="1288" refreshError="1"/>
-      <sheetData sheetId="1289" refreshError="1"/>
-      <sheetData sheetId="1290" refreshError="1"/>
-      <sheetData sheetId="1291" refreshError="1"/>
-      <sheetData sheetId="1292"/>
-      <sheetData sheetId="1293" refreshError="1"/>
-      <sheetData sheetId="1294" refreshError="1"/>
-      <sheetData sheetId="1295" refreshError="1"/>
-      <sheetData sheetId="1296" refreshError="1"/>
-      <sheetData sheetId="1297" refreshError="1"/>
-      <sheetData sheetId="1298" refreshError="1"/>
-      <sheetData sheetId="1299" refreshError="1"/>
-      <sheetData sheetId="1300" refreshError="1"/>
-      <sheetData sheetId="1301" refreshError="1"/>
-      <sheetData sheetId="1302" refreshError="1"/>
-      <sheetData sheetId="1303" refreshError="1"/>
-      <sheetData sheetId="1304" refreshError="1"/>
-      <sheetData sheetId="1305" refreshError="1"/>
-      <sheetData sheetId="1306" refreshError="1"/>
-      <sheetData sheetId="1307" refreshError="1"/>
-      <sheetData sheetId="1308" refreshError="1"/>
-      <sheetData sheetId="1309" refreshError="1"/>
-      <sheetData sheetId="1310" refreshError="1"/>
-      <sheetData sheetId="1311" refreshError="1"/>
-      <sheetData sheetId="1312" refreshError="1"/>
-      <sheetData sheetId="1313" refreshError="1"/>
-      <sheetData sheetId="1314"/>
-      <sheetData sheetId="1315"/>
-      <sheetData sheetId="1316"/>
-      <sheetData sheetId="1317"/>
-      <sheetData sheetId="1318" refreshError="1"/>
-      <sheetData sheetId="1319"/>
-      <sheetData sheetId="1320"/>
-      <sheetData sheetId="1321"/>
-      <sheetData sheetId="1322"/>
-      <sheetData sheetId="1323"/>
-      <sheetData sheetId="1324"/>
-      <sheetData sheetId="1325" refreshError="1"/>
-      <sheetData sheetId="1326" refreshError="1"/>
-      <sheetData sheetId="1327" refreshError="1"/>
-      <sheetData sheetId="1328" refreshError="1"/>
-      <sheetData sheetId="1329" refreshError="1"/>
-      <sheetData sheetId="1330" refreshError="1"/>
-      <sheetData sheetId="1331" refreshError="1"/>
-      <sheetData sheetId="1332" refreshError="1"/>
-      <sheetData sheetId="1333" refreshError="1"/>
-      <sheetData sheetId="1334" refreshError="1"/>
-      <sheetData sheetId="1335" refreshError="1"/>
-      <sheetData sheetId="1336" refreshError="1"/>
-      <sheetData sheetId="1337" refreshError="1"/>
-      <sheetData sheetId="1338" refreshError="1"/>
-      <sheetData sheetId="1339"/>
-      <sheetData sheetId="1340" refreshError="1"/>
-      <sheetData sheetId="1341" refreshError="1"/>
-      <sheetData sheetId="1342" refreshError="1"/>
-      <sheetData sheetId="1343" refreshError="1"/>
-      <sheetData sheetId="1344" refreshError="1"/>
-      <sheetData sheetId="1345" refreshError="1"/>
-      <sheetData sheetId="1346" refreshError="1"/>
-      <sheetData sheetId="1347" refreshError="1"/>
-      <sheetData sheetId="1348" refreshError="1"/>
-      <sheetData sheetId="1349" refreshError="1"/>
-      <sheetData sheetId="1350" refreshError="1"/>
-      <sheetData sheetId="1351" refreshError="1"/>
-      <sheetData sheetId="1352" refreshError="1"/>
-      <sheetData sheetId="1353" refreshError="1"/>
-      <sheetData sheetId="1354" refreshError="1"/>
-      <sheetData sheetId="1355" refreshError="1"/>
-      <sheetData sheetId="1356" refreshError="1"/>
-      <sheetData sheetId="1357" refreshError="1"/>
-      <sheetData sheetId="1358" refreshError="1"/>
-      <sheetData sheetId="1359" refreshError="1"/>
-      <sheetData sheetId="1360" refreshError="1"/>
-      <sheetData sheetId="1361" refreshError="1"/>
-      <sheetData sheetId="1362" refreshError="1"/>
-      <sheetData sheetId="1363" refreshError="1"/>
-      <sheetData sheetId="1364" refreshError="1"/>
-      <sheetData sheetId="1365" refreshError="1"/>
-      <sheetData sheetId="1366" refreshError="1"/>
-      <sheetData sheetId="1367" refreshError="1"/>
-      <sheetData sheetId="1368" refreshError="1"/>
-      <sheetData sheetId="1369" refreshError="1"/>
-      <sheetData sheetId="1370" refreshError="1"/>
-      <sheetData sheetId="1371" refreshError="1"/>
-      <sheetData sheetId="1372" refreshError="1"/>
-      <sheetData sheetId="1373" refreshError="1"/>
-      <sheetData sheetId="1374" refreshError="1"/>
-      <sheetData sheetId="1375" refreshError="1"/>
-      <sheetData sheetId="1376" refreshError="1"/>
-      <sheetData sheetId="1377" refreshError="1"/>
-      <sheetData sheetId="1378" refreshError="1"/>
-      <sheetData sheetId="1379" refreshError="1"/>
-      <sheetData sheetId="1380" refreshError="1"/>
-      <sheetData sheetId="1381" refreshError="1"/>
-      <sheetData sheetId="1382" refreshError="1"/>
-      <sheetData sheetId="1383" refreshError="1"/>
-      <sheetData sheetId="1384" refreshError="1"/>
-      <sheetData sheetId="1385"/>
-      <sheetData sheetId="1386"/>
-      <sheetData sheetId="1387" refreshError="1"/>
-      <sheetData sheetId="1388" refreshError="1"/>
-      <sheetData sheetId="1389" refreshError="1"/>
-      <sheetData sheetId="1390" refreshError="1"/>
-      <sheetData sheetId="1391" refreshError="1"/>
-      <sheetData sheetId="1392" refreshError="1"/>
-      <sheetData sheetId="1393" refreshError="1"/>
-      <sheetData sheetId="1394" refreshError="1"/>
-      <sheetData sheetId="1395" refreshError="1"/>
-      <sheetData sheetId="1396" refreshError="1"/>
-      <sheetData sheetId="1397" refreshError="1"/>
-      <sheetData sheetId="1398"/>
-      <sheetData sheetId="1399"/>
-      <sheetData sheetId="1400"/>
-      <sheetData sheetId="1401" refreshError="1"/>
-      <sheetData sheetId="1402" refreshError="1"/>
-      <sheetData sheetId="1403" refreshError="1"/>
-      <sheetData sheetId="1404" refreshError="1"/>
-      <sheetData sheetId="1405" refreshError="1"/>
-      <sheetData sheetId="1406" refreshError="1"/>
-      <sheetData sheetId="1407" refreshError="1"/>
-      <sheetData sheetId="1408" refreshError="1"/>
-      <sheetData sheetId="1409" refreshError="1"/>
-      <sheetData sheetId="1410" refreshError="1"/>
-      <sheetData sheetId="1411" refreshError="1"/>
-      <sheetData sheetId="1412"/>
-      <sheetData sheetId="1413"/>
-      <sheetData sheetId="1414"/>
-      <sheetData sheetId="1415" refreshError="1"/>
-      <sheetData sheetId="1416" refreshError="1"/>
-      <sheetData sheetId="1417" refreshError="1"/>
-      <sheetData sheetId="1418" refreshError="1"/>
-      <sheetData sheetId="1419" refreshError="1"/>
-      <sheetData sheetId="1420" refreshError="1"/>
-      <sheetData sheetId="1421" refreshError="1"/>
-      <sheetData sheetId="1422" refreshError="1"/>
-      <sheetData sheetId="1423" refreshError="1"/>
-      <sheetData sheetId="1424" refreshError="1"/>
-      <sheetData sheetId="1425" refreshError="1"/>
-      <sheetData sheetId="1426" refreshError="1"/>
-      <sheetData sheetId="1427" refreshError="1"/>
-      <sheetData sheetId="1428" refreshError="1"/>
-      <sheetData sheetId="1429" refreshError="1"/>
-      <sheetData sheetId="1430" refreshError="1"/>
-      <sheetData sheetId="1431" refreshError="1"/>
-      <sheetData sheetId="1432" refreshError="1"/>
-      <sheetData sheetId="1433" refreshError="1"/>
-      <sheetData sheetId="1434" refreshError="1"/>
-      <sheetData sheetId="1435" refreshError="1"/>
-      <sheetData sheetId="1436" refreshError="1"/>
-      <sheetData sheetId="1437" refreshError="1"/>
-      <sheetData sheetId="1438" refreshError="1"/>
-      <sheetData sheetId="1439" refreshError="1"/>
-      <sheetData sheetId="1440" refreshError="1"/>
-      <sheetData sheetId="1441" refreshError="1"/>
-      <sheetData sheetId="1442" refreshError="1"/>
-      <sheetData sheetId="1443" refreshError="1"/>
-      <sheetData sheetId="1444" refreshError="1"/>
-      <sheetData sheetId="1445" refreshError="1"/>
-      <sheetData sheetId="1446" refreshError="1"/>
-      <sheetData sheetId="1447" refreshError="1"/>
-      <sheetData sheetId="1448" refreshError="1"/>
-      <sheetData sheetId="1449" refreshError="1"/>
-      <sheetData sheetId="1450" refreshError="1"/>
-      <sheetData sheetId="1451" refreshError="1"/>
-      <sheetData sheetId="1452" refreshError="1"/>
-      <sheetData sheetId="1453" refreshError="1"/>
-      <sheetData sheetId="1454" refreshError="1"/>
-      <sheetData sheetId="1455" refreshError="1"/>
-      <sheetData sheetId="1456" refreshError="1"/>
-      <sheetData sheetId="1457" refreshError="1"/>
-      <sheetData sheetId="1458" refreshError="1"/>
-      <sheetData sheetId="1459" refreshError="1"/>
-      <sheetData sheetId="1460" refreshError="1"/>
-      <sheetData sheetId="1461" refreshError="1"/>
-      <sheetData sheetId="1462" refreshError="1"/>
-      <sheetData sheetId="1463" refreshError="1"/>
-      <sheetData sheetId="1464" refreshError="1"/>
-      <sheetData sheetId="1465" refreshError="1"/>
-      <sheetData sheetId="1466" refreshError="1"/>
-      <sheetData sheetId="1467" refreshError="1"/>
-      <sheetData sheetId="1468" refreshError="1"/>
-      <sheetData sheetId="1469" refreshError="1"/>
-      <sheetData sheetId="1470" refreshError="1"/>
-      <sheetData sheetId="1471" refreshError="1"/>
-      <sheetData sheetId="1472" refreshError="1"/>
-      <sheetData sheetId="1473" refreshError="1"/>
-      <sheetData sheetId="1474" refreshError="1"/>
-      <sheetData sheetId="1475" refreshError="1"/>
-      <sheetData sheetId="1476" refreshError="1"/>
-      <sheetData sheetId="1477" refreshError="1"/>
-      <sheetData sheetId="1478" refreshError="1"/>
-      <sheetData sheetId="1479" refreshError="1"/>
-      <sheetData sheetId="1480" refreshError="1"/>
-      <sheetData sheetId="1481" refreshError="1"/>
-      <sheetData sheetId="1482" refreshError="1"/>
-      <sheetData sheetId="1483" refreshError="1"/>
-      <sheetData sheetId="1484" refreshError="1"/>
-      <sheetData sheetId="1485" refreshError="1"/>
-      <sheetData sheetId="1486" refreshError="1"/>
-      <sheetData sheetId="1487" refreshError="1"/>
-      <sheetData sheetId="1488" refreshError="1"/>
-      <sheetData sheetId="1489" refreshError="1"/>
-      <sheetData sheetId="1490" refreshError="1"/>
-      <sheetData sheetId="1491" refreshError="1"/>
-      <sheetData sheetId="1492" refreshError="1"/>
-      <sheetData sheetId="1493" refreshError="1"/>
-      <sheetData sheetId="1494" refreshError="1"/>
-      <sheetData sheetId="1495" refreshError="1"/>
-      <sheetData sheetId="1496" refreshError="1"/>
-      <sheetData sheetId="1497" refreshError="1"/>
-      <sheetData sheetId="1498" refreshError="1"/>
-      <sheetData sheetId="1499" refreshError="1"/>
-      <sheetData sheetId="1500" refreshError="1"/>
-      <sheetData sheetId="1501" refreshError="1"/>
-      <sheetData sheetId="1502" refreshError="1"/>
-      <sheetData sheetId="1503" refreshError="1"/>
-      <sheetData sheetId="1504" refreshError="1"/>
-      <sheetData sheetId="1505" refreshError="1"/>
-      <sheetData sheetId="1506" refreshError="1"/>
-      <sheetData sheetId="1507" refreshError="1"/>
-      <sheetData sheetId="1508" refreshError="1"/>
-      <sheetData sheetId="1509" refreshError="1"/>
-      <sheetData sheetId="1510" refreshError="1"/>
-      <sheetData sheetId="1511" refreshError="1"/>
-      <sheetData sheetId="1512" refreshError="1"/>
-      <sheetData sheetId="1513" refreshError="1"/>
-      <sheetData sheetId="1514" refreshError="1"/>
-      <sheetData sheetId="1515" refreshError="1"/>
-      <sheetData sheetId="1516" refreshError="1"/>
-      <sheetData sheetId="1517" refreshError="1"/>
-      <sheetData sheetId="1518" refreshError="1"/>
-      <sheetData sheetId="1519" refreshError="1"/>
-      <sheetData sheetId="1520" refreshError="1"/>
-      <sheetData sheetId="1521" refreshError="1"/>
-      <sheetData sheetId="1522" refreshError="1"/>
-      <sheetData sheetId="1523" refreshError="1"/>
-      <sheetData sheetId="1524" refreshError="1"/>
-      <sheetData sheetId="1525" refreshError="1"/>
-      <sheetData sheetId="1526" refreshError="1"/>
-      <sheetData sheetId="1527" refreshError="1"/>
-      <sheetData sheetId="1528" refreshError="1"/>
-      <sheetData sheetId="1529" refreshError="1"/>
-      <sheetData sheetId="1530" refreshError="1"/>
-      <sheetData sheetId="1531" refreshError="1"/>
-      <sheetData sheetId="1532" refreshError="1"/>
-      <sheetData sheetId="1533" refreshError="1"/>
-      <sheetData sheetId="1534" refreshError="1"/>
-      <sheetData sheetId="1535" refreshError="1"/>
-      <sheetData sheetId="1536" refreshError="1"/>
-      <sheetData sheetId="1537" refreshError="1"/>
-      <sheetData sheetId="1538" refreshError="1"/>
-      <sheetData sheetId="1539" refreshError="1"/>
-      <sheetData sheetId="1540" refreshError="1"/>
-      <sheetData sheetId="1541" refreshError="1"/>
-      <sheetData sheetId="1542" refreshError="1"/>
-      <sheetData sheetId="1543" refreshError="1"/>
-      <sheetData sheetId="1544" refreshError="1"/>
-      <sheetData sheetId="1545" refreshError="1"/>
-      <sheetData sheetId="1546" refreshError="1"/>
-      <sheetData sheetId="1547" refreshError="1"/>
-      <sheetData sheetId="1548" refreshError="1"/>
-      <sheetData sheetId="1549" refreshError="1"/>
-      <sheetData sheetId="1550" refreshError="1"/>
-      <sheetData sheetId="1551" refreshError="1"/>
-      <sheetData sheetId="1552" refreshError="1"/>
-      <sheetData sheetId="1553" refreshError="1"/>
-      <sheetData sheetId="1554" refreshError="1"/>
-      <sheetData sheetId="1555" refreshError="1"/>
-      <sheetData sheetId="1556" refreshError="1"/>
-      <sheetData sheetId="1557" refreshError="1"/>
-      <sheetData sheetId="1558" refreshError="1"/>
-      <sheetData sheetId="1559" refreshError="1"/>
-      <sheetData sheetId="1560" refreshError="1"/>
-      <sheetData sheetId="1561" refreshError="1"/>
-      <sheetData sheetId="1562" refreshError="1"/>
-      <sheetData sheetId="1563" refreshError="1"/>
-      <sheetData sheetId="1564" refreshError="1"/>
-      <sheetData sheetId="1565" refreshError="1"/>
-      <sheetData sheetId="1566" refreshError="1"/>
-      <sheetData sheetId="1567" refreshError="1"/>
-      <sheetData sheetId="1568" refreshError="1"/>
-      <sheetData sheetId="1569" refreshError="1"/>
-      <sheetData sheetId="1570" refreshError="1"/>
-      <sheetData sheetId="1571" refreshError="1"/>
-      <sheetData sheetId="1572" refreshError="1"/>
-      <sheetData sheetId="1573" refreshError="1"/>
-      <sheetData sheetId="1574" refreshError="1"/>
-      <sheetData sheetId="1575" refreshError="1"/>
-      <sheetData sheetId="1576" refreshError="1"/>
-      <sheetData sheetId="1577" refreshError="1"/>
-      <sheetData sheetId="1578" refreshError="1"/>
-      <sheetData sheetId="1579" refreshError="1"/>
-      <sheetData sheetId="1580" refreshError="1"/>
-      <sheetData sheetId="1581" refreshError="1"/>
-      <sheetData sheetId="1582" refreshError="1"/>
-      <sheetData sheetId="1583" refreshError="1"/>
-      <sheetData sheetId="1584" refreshError="1"/>
-      <sheetData sheetId="1585" refreshError="1"/>
-      <sheetData sheetId="1586" refreshError="1"/>
-      <sheetData sheetId="1587" refreshError="1"/>
-      <sheetData sheetId="1588" refreshError="1"/>
-      <sheetData sheetId="1589" refreshError="1"/>
-      <sheetData sheetId="1590" refreshError="1"/>
-      <sheetData sheetId="1591" refreshError="1"/>
-      <sheetData sheetId="1592" refreshError="1"/>
-      <sheetData sheetId="1593" refreshError="1"/>
-      <sheetData sheetId="1594" refreshError="1"/>
-      <sheetData sheetId="1595" refreshError="1"/>
-      <sheetData sheetId="1596" refreshError="1"/>
-      <sheetData sheetId="1597" refreshError="1"/>
-      <sheetData sheetId="1598" refreshError="1"/>
-      <sheetData sheetId="1599" refreshError="1"/>
-      <sheetData sheetId="1600" refreshError="1"/>
-      <sheetData sheetId="1601" refreshError="1"/>
-      <sheetData sheetId="1602" refreshError="1"/>
-      <sheetData sheetId="1603" refreshError="1"/>
-      <sheetData sheetId="1604" refreshError="1"/>
-      <sheetData sheetId="1605" refreshError="1"/>
-      <sheetData sheetId="1606" refreshError="1"/>
-      <sheetData sheetId="1607" refreshError="1"/>
-      <sheetData sheetId="1608" refreshError="1"/>
-      <sheetData sheetId="1609" refreshError="1"/>
-      <sheetData sheetId="1610" refreshError="1"/>
-      <sheetData sheetId="1611" refreshError="1"/>
-      <sheetData sheetId="1612" refreshError="1"/>
-      <sheetData sheetId="1613" refreshError="1"/>
-      <sheetData sheetId="1614" refreshError="1"/>
-      <sheetData sheetId="1615" refreshError="1"/>
-      <sheetData sheetId="1616" refreshError="1"/>
-      <sheetData sheetId="1617" refreshError="1"/>
-      <sheetData sheetId="1618" refreshError="1"/>
-      <sheetData sheetId="1619" refreshError="1"/>
-      <sheetData sheetId="1620" refreshError="1"/>
-      <sheetData sheetId="1621" refreshError="1"/>
-      <sheetData sheetId="1622" refreshError="1"/>
-      <sheetData sheetId="1623" refreshError="1"/>
-      <sheetData sheetId="1624" refreshError="1"/>
-      <sheetData sheetId="1625" refreshError="1"/>
-      <sheetData sheetId="1626" refreshError="1"/>
-      <sheetData sheetId="1627" refreshError="1"/>
-      <sheetData sheetId="1628" refreshError="1"/>
-      <sheetData sheetId="1629" refreshError="1"/>
-      <sheetData sheetId="1630" refreshError="1"/>
-      <sheetData sheetId="1631" refreshError="1"/>
-      <sheetData sheetId="1632" refreshError="1"/>
-      <sheetData sheetId="1633" refreshError="1"/>
-      <sheetData sheetId="1634" refreshError="1"/>
-      <sheetData sheetId="1635" refreshError="1"/>
-      <sheetData sheetId="1636" refreshError="1"/>
-      <sheetData sheetId="1637" refreshError="1"/>
-      <sheetData sheetId="1638" refreshError="1"/>
-      <sheetData sheetId="1639" refreshError="1"/>
-      <sheetData sheetId="1640" refreshError="1"/>
-      <sheetData sheetId="1641" refreshError="1"/>
-      <sheetData sheetId="1642" refreshError="1"/>
-      <sheetData sheetId="1643" refreshError="1"/>
-      <sheetData sheetId="1644" refreshError="1"/>
-      <sheetData sheetId="1645" refreshError="1"/>
-      <sheetData sheetId="1646" refreshError="1"/>
-      <sheetData sheetId="1647" refreshError="1"/>
-      <sheetData sheetId="1648" refreshError="1"/>
-      <sheetData sheetId="1649" refreshError="1"/>
-      <sheetData sheetId="1650" refreshError="1"/>
-      <sheetData sheetId="1651" refreshError="1"/>
-      <sheetData sheetId="1652" refreshError="1"/>
-      <sheetData sheetId="1653" refreshError="1"/>
-      <sheetData sheetId="1654" refreshError="1"/>
-      <sheetData sheetId="1655" refreshError="1"/>
-      <sheetData sheetId="1656" refreshError="1"/>
-      <sheetData sheetId="1657" refreshError="1"/>
-      <sheetData sheetId="1658" refreshError="1"/>
-      <sheetData sheetId="1659" refreshError="1"/>
-      <sheetData sheetId="1660" refreshError="1"/>
-      <sheetData sheetId="1661" refreshError="1"/>
-      <sheetData sheetId="1662" refreshError="1"/>
-      <sheetData sheetId="1663" refreshError="1"/>
-      <sheetData sheetId="1664" refreshError="1"/>
-      <sheetData sheetId="1665" refreshError="1"/>
-      <sheetData sheetId="1666" refreshError="1"/>
-      <sheetData sheetId="1667" refreshError="1"/>
-      <sheetData sheetId="1668" refreshError="1"/>
-      <sheetData sheetId="1669" refreshError="1"/>
-      <sheetData sheetId="1670" refreshError="1"/>
-      <sheetData sheetId="1671" refreshError="1"/>
-      <sheetData sheetId="1672" refreshError="1"/>
-      <sheetData sheetId="1673" refreshError="1"/>
-      <sheetData sheetId="1674" refreshError="1"/>
-      <sheetData sheetId="1675" refreshError="1"/>
-      <sheetData sheetId="1676" refreshError="1"/>
-      <sheetData sheetId="1677" refreshError="1"/>
-      <sheetData sheetId="1678" refreshError="1"/>
-      <sheetData sheetId="1679" refreshError="1"/>
-      <sheetData sheetId="1680" refreshError="1"/>
-      <sheetData sheetId="1681" refreshError="1"/>
-      <sheetData sheetId="1682" refreshError="1"/>
-      <sheetData sheetId="1683" refreshError="1"/>
-      <sheetData sheetId="1684" refreshError="1"/>
-      <sheetData sheetId="1685" refreshError="1"/>
-      <sheetData sheetId="1686" refreshError="1"/>
-      <sheetData sheetId="1687" refreshError="1"/>
-      <sheetData sheetId="1688" refreshError="1"/>
-      <sheetData sheetId="1689" refreshError="1"/>
-      <sheetData sheetId="1690" refreshError="1"/>
-      <sheetData sheetId="1691" refreshError="1"/>
-      <sheetData sheetId="1692" refreshError="1"/>
-      <sheetData sheetId="1693" refreshError="1"/>
-      <sheetData sheetId="1694" refreshError="1"/>
-      <sheetData sheetId="1695" refreshError="1"/>
-      <sheetData sheetId="1696" refreshError="1"/>
-      <sheetData sheetId="1697" refreshError="1"/>
-      <sheetData sheetId="1698" refreshError="1"/>
-      <sheetData sheetId="1699" refreshError="1"/>
-      <sheetData sheetId="1700" refreshError="1"/>
-      <sheetData sheetId="1701" refreshError="1"/>
-      <sheetData sheetId="1702" refreshError="1"/>
-      <sheetData sheetId="1703"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink3.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="索引"/>
-      <sheetName val="货币资金Cx"/>
-      <sheetName val="货币资金Mx"/>
-      <sheetName val="分录"/>
-      <sheetName val="标本-资产"/>
-      <sheetName val="企业表一"/>
-      <sheetName val="M-5C"/>
-      <sheetName val="M-5A"/>
-      <sheetName val="资产负债表"/>
-      <sheetName val="数量金额总账"/>
-      <sheetName val="设备部房屋"/>
-      <sheetName val="核算项目余额表"/>
-      <sheetName val="完"/>
-      <sheetName val="W"/>
-      <sheetName val="2004"/>
-      <sheetName val="B"/>
-      <sheetName val="表头"/>
-      <sheetName val="PER SALES ORG"/>
-      <sheetName val="1月"/>
-      <sheetName val="SW-TEO"/>
-      <sheetName val="Detailed Testing"/>
-      <sheetName val="银行借款询证"/>
-      <sheetName val="余额表"/>
-      <sheetName val="本期报表"/>
-      <sheetName val="breakdown"/>
-      <sheetName val="盈余公积 （合并)"/>
-      <sheetName val="Toolbox"/>
-      <sheetName val="eqpmad2"/>
-      <sheetName val="提足折旧"/>
-      <sheetName val="DATA"/>
-      <sheetName val="委托加工材料"/>
-      <sheetName val="材料采购-入库"/>
-      <sheetName val="原材料－其他"/>
-      <sheetName val="材料成本差异－运费等"/>
-      <sheetName val="邻酮定乙酚发出测试"/>
-      <sheetName val="管理费用(集团董事会)"/>
-      <sheetName val="Sheet1"/>
-      <sheetName val="FS"/>
-      <sheetName val="gl"/>
-      <sheetName val="Adm"/>
-      <sheetName val="sell"/>
-      <sheetName val="Fin"/>
-      <sheetName val="Erection"/>
-      <sheetName val="剥离前"/>
-      <sheetName val="XL4Poppy"/>
-      <sheetName val="08"/>
-      <sheetName val="02"/>
-      <sheetName val="03"/>
-      <sheetName val="04"/>
-      <sheetName val="05"/>
-      <sheetName val="06"/>
-      <sheetName val="07"/>
-      <sheetName val="10"/>
-      <sheetName val="09"/>
-      <sheetName val="UFPrn20031114182129"/>
-      <sheetName val="订单418"/>
-      <sheetName val="Collateral"/>
-      <sheetName val="Disposition"/>
-      <sheetName val="Validation"/>
-      <sheetName val="35.1租赁明细"/>
-      <sheetName val="中山低值"/>
-      <sheetName val="分产品销售收入、成本分析表"/>
-      <sheetName val="E1020"/>
-      <sheetName val="1月固定资产清单"/>
-      <sheetName val="关联方—创斯达"/>
-      <sheetName val="关联方—东风汽车"/>
-      <sheetName val="ZH1-4其他应收款个别认定"/>
-      <sheetName val="ZH1-3应收账款个别认定"/>
-      <sheetName val="各单位目标指标"/>
-      <sheetName val="新城资金明细"/>
-      <sheetName val="申鑫大厦租金明细"/>
-      <sheetName val="三林明细"/>
-      <sheetName val="东陆明细"/>
-      <sheetName val="4-货币资金-现金"/>
-      <sheetName val="基础信息"/>
-      <sheetName val="XREF"/>
-      <sheetName val="A430"/>
-      <sheetName val="货币资金审定表"/>
-      <sheetName val="balance"/>
-      <sheetName val="PRC-BS-SZ"/>
-      <sheetName val="A1"/>
-      <sheetName val="账面外销"/>
-      <sheetName val="销售费用Dy"/>
-      <sheetName val="细节测试审计抽样"/>
-      <sheetName val="YS02-02"/>
-      <sheetName val="短期借款Dy"/>
-      <sheetName val="采购订单3名"/>
-      <sheetName val="P12 TB SZ"/>
-      <sheetName val="选择报表"/>
-      <sheetName val="CF附注"/>
-      <sheetName val="试算平衡表"/>
-      <sheetName val="原TB表"/>
-      <sheetName val="工资"/>
-      <sheetName val="27-7"/>
-      <sheetName val="dxnsjtempsheet"/>
-      <sheetName val="５８D"/>
-      <sheetName val="存货明细表"/>
-      <sheetName val="清单12.31"/>
-      <sheetName val="短期投资股票投资.dbf"/>
-      <sheetName val="短期投资国债投资.dbf"/>
-      <sheetName val="股票投资收益.dbf"/>
-      <sheetName val="其他货币海通.dbf"/>
-      <sheetName val="其他货币零领路.dbf"/>
-      <sheetName val="投资收益债券.dbf"/>
-      <sheetName val="营业费用测试"/>
-      <sheetName val="科目余额表"/>
-      <sheetName val="凭证抽查表 "/>
-      <sheetName val="资产减值损失审核表"/>
-      <sheetName val="坯布"/>
-      <sheetName val="材料"/>
-      <sheetName val="外销"/>
-      <sheetName val="Summary"/>
-      <sheetName val="dghn"/>
-      <sheetName val="报表项目"/>
-      <sheetName val="01"/>
-      <sheetName val="010"/>
-      <sheetName val="011"/>
-      <sheetName val="012"/>
-      <sheetName val="表头（请先填写）"/>
-      <sheetName val="调整分录汇总表"/>
-      <sheetName val="明细表（账龄）D2-2"/>
-      <sheetName val="其他应付款科目余额2005.12.31"/>
-      <sheetName val="期末应付帐款明细表"/>
-      <sheetName val="期初应付帐款明细表"/>
-      <sheetName val="其他应收款－个人借款明细"/>
-      <sheetName val="生产成本"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1" refreshError="1"/>
-      <sheetData sheetId="2" refreshError="1"/>
-      <sheetData sheetId="3" refreshError="1"/>
-      <sheetData sheetId="4" refreshError="1"/>
-      <sheetData sheetId="5" refreshError="1"/>
-      <sheetData sheetId="6" refreshError="1"/>
-      <sheetData sheetId="7" refreshError="1"/>
-      <sheetData sheetId="8" refreshError="1"/>
-      <sheetData sheetId="9" refreshError="1"/>
-      <sheetData sheetId="10" refreshError="1"/>
-      <sheetData sheetId="11" refreshError="1"/>
-      <sheetData sheetId="12" refreshError="1"/>
-      <sheetData sheetId="13" refreshError="1"/>
-      <sheetData sheetId="14" refreshError="1"/>
-      <sheetData sheetId="15" refreshError="1"/>
-      <sheetData sheetId="16" refreshError="1"/>
-      <sheetData sheetId="17" refreshError="1"/>
-      <sheetData sheetId="18" refreshError="1"/>
-      <sheetData sheetId="19" refreshError="1"/>
-      <sheetData sheetId="20" refreshError="1"/>
-      <sheetData sheetId="21" refreshError="1"/>
-      <sheetData sheetId="22" refreshError="1"/>
-      <sheetData sheetId="23" refreshError="1"/>
-      <sheetData sheetId="24" refreshError="1"/>
-      <sheetData sheetId="25" refreshError="1"/>
-      <sheetData sheetId="26" refreshError="1"/>
-      <sheetData sheetId="27" refreshError="1"/>
-      <sheetData sheetId="28" refreshError="1"/>
-      <sheetData sheetId="29" refreshError="1"/>
-      <sheetData sheetId="30" refreshError="1"/>
-      <sheetData sheetId="31" refreshError="1"/>
-      <sheetData sheetId="32" refreshError="1"/>
-      <sheetData sheetId="33" refreshError="1"/>
-      <sheetData sheetId="34" refreshError="1"/>
-      <sheetData sheetId="35" refreshError="1"/>
-      <sheetData sheetId="36" refreshError="1"/>
-      <sheetData sheetId="37" refreshError="1"/>
-      <sheetData sheetId="38" refreshError="1"/>
-      <sheetData sheetId="39" refreshError="1"/>
-      <sheetData sheetId="40" refreshError="1"/>
-      <sheetData sheetId="41" refreshError="1"/>
-      <sheetData sheetId="42" refreshError="1"/>
-      <sheetData sheetId="43" refreshError="1"/>
-      <sheetData sheetId="44" refreshError="1"/>
-      <sheetData sheetId="45" refreshError="1"/>
-      <sheetData sheetId="46" refreshError="1"/>
-      <sheetData sheetId="47" refreshError="1"/>
-      <sheetData sheetId="48" refreshError="1"/>
-      <sheetData sheetId="49" refreshError="1"/>
-      <sheetData sheetId="50" refreshError="1"/>
-      <sheetData sheetId="51" refreshError="1"/>
-      <sheetData sheetId="52" refreshError="1"/>
-      <sheetData sheetId="53" refreshError="1"/>
-      <sheetData sheetId="54" refreshError="1"/>
-      <sheetData sheetId="55" refreshError="1"/>
-      <sheetData sheetId="56" refreshError="1"/>
-      <sheetData sheetId="57" refreshError="1"/>
-      <sheetData sheetId="58" refreshError="1"/>
-      <sheetData sheetId="59" refreshError="1"/>
-      <sheetData sheetId="60" refreshError="1"/>
-      <sheetData sheetId="61" refreshError="1"/>
-      <sheetData sheetId="62" refreshError="1"/>
-      <sheetData sheetId="63" refreshError="1"/>
-      <sheetData sheetId="64" refreshError="1"/>
-      <sheetData sheetId="65" refreshError="1"/>
-      <sheetData sheetId="66" refreshError="1"/>
-      <sheetData sheetId="67" refreshError="1"/>
-      <sheetData sheetId="68" refreshError="1"/>
-      <sheetData sheetId="69" refreshError="1"/>
-      <sheetData sheetId="70" refreshError="1"/>
-      <sheetData sheetId="71" refreshError="1"/>
-      <sheetData sheetId="72" refreshError="1"/>
-      <sheetData sheetId="73" refreshError="1"/>
-      <sheetData sheetId="74" refreshError="1"/>
-      <sheetData sheetId="75" refreshError="1"/>
-      <sheetData sheetId="76" refreshError="1"/>
-      <sheetData sheetId="77" refreshError="1"/>
-      <sheetData sheetId="78" refreshError="1"/>
-      <sheetData sheetId="79" refreshError="1"/>
-      <sheetData sheetId="80" refreshError="1"/>
-      <sheetData sheetId="81" refreshError="1"/>
-      <sheetData sheetId="82" refreshError="1"/>
-      <sheetData sheetId="83" refreshError="1"/>
-      <sheetData sheetId="84" refreshError="1"/>
-      <sheetData sheetId="85" refreshError="1"/>
-      <sheetData sheetId="86" refreshError="1"/>
-      <sheetData sheetId="87" refreshError="1"/>
-      <sheetData sheetId="88" refreshError="1"/>
-      <sheetData sheetId="89" refreshError="1"/>
-      <sheetData sheetId="90" refreshError="1"/>
-      <sheetData sheetId="91" refreshError="1"/>
-      <sheetData sheetId="92" refreshError="1"/>
-      <sheetData sheetId="93" refreshError="1"/>
-      <sheetData sheetId="94" refreshError="1"/>
-      <sheetData sheetId="95" refreshError="1"/>
-      <sheetData sheetId="96" refreshError="1"/>
-      <sheetData sheetId="97" refreshError="1"/>
-      <sheetData sheetId="98" refreshError="1"/>
-      <sheetData sheetId="99" refreshError="1"/>
-      <sheetData sheetId="100" refreshError="1"/>
-      <sheetData sheetId="101" refreshError="1"/>
-      <sheetData sheetId="102" refreshError="1"/>
-      <sheetData sheetId="103" refreshError="1"/>
-      <sheetData sheetId="104" refreshError="1"/>
-      <sheetData sheetId="105" refreshError="1"/>
-      <sheetData sheetId="106" refreshError="1"/>
-      <sheetData sheetId="107" refreshError="1"/>
-      <sheetData sheetId="108" refreshError="1"/>
-      <sheetData sheetId="109" refreshError="1"/>
-      <sheetData sheetId="110" refreshError="1"/>
-      <sheetData sheetId="111" refreshError="1"/>
-      <sheetData sheetId="112" refreshError="1"/>
-      <sheetData sheetId="113" refreshError="1"/>
-      <sheetData sheetId="114" refreshError="1"/>
-      <sheetData sheetId="115" refreshError="1"/>
-      <sheetData sheetId="116" refreshError="1"/>
-      <sheetData sheetId="117" refreshError="1"/>
-      <sheetData sheetId="118" refreshError="1"/>
-      <sheetData sheetId="119" refreshError="1"/>
-      <sheetData sheetId="120" refreshError="1"/>
-      <sheetData sheetId="121" refreshError="1"/>
-      <sheetData sheetId="122" refreshError="1"/>
-      <sheetData sheetId="123" refreshError="1"/>
-      <sheetData sheetId="124" refreshError="1"/>
-      <sheetData sheetId="125" refreshError="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题​​">
   <a:themeElements>
